--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366411710604278</v>
+        <v>1.366435215093077</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.358716602164165</v>
+        <v>1.358759429947561</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.355675419741639</v>
+        <v>1.355726410825832</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.34958129601524</v>
+        <v>1.349654884820659</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347249476787336</v>
+        <v>1.347326311174473</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343045593369671</v>
+        <v>1.34312530812603</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.338589412849104</v>
+        <v>1.3386708491383</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336123615393827</v>
+        <v>1.336205828296242</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339371011886543</v>
+        <v>1.339421198829941</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334145782583904</v>
+        <v>1.334138030909462</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335074883364525</v>
+        <v>1.335065826648596</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332914225801054</v>
+        <v>1.332903817486291</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332746675716926</v>
+        <v>1.332714111710153</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.33006165411559</v>
+        <v>1.330035332435432</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328177589864661</v>
+        <v>1.328156529084794</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331432496880012</v>
+        <v>1.331416037029497</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329266292422152</v>
+        <v>1.329283643730717</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.323871306391097</v>
+        <v>1.323912688174463</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.318890694657618</v>
+        <v>1.318949384168603</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.31823930343308</v>
+        <v>1.318341633828067</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.315610799362853</v>
+        <v>1.315691570732521</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.319663508660375</v>
+        <v>1.319717824473229</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.319311340414894</v>
+        <v>1.319253677130596</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.314481892393355</v>
+        <v>1.314354516996707</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.312885244441357</v>
+        <v>1.312690402411548</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.306508279249057</v>
+        <v>1.306273412704983</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.297293562756569</v>
+        <v>1.297010223150652</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.294297505046214</v>
+        <v>1.293969138801053</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.298547465327815</v>
+        <v>1.298231575986862</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.317542626699041</v>
+        <v>1.317047104624338</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.330568508631175</v>
+        <v>1.330046361772239</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.359538833792441</v>
+        <v>1.359268906723299</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.375226949982457</v>
+        <v>1.375183686274521</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.379905901247062</v>
+        <v>1.379948409296731</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.388099398458248</v>
+        <v>1.388238943036264</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.38914448676836</v>
+        <v>1.389346140074408</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.386391016975772</v>
+        <v>1.386696770073965</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.384949227806556</v>
+        <v>1.385346078746267</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.387030954976693</v>
+        <v>1.387635822758624</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.38290801187807</v>
+        <v>1.383549727998415</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.386013974912246</v>
+        <v>1.386702342257669</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.370808002285425</v>
+        <v>1.371289079316832</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.366248547389151</v>
+        <v>1.366693631379306</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.355135354071797</v>
+        <v>1.35537946218197</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339987810400924</v>
+        <v>1.339277152846722</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331692182443229</v>
+        <v>1.33236076998493</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336057571564437</v>
+        <v>1.336023217987793</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.33867316013579</v>
+        <v>1.338318306111257</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.33920425626149</v>
+        <v>1.339095060675793</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.341927581476461</v>
+        <v>1.341761121750187</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.343376219949268</v>
+        <v>1.343608756683762</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.346859818172665</v>
+        <v>1.347116637174987</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.346758001230479</v>
+        <v>1.347530751823174</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.350584362833563</v>
+        <v>1.351471900941884</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.351395622406441</v>
+        <v>1.353377831776619</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.351002265996508</v>
+        <v>1.353656138021406</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.350375283334148</v>
+        <v>1.355029183811003</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347229832030073</v>
+        <v>1.356041859800842</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,15 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.3321</v>
+        <v>1.356337442537088</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B101">
+        <v>1.368646842618728</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366435215093077</v>
+        <v>1.366446086489516</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.358759429947561</v>
+        <v>1.358779247273995</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.355726410825832</v>
+        <v>1.355750024593756</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.349654884820659</v>
+        <v>1.349688959855019</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347326311174473</v>
+        <v>1.347361887159839</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.34312530812603</v>
+        <v>1.343162215735168</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.3386708491383</v>
+        <v>1.338708553069991</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336205828296242</v>
+        <v>1.336243892471877</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339421198829941</v>
+        <v>1.339444531290147</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334138030909462</v>
+        <v>1.334134487947946</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335065826648596</v>
+        <v>1.335061681100798</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332903817486291</v>
+        <v>1.332899047529454</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332714111710153</v>
+        <v>1.332699100786788</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.330035332435432</v>
+        <v>1.330023181363573</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328156529084794</v>
+        <v>1.328146792378113</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331416037029497</v>
+        <v>1.331408424155383</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329283643730717</v>
+        <v>1.329291610233641</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.323912688174463</v>
+        <v>1.323931773883726</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.318949384168603</v>
+        <v>1.318976465893367</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.318341633828067</v>
+        <v>1.318389023395137</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.315691570732521</v>
+        <v>1.315729195116189</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.319717824473229</v>
+        <v>1.319743333015971</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.319253677130596</v>
+        <v>1.319227262587537</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.314354516996707</v>
+        <v>1.314295840321286</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.312690402411548</v>
+        <v>1.312600499735159</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.306273412704983</v>
+        <v>1.306164930276523</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.297010223150652</v>
+        <v>1.296879256672608</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.293969138801053</v>
+        <v>1.293817250170985</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.298231575986862</v>
+        <v>1.298085300285419</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.317047104624338</v>
+        <v>1.316817013827262</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.330046361772239</v>
+        <v>1.329803907949373</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.359268906723299</v>
+        <v>1.359143136957565</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.375183686274521</v>
+        <v>1.375163336075162</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.379948409296731</v>
+        <v>1.3799675414666</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.388238943036264</v>
+        <v>1.388302773914962</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.389346140074408</v>
+        <v>1.389438402659615</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.386696770073965</v>
+        <v>1.386837260020477</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.385346078746267</v>
+        <v>1.385528794463675</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.387635822758624</v>
+        <v>1.387916149871046</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.383549727998415</v>
+        <v>1.383847614174289</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.386702342257669</v>
+        <v>1.387022179427081</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.371289079316832</v>
+        <v>1.371513456211256</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.366693631379306</v>
+        <v>1.366901748487866</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.35537946218197</v>
+        <v>1.355494449929323</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339277152846722</v>
+        <v>1.339280731037548</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.33236076998493</v>
+        <v>1.332279551682509</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336023217987793</v>
+        <v>1.336891504319206</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338318306111257</v>
+        <v>1.339057280064206</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339095060675793</v>
+        <v>1.340049121654504</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.341761121750187</v>
+        <v>1.342832399431968</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.343608756683762</v>
+        <v>1.344861189671835</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.347116637174987</v>
+        <v>1.348351789240373</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.347530751823174</v>
+        <v>1.34912860531977</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.351471900941884</v>
+        <v>1.352954376691982</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.353377831776619</v>
+        <v>1.355038132520868</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.353656138021406</v>
+        <v>1.356793997176424</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.355029183811003</v>
+        <v>1.358847949589684</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.356041859800842</v>
+        <v>1.3607482422682</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.356337442537088</v>
+        <v>1.362641280881585</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,15 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.368646842618728</v>
+        <v>1.372083415632334</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B102">
+        <v>1.371023311740402</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.339057280064206</v>
+        <v>1.339073208421779</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.340049121654504</v>
+        <v>1.340067397386124</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.342832399431968</v>
+        <v>1.3428544013467</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.344861189671835</v>
+        <v>1.344867784536282</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.348351789240373</v>
+        <v>1.348376711420542</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.34912860531977</v>
+        <v>1.34919827532969</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.352954376691982</v>
+        <v>1.352989611316955</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.355038132520868</v>
+        <v>1.355060755251103</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.356793997176424</v>
+        <v>1.356933900356258</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.358847949589684</v>
+        <v>1.359037344455757</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.3607482422682</v>
+        <v>1.361060157377888</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.362641280881585</v>
+        <v>1.362397643284218</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.372083415632334</v>
+        <v>1.371711098570247</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.371023311740402</v>
+        <v>1.370615582579354</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B102"/>
+  <dimension ref="A1:B103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.371711098570247</v>
+        <v>1.371514084322237</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,15 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.370615582579354</v>
+        <v>1.369911777469477</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B103">
+        <v>1.365847469006765</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B103"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366446086489516</v>
+        <v>1.366456427897366</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.358779247273995</v>
+        <v>1.358798103423411</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.355750024593756</v>
+        <v>1.355772504232855</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.349688959855019</v>
+        <v>1.349721396149728</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347361887159839</v>
+        <v>1.347395751104796</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343162215735168</v>
+        <v>1.3431973460198</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.338708553069991</v>
+        <v>1.338744440896482</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336243892471877</v>
+        <v>1.336280123591902</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339444531290147</v>
+        <v>1.339466796458775</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334134487947946</v>
+        <v>1.334131142576339</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335061681100798</v>
+        <v>1.335057763123286</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332899047529454</v>
+        <v>1.332894536017212</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332699100786788</v>
+        <v>1.332684851557163</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.330023181363573</v>
+        <v>1.330011636571937</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328146792378113</v>
+        <v>1.328137532992047</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331408424155383</v>
+        <v>1.331401182608113</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329291610233641</v>
+        <v>1.329299153718019</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.323931773883726</v>
+        <v>1.32394989680855</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.318976465893367</v>
+        <v>1.319002189465684</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.318389023395137</v>
+        <v>1.318434137068432</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.315729195116189</v>
+        <v>1.315765140730309</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.319743333015971</v>
+        <v>1.319767824508264</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.319227262587537</v>
+        <v>1.319202287237663</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.314295840321286</v>
+        <v>1.314240166137796</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.312600499735159</v>
+        <v>1.312515111037382</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.306164930276523</v>
+        <v>1.306061829485719</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.296879256672608</v>
+        <v>1.29675473201236</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.293817250170985</v>
+        <v>1.293672768575524</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.298085300285419</v>
+        <v>1.297946061856574</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.316817013827262</v>
+        <v>1.316597617705821</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.329803907949373</v>
+        <v>1.329572723272645</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.359143136957565</v>
+        <v>1.359022959145919</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.375163336075162</v>
+        <v>1.375143781120826</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.3799675414666</v>
+        <v>1.379985431366799</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.388302773914962</v>
+        <v>1.38836307300028</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.389438402659615</v>
+        <v>1.38952556970473</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.386837260020477</v>
+        <v>1.386970345110135</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.385528794463675</v>
+        <v>1.385702095326058</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.387916149871046</v>
+        <v>1.388183127002748</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.383847614174289</v>
+        <v>1.384131594601484</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.387022179427081</v>
+        <v>1.387327263466364</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.371513456211256</v>
+        <v>1.371727986041199</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.366901748487866</v>
+        <v>1.367101040497663</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.355494449929323</v>
+        <v>1.355605057418752</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339280731037548</v>
+        <v>1.339284526816627</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.332279551682509</v>
+        <v>1.332201960096884</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336891504319206</v>
+        <v>1.337637983883946</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.339073208421779</v>
+        <v>1.339700039916706</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.340067397386124</v>
+        <v>1.34083011113433</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.3428544013467</v>
+        <v>1.343598280158347</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.344867784536282</v>
+        <v>1.345671167327715</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.348376711420542</v>
+        <v>1.349112037712729</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.34919827532969</v>
+        <v>1.350198030545259</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.352989611316955</v>
+        <v>1.353792848628332</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.355060755251103</v>
+        <v>1.355921847716171</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.356933900356258</v>
+        <v>1.358763834228212</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.359037344455757</v>
+        <v>1.361169171254878</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.361060157377888</v>
+        <v>1.36355831640572</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.362397643284218</v>
+        <v>1.365006344424422</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.371514084322237</v>
+        <v>1.370888259887359</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.369911777469477</v>
+        <v>1.36754524531205</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,15 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.365847469006765</v>
+        <v>1.363306013929949</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B104">
+        <v>1.356452572610706</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366456427897366</v>
+        <v>1.366466277143259</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.358798103423411</v>
+        <v>1.358816066640765</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.355772504232855</v>
+        <v>1.355793929465748</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.349721396149728</v>
+        <v>1.349752309030178</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347395751104796</v>
+        <v>1.347428023571916</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.3431973460198</v>
+        <v>1.343230824224801</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.338744440896482</v>
+        <v>1.338778640626713</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336280123591902</v>
+        <v>1.336314650832654</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339466796458775</v>
+        <v>1.339488065537245</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334131142576339</v>
+        <v>1.334127978954272</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335057763123286</v>
+        <v>1.335054054694421</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332894536017212</v>
+        <v>1.332890262694461</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332684851557163</v>
+        <v>1.332671307652949</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.330011636571937</v>
+        <v>1.330000653947386</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328137532992047</v>
+        <v>1.3281287167106</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331401182608113</v>
+        <v>1.331394285917352</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329299153718019</v>
+        <v>1.329306306746063</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.32394989680855</v>
+        <v>1.323967127651864</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319002189465684</v>
+        <v>1.319026654106065</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.318434137068432</v>
+        <v>1.31847713462716</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.315765140730309</v>
+        <v>1.315799516237684</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.319767824508264</v>
+        <v>1.319791355634872</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.319202287237663</v>
+        <v>1.319178638502511</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.314240166137796</v>
+        <v>1.314187271840877</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.312515111037382</v>
+        <v>1.312433907566358</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.306061829485719</v>
+        <v>1.305963723244025</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.29675473201236</v>
+        <v>1.296636189987427</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.293672768575524</v>
+        <v>1.293535170867854</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.297946061856574</v>
+        <v>1.297813368492383</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.316597617705821</v>
+        <v>1.316388193058646</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.329572723272645</v>
+        <v>1.329352045625974</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.359022959145919</v>
+        <v>1.358908012925684</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.375143781120826</v>
+        <v>1.375124980002772</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.379985431366799</v>
+        <v>1.380002189821639</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.38836307300028</v>
+        <v>1.388420120362411</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.38952556970473</v>
+        <v>1.389608042458327</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.386970345110135</v>
+        <v>1.387096585732545</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.385702095326058</v>
+        <v>1.385866678764053</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.388183127002748</v>
+        <v>1.388437676569382</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.384131594601484</v>
+        <v>1.384402608788269</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.387327263466364</v>
+        <v>1.38761858098274</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.371727986041199</v>
+        <v>1.371933292583749</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.367101040497663</v>
+        <v>1.367292043238108</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.355605057418752</v>
+        <v>1.355711513915812</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339284526816627</v>
+        <v>1.339288501234741</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.332201960096884</v>
+        <v>1.332127761762825</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.337637983883946</v>
+        <v>1.33758886374868</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.339700039916706</v>
+        <v>1.33917998984262</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.34083011113433</v>
+        <v>1.339965644104631</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.343598280158347</v>
+        <v>1.342552355509106</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.345671167327715</v>
+        <v>1.344242411260012</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.349112037712729</v>
+        <v>1.347021317983925</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.350198030545259</v>
+        <v>1.347567314065958</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.353792848628332</v>
+        <v>1.3504016883072</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.355921847716171</v>
+        <v>1.351595177782734</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.358763834228212</v>
+        <v>1.353318679657179</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.361169171254878</v>
+        <v>1.354839485122797</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.36355831640572</v>
+        <v>1.356050496139299</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.365006344424422</v>
+        <v>1.355447540362102</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.370888259887359</v>
+        <v>1.353760479355568</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.36754524531205</v>
+        <v>1.343368408336602</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.363306013929949</v>
+        <v>1.336506267527984</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.356452572610706</v>
+        <v>1.318618767527984</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366466277143259</v>
+        <v>1.366475668538401</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.358816066640765</v>
+        <v>1.358833198862187</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.355793929465748</v>
+        <v>1.355814372720056</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.349752309030178</v>
+        <v>1.349781803258699</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347428023571916</v>
+        <v>1.347458814073794</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343230824224801</v>
+        <v>1.343262764108089</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.338778640626713</v>
+        <v>1.338811268526222</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336314650832654</v>
+        <v>1.336347591522403</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339488065537245</v>
+        <v>1.339508403568239</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334127978954272</v>
+        <v>1.334124982871608</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335054054694421</v>
+        <v>1.335050539629226</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332890262694461</v>
+        <v>1.332886209353006</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332671307652949</v>
+        <v>1.332658418119076</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.330000653947386</v>
+        <v>1.329990193541335</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.3281287167106</v>
+        <v>1.328120312507994</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331394285917352</v>
+        <v>1.3313877100658</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329306306746063</v>
+        <v>1.329313098643077</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.323967127651864</v>
+        <v>1.323983530389848</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319026654106065</v>
+        <v>1.319049949638333</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.31847713462716</v>
+        <v>1.318518161265418</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.315799516237684</v>
+        <v>1.315832421240216</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.319791355634872</v>
+        <v>1.319813979260304</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.319178638502511</v>
+        <v>1.319156215095318</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.314187271840877</v>
+        <v>1.314136956123239</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.312433907566358</v>
+        <v>1.312356591490631</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.305963723244025</v>
+        <v>1.305870260400145</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.296636189987427</v>
+        <v>1.296523213639212</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.293535170867854</v>
+        <v>1.293403981532754</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.297813368492383</v>
+        <v>1.297686772518478</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.316388193058646</v>
+        <v>1.31618807996142</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.329352045625974</v>
+        <v>1.329141179588285</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.358908012925684</v>
+        <v>1.358797967826743</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.375124980002772</v>
+        <v>1.37510689363567</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380002189821639</v>
+        <v>1.380017915316404</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.388420120362411</v>
+        <v>1.388474167650855</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.389608042458327</v>
+        <v>1.389686181864799</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.387096585732545</v>
+        <v>1.387216487940978</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.385866678764053</v>
+        <v>1.386023175966996</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.388437676569382</v>
+        <v>1.388680638724694</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.384402608788269</v>
+        <v>1.384661514556612</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.38761858098274</v>
+        <v>1.387897033546705</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.371933292583749</v>
+        <v>1.372129949012601</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.367292043238108</v>
+        <v>1.367475251359991</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.355711513915812</v>
+        <v>1.355814034693148</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339288501234741</v>
+        <v>1.339292620725855</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.332127761762825</v>
+        <v>1.332056742441</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.33758886374868</v>
+        <v>1.33754184653876</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.33917998984262</v>
+        <v>1.339151092362434</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339965644104631</v>
+        <v>1.339989075845228</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.342552355509106</v>
+        <v>1.342446484606932</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.344242411260012</v>
+        <v>1.344038772591555</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.347021317983925</v>
+        <v>1.346841620345542</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.347567314065958</v>
+        <v>1.347504111602518</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.3504016883072</v>
+        <v>1.350016604942976</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.351595177782734</v>
+        <v>1.351086493226023</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.353318679657179</v>
+        <v>1.352778469747084</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.354839485122797</v>
+        <v>1.354606122205487</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.356050496139299</v>
+        <v>1.356727172628103</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.355447540362102</v>
+        <v>1.357218937713899</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.353760479355568</v>
+        <v>1.356757039645325</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.343368408336602</v>
+        <v>1.348812066076438</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.336506267527984</v>
+        <v>1.342454169285812</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.318618767527984</v>
+        <v>1.330081421661184</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -30,8 +30,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -47,7 +55,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,13 +63,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -357,22 +383,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>44743</v>
       </c>
       <c r="B2">
@@ -380,7 +406,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>44778</v>
       </c>
       <c r="B3">
@@ -388,7 +414,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>44806</v>
       </c>
       <c r="B4">
@@ -396,7 +422,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>44834</v>
       </c>
       <c r="B5">
@@ -404,7 +430,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>44869</v>
       </c>
       <c r="B6">
@@ -412,7 +438,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>44897</v>
       </c>
       <c r="B7">
@@ -420,7 +446,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>44932</v>
       </c>
       <c r="B8">
@@ -428,7 +454,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>44960</v>
       </c>
       <c r="B9">
@@ -436,7 +462,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>44988</v>
       </c>
       <c r="B10">
@@ -444,7 +470,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>45016</v>
       </c>
       <c r="B11">
@@ -452,7 +478,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <v>45051</v>
       </c>
       <c r="B12">
@@ -460,7 +486,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2">
+      <c r="A13" s="3">
         <v>45079</v>
       </c>
       <c r="B13">
@@ -468,7 +494,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <v>45107</v>
       </c>
       <c r="B14">
@@ -476,7 +502,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2">
+      <c r="A15" s="3">
         <v>45142</v>
       </c>
       <c r="B15">
@@ -484,7 +510,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>45170</v>
       </c>
       <c r="B16">
@@ -492,7 +518,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2">
+      <c r="A17" s="3">
         <v>45205</v>
       </c>
       <c r="B17">
@@ -500,7 +526,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="2">
+      <c r="A18" s="3">
         <v>45233</v>
       </c>
       <c r="B18">
@@ -508,7 +534,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>45261</v>
       </c>
       <c r="B19">
@@ -516,7 +542,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>45296</v>
       </c>
       <c r="B20">
@@ -524,7 +550,7 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>45324</v>
       </c>
       <c r="B21">
@@ -532,7 +558,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <v>45352</v>
       </c>
       <c r="B22">
@@ -540,7 +566,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <v>45387</v>
       </c>
       <c r="B23">
@@ -548,7 +574,7 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="2">
+      <c r="A24" s="3">
         <v>45415</v>
       </c>
       <c r="B24">
@@ -556,7 +582,7 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="2">
+      <c r="A25" s="3">
         <v>45443</v>
       </c>
       <c r="B25">
@@ -564,7 +590,7 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <v>45478</v>
       </c>
       <c r="B26">
@@ -572,7 +598,7 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <v>45506</v>
       </c>
       <c r="B27">
@@ -580,7 +606,7 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <v>45541</v>
       </c>
       <c r="B28">
@@ -588,7 +614,7 @@
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="2">
+      <c r="A29" s="3">
         <v>45569</v>
       </c>
       <c r="B29">
@@ -596,7 +622,7 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <v>45597</v>
       </c>
       <c r="B30">
@@ -604,7 +630,7 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="2">
+      <c r="A31" s="3">
         <v>45632</v>
       </c>
       <c r="B31">
@@ -612,7 +638,7 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <v>45660</v>
       </c>
       <c r="B32">
@@ -620,7 +646,7 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>45688</v>
       </c>
       <c r="B33">
@@ -628,7 +654,7 @@
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <v>45716</v>
       </c>
       <c r="B34">
@@ -636,7 +662,7 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <v>45751</v>
       </c>
       <c r="B35">
@@ -644,7 +670,7 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <v>45779</v>
       </c>
       <c r="B36">
@@ -652,7 +678,7 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>45814</v>
       </c>
       <c r="B37">
@@ -660,7 +686,7 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <v>45821</v>
       </c>
       <c r="B38">
@@ -668,7 +694,7 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <v>45828</v>
       </c>
       <c r="B39">
@@ -676,7 +702,7 @@
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <v>45835</v>
       </c>
       <c r="B40">
@@ -684,7 +710,7 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="2">
+      <c r="A41" s="3">
         <v>45842</v>
       </c>
       <c r="B41">
@@ -692,507 +718,515 @@
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="2">
+      <c r="A42" s="3">
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366475668538401</v>
+        <v>1.366484633277613</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="2">
+      <c r="A43" s="3">
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.358833198862187</v>
+        <v>1.358849556427267</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="2">
+      <c r="A44" s="3">
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.355814372720056</v>
+        <v>1.355833899943489</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="2">
+      <c r="A45" s="3">
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.349781803258699</v>
+        <v>1.349809974215763</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="2">
+      <c r="A46" s="3">
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347458814073794</v>
+        <v>1.347488222309511</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="2">
+      <c r="A47" s="3">
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343262764108089</v>
+        <v>1.343293269226868</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="2">
+      <c r="A48" s="3">
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.338811268526222</v>
+        <v>1.33884243043244</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="2">
+      <c r="A49" s="3">
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336347591522403</v>
+        <v>1.336379052468101</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="2">
+      <c r="A50" s="3">
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339508403568239</v>
+        <v>1.339527870083249</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="2">
+      <c r="A51" s="3">
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334124982871608</v>
+        <v>1.33412214154583</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="2">
+      <c r="A52" s="3">
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335050539629226</v>
+        <v>1.335047203352938</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="2">
+      <c r="A53" s="3">
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332886209353006</v>
+        <v>1.332882359580955</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="2">
+      <c r="A54" s="3">
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332658418119076</v>
+        <v>1.332646136780705</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="2">
+      <c r="A55" s="3">
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329990193541335</v>
+        <v>1.329980219091096</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="2">
+      <c r="A56" s="3">
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328120312507994</v>
+        <v>1.32811229218572</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="2">
+      <c r="A57" s="3">
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.3313877100658</v>
+        <v>1.331381433211962</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="2">
+      <c r="A58" s="3">
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329313098643077</v>
+        <v>1.329319555887724</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="2">
+      <c r="A59" s="3">
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.323983530389848</v>
+        <v>1.323999163050091</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="2">
+      <c r="A60" s="3">
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319049949638333</v>
+        <v>1.319072157572249</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="2">
+      <c r="A61" s="3">
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.318518161265418</v>
+        <v>1.31855734921606</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="2">
+      <c r="A62" s="3">
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.315832421240216</v>
+        <v>1.315863947189986</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="2">
+      <c r="A63" s="3">
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.319813979260304</v>
+        <v>1.319835744702146</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="2">
+      <c r="A64" s="3">
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.319156215095318</v>
+        <v>1.319134925654852</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="2">
+      <c r="A65" s="3">
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.314136956123239</v>
+        <v>1.314089036506344</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="2">
+      <c r="A66" s="3">
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.312356591490631</v>
+        <v>1.312282892373458</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="2">
+      <c r="A67" s="3">
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.305870260400145</v>
+        <v>1.305781121697778</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="2">
+      <c r="A68" s="3">
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.296523213639212</v>
+        <v>1.296415423531899</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="2">
+      <c r="A69" s="3">
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.293403981532754</v>
+        <v>1.293278767439869</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="2">
+      <c r="A70" s="3">
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.297686772518478</v>
+        <v>1.297565865903457</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="2">
+      <c r="A71" s="3">
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.31618807996142</v>
+        <v>1.315996675048443</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="2">
+      <c r="A72" s="3">
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.329141179588285</v>
+        <v>1.328939489349963</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="2">
+      <c r="A73" s="3">
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.358797967826743</v>
+        <v>1.358692520283714</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="2">
+      <c r="A74" s="3">
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.37510689363567</v>
+        <v>1.375089485175712</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="2">
+      <c r="A75" s="3">
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380017915316404</v>
+        <v>1.3800326956246</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="2">
+      <c r="A76" s="3">
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.388474167650855</v>
+        <v>1.388525441565975</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="2">
+      <c r="A77" s="3">
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.389686181864799</v>
+        <v>1.389760313427537</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="2">
+      <c r="A78" s="3">
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.387216487940978</v>
+        <v>1.387330509798802</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="2">
+      <c r="A79" s="3">
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.386023175966996</v>
+        <v>1.386172159464055</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="2">
+      <c r="A80" s="3">
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.388680638724694</v>
+        <v>1.388912780242737</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="2">
+      <c r="A81" s="3">
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.384661514556612</v>
+        <v>1.384909096610065</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="2">
+      <c r="A82" s="3">
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.387897033546705</v>
+        <v>1.388163446546211</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="2">
+      <c r="A83" s="3">
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.372129949012601</v>
+        <v>1.37231848281154</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="2">
+      <c r="A84" s="3">
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.367475251359991</v>
+        <v>1.367651122054865</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="2">
+      <c r="A85" s="3">
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.355814034693148</v>
+        <v>1.355912821842451</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="2">
+      <c r="A86" s="3">
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339292620725855</v>
+        <v>1.339296856341011</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="2">
+      <c r="A87" s="3">
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.332056742441</v>
+        <v>1.331988705224737</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="2">
+      <c r="A88" s="3">
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.33754184653876</v>
+        <v>1.337496802363983</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="2">
+      <c r="A89" s="3">
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.339151092362434</v>
+        <v>1.339123348680198</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="2">
+      <c r="A90" s="3">
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339989075845228</v>
+        <v>1.339960449352046</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="2">
+      <c r="A91" s="3">
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.342446484606932</v>
+        <v>1.340841467820751</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="2">
+      <c r="A92" s="3">
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.344038772591555</v>
+        <v>1.341981852430609</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="2">
+      <c r="A93" s="3">
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.346841620345542</v>
+        <v>1.344332847311346</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="2">
+      <c r="A94" s="3">
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.347504111602518</v>
+        <v>1.344168038777756</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="2">
+      <c r="A95" s="3">
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.350016604942976</v>
+        <v>1.345827930241866</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="2">
+      <c r="A96" s="3">
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.351086493226023</v>
+        <v>1.346033261768651</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="2">
+      <c r="A97" s="3">
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.352778469747084</v>
+        <v>1.346761902651822</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="2">
+      <c r="A98" s="3">
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.354606122205487</v>
+        <v>1.347799730863393</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="2">
+      <c r="A99" s="3">
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.356727172628103</v>
+        <v>1.349232460179564</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="2">
+      <c r="A100" s="3">
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.357218937713899</v>
+        <v>1.348956919848281</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="2">
+      <c r="A101" s="3">
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.356757039645325</v>
+        <v>1.346254157037531</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="2">
+      <c r="A102" s="3">
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.348812066076438</v>
+        <v>1.338039599111029</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="2">
+      <c r="A103" s="3">
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.342454169285812</v>
+        <v>1.332224906325376</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="2">
+      <c r="A104" s="3">
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.330081421661184</v>
+        <v>1.319181451521372</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B105">
+        <v>1.301181451521372</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366484633277613</v>
+        <v>1.366493199785236</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.358849556427267</v>
+        <v>1.358865190696996</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.355833899943489</v>
+        <v>1.355852571312131</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.349809974215763</v>
+        <v>1.349836908926288</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347488222309511</v>
+        <v>1.347516339238843</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343293269226868</v>
+        <v>1.343322434054971</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.33884243043244</v>
+        <v>1.338872222897221</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336379052468101</v>
+        <v>1.336409131107904</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339527870083249</v>
+        <v>1.339546519670694</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.33412214154583</v>
+        <v>1.334119443448693</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335047203352938</v>
+        <v>1.335044032707041</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332882359580955</v>
+        <v>1.332878698547852</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332646136780705</v>
+        <v>1.332634421696813</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329980219091096</v>
+        <v>1.329970697605561</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.32811229218572</v>
+        <v>1.328104630057994</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331381433211962</v>
+        <v>1.331375435449621</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329319555887724</v>
+        <v>1.32932570244742</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.323999163050091</v>
+        <v>1.324014078384576</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319072157572249</v>
+        <v>1.319093352040322</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.31855734921606</v>
+        <v>1.318594819162745</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.315863947189986</v>
+        <v>1.315894178194553</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.319835744702146</v>
+        <v>1.319856697988741</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.319134925654852</v>
+        <v>1.319114687571162</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.314089036506344</v>
+        <v>1.314043347204607</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.312282892373458</v>
+        <v>1.312212564115532</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.305781121697778</v>
+        <v>1.30569601626273</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.296415423531899</v>
+        <v>1.296312473660313</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.293278767439869</v>
+        <v>1.293159133268744</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.297565865903457</v>
+        <v>1.297450275994543</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.315996675048443</v>
+        <v>1.315813425625389</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.328939489349963</v>
+        <v>1.328746392506062</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.358692520283714</v>
+        <v>1.358591390992765</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.375089485175712</v>
+        <v>1.375072719924553</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.3800326956246</v>
+        <v>1.380046609189276</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.388525441565975</v>
+        <v>1.388574146839274</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.389760313427537</v>
+        <v>1.389830731393183</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.387330509798802</v>
+        <v>1.387439066866858</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.386172159464055</v>
+        <v>1.386314149699843</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.388912780242737</v>
+        <v>1.389134802284951</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.384909096610065</v>
+        <v>1.38514607406148</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.388163446546211</v>
+        <v>1.388418576972354</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.37231848281154</v>
+        <v>1.372499380142491</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.367651122054865</v>
+        <v>1.367820078402052</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.355912821842451</v>
+        <v>1.356008065074055</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339296856341011</v>
+        <v>1.339301183099184</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331988705224737</v>
+        <v>1.331923468859767</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.337496802363983</v>
+        <v>1.337453611609728</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.339123348680198</v>
+        <v>1.339096693202653</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339960449352046</v>
+        <v>1.339932866495552</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340841467820751</v>
+        <v>1.340837054372234</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.341981852430609</v>
+        <v>1.340189560015478</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.344332847311346</v>
+        <v>1.341981813027249</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.344168038777756</v>
+        <v>1.341558676023985</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.345827930241866</v>
+        <v>1.342234403498619</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.346033261768651</v>
+        <v>1.341600234500051</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.346761902651822</v>
+        <v>1.34143128490443</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.347799730863393</v>
+        <v>1.341530585160326</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.349232460179564</v>
+        <v>1.341907539679053</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.348956919848281</v>
+        <v>1.340710013010864</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.346254157037531</v>
+        <v>1.335412046970301</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.338039599111029</v>
+        <v>1.32682080518361</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.332224906325376</v>
+        <v>1.321149496011285</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.319181451521372</v>
+        <v>1.307313375144784</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,15 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.301181451521372</v>
+        <v>1.289425875144784</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B106">
+        <v>1.271538375144784</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366493199785236</v>
+        <v>1.366501394015969</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.358865190696996</v>
+        <v>1.358880148591625</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.355852571312131</v>
+        <v>1.355870441847872</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.349836908926288</v>
+        <v>1.349862686954224</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347516339238843</v>
+        <v>1.347543248018516</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343322434054971</v>
+        <v>1.3433503449566</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.338872222897221</v>
+        <v>1.338900734182507</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336409131107904</v>
+        <v>1.336437916515571</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339546519670694</v>
+        <v>1.339564402475641</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334119443448693</v>
+        <v>1.334116878157364</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335044032707041</v>
+        <v>1.335041015782535</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332878698547852</v>
+        <v>1.332875212819784</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332634421696813</v>
+        <v>1.3326232346869</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329970697605561</v>
+        <v>1.329961599005406</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328104630057994</v>
+        <v>1.328097302678252</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331375435449621</v>
+        <v>1.331369698598479</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.32932570244742</v>
+        <v>1.329331560067617</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324014078384576</v>
+        <v>1.324028324453644</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319093352040322</v>
+        <v>1.319113600611167</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.318594819162745</v>
+        <v>1.31863068147166</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.315894178194553</v>
+        <v>1.315923191730185</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.319856697988741</v>
+        <v>1.319876882100548</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.319114687571162</v>
+        <v>1.31909542597274</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.314043347204607</v>
+        <v>1.313999737272023</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.312212564115532</v>
+        <v>1.312145382295552</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.30569601626273</v>
+        <v>1.305614678540855</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.296312473660313</v>
+        <v>1.296214047877434</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.293159133268744</v>
+        <v>1.293044717508399</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.297450275994543</v>
+        <v>1.29733966178853</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.315813425625389</v>
+        <v>1.31563782449676</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.328746392506062</v>
+        <v>1.328561354603307</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.358591390992765</v>
+        <v>1.358494322568615</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.375072719924553</v>
+        <v>1.37505656522512</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380046609189276</v>
+        <v>1.380059726300062</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.388574146839274</v>
+        <v>1.38862046880084</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.389830731393183</v>
+        <v>1.389897702363851</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.387439066866858</v>
+        <v>1.38754253696301</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.386314149699843</v>
+        <v>1.386449620754999</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.389134802284951</v>
+        <v>1.389347347210406</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.38514607406148</v>
+        <v>1.385373107062504</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.388418576972354</v>
+        <v>1.388663120281707</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.372499380142491</v>
+        <v>1.372673089734867</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.367820078402052</v>
+        <v>1.367982512381972</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.356008065074055</v>
+        <v>1.356099942492722</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339301183099184</v>
+        <v>1.339305579435851</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331923468859767</v>
+        <v>1.331860866250547</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.337453611609728</v>
+        <v>1.337412163963167</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.339096693202653</v>
+        <v>1.339071065017583</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339932866495552</v>
+        <v>1.339906273817563</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340837054372234</v>
+        <v>1.340832650513374</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340189560015478</v>
+        <v>1.34020298195551</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.341981813027249</v>
+        <v>1.342009403658718</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341558676023985</v>
+        <v>1.341496198724176</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.342234403498619</v>
+        <v>1.342024306459805</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341600234500051</v>
+        <v>1.341305548001636</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.34143128490443</v>
+        <v>1.340693971560077</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.341530585160326</v>
+        <v>1.340424185396303</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.341907539679053</v>
+        <v>1.340429466764693</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.340710013010864</v>
+        <v>1.338950820567734</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.335412046970301</v>
+        <v>1.333750341039377</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.32682080518361</v>
+        <v>1.325762236689512</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.321149496011285</v>
+        <v>1.319234274573079</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.307313375144784</v>
+        <v>1.306578821230541</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.289425875144784</v>
+        <v>1.281702805511657</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,15 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.271538375144784</v>
+        <v>1.281324255053418</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B107">
+        <v>1.302699255053418</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.342024306459805</v>
+        <v>1.342046933925776</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341305548001636</v>
+        <v>1.341345545787775</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.340693971560077</v>
+        <v>1.340824027269194</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.340424185396303</v>
+        <v>1.340611437631391</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.340429466764693</v>
+        <v>1.340794363397867</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.338950820567734</v>
+        <v>1.339563122985626</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.333750341039377</v>
+        <v>1.334664879395385</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.325762236689512</v>
+        <v>1.326831366736613</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.319234274573079</v>
+        <v>1.320507925304383</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.306578821230541</v>
+        <v>1.307839251217884</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.281702805511657</v>
+        <v>1.283513924868723</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.281324255053418</v>
+        <v>1.28375809303373</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.302699255053418</v>
+        <v>1.30513309303373</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366501394015969</v>
+        <v>1.366509239717341</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.358880148591625</v>
+        <v>1.3588944730603</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.355870441847872</v>
+        <v>1.355887561958295</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.349862686954224</v>
+        <v>1.3498873811847</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347543248018516</v>
+        <v>1.347569024820719</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.3433503449566</v>
+        <v>1.343377081037544</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.338900734182507</v>
+        <v>1.33892804513067</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336437916515571</v>
+        <v>1.336465490278456</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339564402475641</v>
+        <v>1.339581564640473</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334116878157364</v>
+        <v>1.334114436226125</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335041015782535</v>
+        <v>1.335038141776057</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332875212819784</v>
+        <v>1.33287189019971</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.3326232346869</v>
+        <v>1.33261254091966</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329961599005406</v>
+        <v>1.329952895809624</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328097302678252</v>
+        <v>1.328090288600574</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331369698598479</v>
+        <v>1.331364206021349</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329331560067617</v>
+        <v>1.329337148522178</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324028324453644</v>
+        <v>1.324041945134347</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319113600611167</v>
+        <v>1.319132964997892</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.31863068147166</v>
+        <v>1.318665037269174</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.315923191730185</v>
+        <v>1.315951059274849</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.319876882100548</v>
+        <v>1.319896337195107</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.31909542597274</v>
+        <v>1.319077072849984</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313999737272023</v>
+        <v>1.313958068988857</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.312145382295552</v>
+        <v>1.312081141849893</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.305614678540855</v>
+        <v>1.305536865621243</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.296214047877434</v>
+        <v>1.296119856766813</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.293044717508399</v>
+        <v>1.292935188949756</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.29733966178853</v>
+        <v>1.29723371066176</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.31563782449676</v>
+        <v>1.315469405409633</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.328561354603307</v>
+        <v>1.328383884337047</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.358494322568615</v>
+        <v>1.358401077463544</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.37505656522512</v>
+        <v>1.375040990353668</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380059726300062</v>
+        <v>1.380072110099778</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.38862046880084</v>
+        <v>1.388664575598587</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.389897702363851</v>
+        <v>1.389961468425559</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.38754253696301</v>
+        <v>1.387641264302919</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.386449620754999</v>
+        <v>1.386579005337275</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.389347347210406</v>
+        <v>1.389551004562615</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.385373107062504</v>
+        <v>1.385590802655488</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.388663120281707</v>
+        <v>1.388897716458708</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.372673089734867</v>
+        <v>1.372840026354265</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.367982512381972</v>
+        <v>1.36813878759079</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.356099942492722</v>
+        <v>1.356188621342126</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339305579435851</v>
+        <v>1.339310026733459</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331860866250547</v>
+        <v>1.331800743130244</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.337412163963167</v>
+        <v>1.33737235754519</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.339071065017583</v>
+        <v>1.339046407506619</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339906273817563</v>
+        <v>1.339880621206668</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340832650513374</v>
+        <v>1.340828266763826</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.34020298195551</v>
+        <v>1.340215648567657</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342009403658718</v>
+        <v>1.342035697989904</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341496198724176</v>
+        <v>1.341440109289532</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.342046933925776</v>
+        <v>1.341882697008315</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341345545787775</v>
+        <v>1.341124901634071</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.340824027269194</v>
+        <v>1.340307655837107</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.340611437631391</v>
+        <v>1.33984074404466</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.340794363397867</v>
+        <v>1.339874943148578</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.339563122985626</v>
+        <v>1.33863229047743</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.334664879395385</v>
+        <v>1.334085714653688</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.326831366736613</v>
+        <v>1.326836477050813</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.320507925304383</v>
+        <v>1.320027971780612</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.307839251217884</v>
+        <v>1.308210367511564</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.283513924868723</v>
+        <v>1.289591307066664</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.28375809303373</v>
+        <v>1.29269208777058</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.30513309303373</v>
+        <v>1.310971828313747</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366509239717341</v>
+        <v>1.366516758659417</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.3588944730603</v>
+        <v>1.358908203492347</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.355887561958295</v>
+        <v>1.355903977910142</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.3498873811847</v>
+        <v>1.349911058509889</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347569024820719</v>
+        <v>1.347593739550775</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343377081037544</v>
+        <v>1.343402714891455</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.33892804513067</v>
+        <v>1.338954229927528</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336465490278456</v>
+        <v>1.336491927267263</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339581564640473</v>
+        <v>1.339598048694453</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334114436226125</v>
+        <v>1.334112109075414</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335038141776057</v>
+        <v>1.335035400865346</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.33287189019971</v>
+        <v>1.332868719589099</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.33261254091966</v>
+        <v>1.332602308554387</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329952895809624</v>
+        <v>1.329944562861609</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328090288600574</v>
+        <v>1.328083568170945</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331364206021349</v>
+        <v>1.331358942464085</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329337148522178</v>
+        <v>1.329342485830786</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324041945134347</v>
+        <v>1.324054980564324</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319132964997892</v>
+        <v>1.319151501676972</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.318665037269174</v>
+        <v>1.318697979387411</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.315951059274849</v>
+        <v>1.315977846871081</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.319896337195107</v>
+        <v>1.31991510081597</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.319077072849984</v>
+        <v>1.319059566294191</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313958068988857</v>
+        <v>1.31391821645308</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.312081141849893</v>
+        <v>1.312019655042285</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.305536865621243</v>
+        <v>1.305462354889637</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.296119856766813</v>
+        <v>1.296029634897073</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.292935188949756</v>
+        <v>1.292830243602162</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.29723371066176</v>
+        <v>1.297132135494916</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.315469405409633</v>
+        <v>1.31530773903038</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.328383884337047</v>
+        <v>1.328213529310242</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.358401077463544</v>
+        <v>1.358311436115505</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.375040990353668</v>
+        <v>1.375025966411157</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380072110099778</v>
+        <v>1.380083817448291</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.388664575598587</v>
+        <v>1.38870662012266</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.389961468425559</v>
+        <v>1.390022249866047</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.387641264302919</v>
+        <v>1.38773556311299</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.386579005337275</v>
+        <v>1.386702699148298</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.389551004562615</v>
+        <v>1.389746316345674</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.385590802655488</v>
+        <v>1.385799719950639</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.388897716458708</v>
+        <v>1.389122955383363</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.372840026354265</v>
+        <v>1.373000573901014</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.36813878759079</v>
+        <v>1.368289241687886</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.356188621342126</v>
+        <v>1.356274258713502</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339310026733459</v>
+        <v>1.339314508920689</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331800743130244</v>
+        <v>1.331742956874509</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.33737235754519</v>
+        <v>1.337334098135328</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.339046407506619</v>
+        <v>1.339022667992571</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339880621206668</v>
+        <v>1.339855861669491</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340828266763826</v>
+        <v>1.340823911889217</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340215648567657</v>
+        <v>1.340227617619686</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342035697989904</v>
+        <v>1.342060783869841</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341440109289532</v>
+        <v>1.341464042814478</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.341882697008315</v>
+        <v>1.341371262468521</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341124901634071</v>
+        <v>1.340784091015477</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.340307655837107</v>
+        <v>1.340028024581922</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.33984074404466</v>
+        <v>1.339775407618122</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.339874943148578</v>
+        <v>1.339970585283045</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.33863229047743</v>
+        <v>1.338932930115195</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.334085714653688</v>
+        <v>1.334890754469095</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.326836477050813</v>
+        <v>1.328332424946195</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.320027971780612</v>
+        <v>1.322028193420125</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.308210367511564</v>
+        <v>1.311309294798418</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.289591307066664</v>
+        <v>1.297775422714901</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.29269208777058</v>
+        <v>1.301907537937952</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,15 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.310971828313747</v>
+        <v>1.318769385518199</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B108">
+        <v>1.339604733017876</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366516758659417</v>
+        <v>1.366523970836401</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.358908203492347</v>
+        <v>1.358921376078488</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.355903977910142</v>
+        <v>1.355919732245688</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.349911058509889</v>
+        <v>1.349933780432102</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347593739550775</v>
+        <v>1.347617456478178</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343402714891455</v>
+        <v>1.343427313255976</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.338954229927528</v>
+        <v>1.338979356773182</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336491927267263</v>
+        <v>1.33651729631281</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339598048694453</v>
+        <v>1.339613893898895</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334112109075414</v>
+        <v>1.334109888895558</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335035400865346</v>
+        <v>1.335032784101062</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332868719589099</v>
+        <v>1.33286569086765</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332602308554387</v>
+        <v>1.332592508427396</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329944562861609</v>
+        <v>1.329936577089087</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328083568170945</v>
+        <v>1.328077123344099</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331358942464085</v>
+        <v>1.331353893914984</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329342485830786</v>
+        <v>1.329347588448331</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324054980564324</v>
+        <v>1.324067467530515</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319151501676972</v>
+        <v>1.319169262430479</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.318697979387411</v>
+        <v>1.318729593196203</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.315977846871081</v>
+        <v>1.316003615627478</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.31991510081597</v>
+        <v>1.319933208086215</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.319059566294191</v>
+        <v>1.319042849834813</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.31391821645308</v>
+        <v>1.313880064347042</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.312019655042285</v>
+        <v>1.311960749682312</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.305462354889637</v>
+        <v>1.305390941965847</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.296029634897073</v>
+        <v>1.295943138405529</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.292830243602162</v>
+        <v>1.292729601975847</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.297132135494916</v>
+        <v>1.29703467213846</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.31530773903038</v>
+        <v>1.315152429383527</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.328213529310242</v>
+        <v>1.328049872279767</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.358311436115505</v>
+        <v>1.35822519529698</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.375025966411157</v>
+        <v>1.375011466216132</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380083817448291</v>
+        <v>1.380094899666345</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.38870662012266</v>
+        <v>1.388746741679323</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390022249866047</v>
+        <v>1.390080247542905</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.38773556311299</v>
+        <v>1.387825720791605</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.386702699148298</v>
+        <v>1.386821064714325</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.389746316345674</v>
+        <v>1.389933781685403</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.385799719950639</v>
+        <v>1.386000374716231</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.389122955383363</v>
+        <v>1.389339381594209</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.373000573901014</v>
+        <v>1.373155088182579</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.368289241687886</v>
+        <v>1.368434188604366</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.356274258713502</v>
+        <v>1.356357002216019</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339314508920689</v>
+        <v>1.339319012129674</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331742956874509</v>
+        <v>1.331687375441706</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.337334098135328</v>
+        <v>1.337297298478632</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.339022667992571</v>
+        <v>1.338999797418311</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339855861669491</v>
+        <v>1.339831951116085</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340823911889217</v>
+        <v>1.340819593163859</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340227617619686</v>
+        <v>1.340238941383304</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342060783869841</v>
+        <v>1.342084741485836</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341464042814478</v>
+        <v>1.341486945198809</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.341371262468521</v>
+        <v>1.341262374877647</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.340784091015477</v>
+        <v>1.340893388543568</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.340028024581922</v>
+        <v>1.340216161083879</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.339775407618122</v>
+        <v>1.340217816534888</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.339970585283045</v>
+        <v>1.340628791344725</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.338932930115195</v>
+        <v>1.339839071409825</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.334890754469095</v>
+        <v>1.33634611017472</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.328332424946195</v>
+        <v>1.330436056300185</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.322028193420125</v>
+        <v>1.324639864011997</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.311309294798418</v>
+        <v>1.314892165579828</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.297775422714901</v>
+        <v>1.30592937478338</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.301907537937952</v>
+        <v>1.311454000744718</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.318769385518199</v>
+        <v>1.327047883477007</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.339604733017876</v>
+        <v>1.348422883477006</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366523970836401</v>
+        <v>1.366530894644072</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.358921376078488</v>
+        <v>1.358934024128976</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.355919732245688</v>
+        <v>1.355934864149899</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.349933780432102</v>
+        <v>1.349955603595552</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347617456478178</v>
+        <v>1.347640234792936</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343427313255976</v>
+        <v>1.343450937591159</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.338979356773182</v>
+        <v>1.339003488473367</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.33651729631281</v>
+        <v>1.336541660802635</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339613893898895</v>
+        <v>1.339629136553721</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334109888895558</v>
+        <v>1.334107768562981</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335032784101062</v>
+        <v>1.335030283312537</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.33286569086765</v>
+        <v>1.332862794788405</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332592508427396</v>
+        <v>1.332583113777026</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329936577089087</v>
+        <v>1.329928917293138</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328077123344099</v>
+        <v>1.328070937522358</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331353893914984</v>
+        <v>1.331349047480987</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329347588448331</v>
+        <v>1.329352471430371</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324067467530515</v>
+        <v>1.324079439810527</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319169262430479</v>
+        <v>1.319186294822487</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.318729593196203</v>
+        <v>1.318759957337045</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316003615627478</v>
+        <v>1.316028422166375</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.319933208086215</v>
+        <v>1.319950691887314</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.319042849834813</v>
+        <v>1.319026871860594</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313880064347042</v>
+        <v>1.313843506854584</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311960749682312</v>
+        <v>1.311904267558058</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.305390941965847</v>
+        <v>1.305322438886087</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.295943138405529</v>
+        <v>1.295860142866126</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.292729601975847</v>
+        <v>1.292633006681084</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.29703467213846</v>
+        <v>1.296941077172795</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.315152429383527</v>
+        <v>1.315003110692433</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.328049872279767</v>
+        <v>1.327892527826374</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.35822519529698</v>
+        <v>1.358142166640069</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.375011466216132</v>
+        <v>1.374997464200595</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380094899666345</v>
+        <v>1.380105403178097</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.388746741679323</v>
+        <v>1.388785067451243</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390080247542905</v>
+        <v>1.390135644952872</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.387825720791605</v>
+        <v>1.387912000682594</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.386821064714325</v>
+        <v>1.386934434755493</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.389933781685403</v>
+        <v>1.390113860956805</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.386000374716231</v>
+        <v>1.386193243457075</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.389339381594209</v>
+        <v>1.389547498523618</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.373155088182579</v>
+        <v>1.373303899398131</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.368434188604366</v>
+        <v>1.368573920537867</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.356357002216019</v>
+        <v>1.356436990607902</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339319012129674</v>
+        <v>1.339323524402164</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331687375441706</v>
+        <v>1.331633876424575</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.337297298478632</v>
+        <v>1.337261877664864</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338999797418311</v>
+        <v>1.338977750054409</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339831951116085</v>
+        <v>1.339808848159264</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340819593163859</v>
+        <v>1.340815316592643</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340238941383304</v>
+        <v>1.340249667253371</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342084741485836</v>
+        <v>1.342107644171935</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341486945198809</v>
+        <v>1.341508880574429</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.341262374877647</v>
+        <v>1.342183963184632</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.340893388543568</v>
+        <v>1.342170287234499</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.340216161083879</v>
+        <v>1.341599406898806</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.340217816534888</v>
+        <v>1.34205589407889</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.340628791344725</v>
+        <v>1.342852265635727</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.339839071409825</v>
+        <v>1.342518753106311</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.33634611017472</v>
+        <v>1.339863662440123</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.330436056300185</v>
+        <v>1.334756737290559</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.324639864011997</v>
+        <v>1.329592222393406</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.314892165579828</v>
+        <v>1.321176426697603</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.30592937478338</v>
+        <v>1.316531570952349</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.311454000744718</v>
+        <v>1.323512078815546</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.327047883477007</v>
+        <v>1.33897039865233</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.348422883477006</v>
+        <v>1.364211242007055</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366530894644072</v>
+        <v>1.366543943663915</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.358934024128976</v>
+        <v>1.358957867114818</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.355934864149899</v>
+        <v>1.355963402528234</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.349955603595552</v>
+        <v>1.34999675869941</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347640234792936</v>
+        <v>1.347683189841657</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343450937591159</v>
+        <v>1.343495486634914</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339003488473367</v>
+        <v>1.339048993764835</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336541660802635</v>
+        <v>1.336587605552598</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339629136553721</v>
+        <v>1.339657946214858</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334107768562981</v>
+        <v>1.334103801946018</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335030283312537</v>
+        <v>1.335025600389492</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332862794788405</v>
+        <v>1.332857367396289</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332583113777026</v>
+        <v>1.332565444447115</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329928917293138</v>
+        <v>1.329914499108172</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328070937522358</v>
+        <v>1.328059282904726</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331349047480987</v>
+        <v>1.331339914336009</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329352471430371</v>
+        <v>1.329361632565886</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324079439810527</v>
+        <v>1.324101962144093</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319186294822487</v>
+        <v>1.319218346157553</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.318759957337045</v>
+        <v>1.318817221360221</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316028422166375</v>
+        <v>1.316075355010206</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.319950691887314</v>
+        <v>1.319983910377592</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.319026871860594</v>
+        <v>1.318996946238606</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313843506854584</v>
+        <v>1.31377479434533</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311904267558058</v>
+        <v>1.311798001926716</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.305322438886087</v>
+        <v>1.305193483034587</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.295860142866126</v>
+        <v>1.295703843022124</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.292633006681084</v>
+        <v>1.292451023510088</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.296941077172795</v>
+        <v>1.296764610702933</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.315003110692433</v>
+        <v>1.314721117516615</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.327892527826374</v>
+        <v>1.32759537665127</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.358142166640069</v>
+        <v>1.357985058854702</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374997464200595</v>
+        <v>1.374970859906891</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380105403178097</v>
+        <v>1.380124838563886</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.388785067451243</v>
+        <v>1.388856787262171</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390135644952872</v>
+        <v>1.390239296813601</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.387912000682594</v>
+        <v>1.388073874553476</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.386934434755493</v>
+        <v>1.387147387592445</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.390113860956805</v>
+        <v>1.390453530614745</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.386193243457075</v>
+        <v>1.386557353962384</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.389547498523618</v>
+        <v>1.389940634975384</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.373303899398131</v>
+        <v>1.373585618542451</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.368573920537867</v>
+        <v>1.368838810229577</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.356436990607902</v>
+        <v>1.356589216351776</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339323524402164</v>
+        <v>1.339332536373477</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331633876424575</v>
+        <v>1.331532679166929</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.337261877664864</v>
+        <v>1.337194877363693</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338977750054409</v>
+        <v>1.338935957104785</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339808848159264</v>
+        <v>1.339764911890909</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340815316592643</v>
+        <v>1.340806908683719</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340249667253371</v>
+        <v>1.340269493674729</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342107644171935</v>
+        <v>1.342150547993833</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341508880574429</v>
+        <v>1.341550081659279</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.342183963184632</v>
+        <v>1.342928207427465</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.342170287234499</v>
+        <v>1.343346353586948</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341599406898806</v>
+        <v>1.342893554634485</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.34205589407889</v>
+        <v>1.344059845280247</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.342852265635727</v>
+        <v>1.345262202347028</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.342518753106311</v>
+        <v>1.3453566838888</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.339863662440123</v>
+        <v>1.343463163533409</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.334756737290559</v>
+        <v>1.339120234753213</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.329592222393406</v>
+        <v>1.334665110334838</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.321176426697603</v>
+        <v>1.327861759714668</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.316531570952349</v>
+        <v>1.326455229750745</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.323512078815546</v>
+        <v>1.333101870250726</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.33897039865233</v>
+        <v>1.346685515554194</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.364211242007055</v>
+        <v>1.366606366740299</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366543943663915</v>
+        <v>1.366550098996884</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.358957867114818</v>
+        <v>1.358969116639518</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.355963402528234</v>
+        <v>1.355976873327228</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.34999675869941</v>
+        <v>1.350016183607779</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347683189841657</v>
+        <v>1.347703463711292</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343495486634914</v>
+        <v>1.343516512193045</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339048993764835</v>
+        <v>1.339070470409586</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336587605552598</v>
+        <v>1.336609289824516</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339657946214858</v>
+        <v>1.339671573325918</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334103801946018</v>
+        <v>1.334101944230825</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335025600389492</v>
+        <v>1.335023405115244</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332857367396289</v>
+        <v>1.332854821185406</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332565444447115</v>
+        <v>1.332557126216843</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329914499108172</v>
+        <v>1.329907706120229</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328059282904726</v>
+        <v>1.328053786951702</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331339914336009</v>
+        <v>1.331335606509489</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329361632565886</v>
+        <v>1.32936593505322</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324101962144093</v>
+        <v>1.324112567240119</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319218346157553</v>
+        <v>1.319233442677622</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.318817221360221</v>
+        <v>1.318844250367327</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316075355010206</v>
+        <v>1.316097575528383</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.319983910377592</v>
+        <v>1.319999701044008</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318996946238606</v>
+        <v>1.318982915401538</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.31377479434533</v>
+        <v>1.313742467168576</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311798001926716</v>
+        <v>1.311747960225098</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.305193483034587</v>
+        <v>1.305132722860127</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.295703843022124</v>
+        <v>1.295630171118976</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.292451023510088</v>
+        <v>1.292365213384603</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.296764610702933</v>
+        <v>1.296681339236136</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.314721117516615</v>
+        <v>1.314587838683209</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.32759537665127</v>
+        <v>1.327454933136748</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.357985058854702</v>
+        <v>1.357910666076349</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374970859906891</v>
+        <v>1.374958213681824</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380124838563886</v>
+        <v>1.380133843460114</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.388856787262171</v>
+        <v>1.388890385784456</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390239296813601</v>
+        <v>1.390287846701174</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.388073874553476</v>
+        <v>1.388149895501678</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.387147387592445</v>
+        <v>1.387247511854455</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.390453530614745</v>
+        <v>1.390613878992107</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.386557353962384</v>
+        <v>1.386729383190125</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.389940634975384</v>
+        <v>1.390126487823111</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.373585618542451</v>
+        <v>1.373719077799597</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.368838810229577</v>
+        <v>1.368964459110245</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.356589216351776</v>
+        <v>1.356661692103601</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339332536373477</v>
+        <v>1.339337019602813</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331532679166929</v>
+        <v>1.331484777058069</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.337194877363693</v>
+        <v>1.337163163043294</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338935957104785</v>
+        <v>1.338916134419008</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339764911890909</v>
+        <v>1.339744007699389</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340806908683719</v>
+        <v>1.340802784561508</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340269493674729</v>
+        <v>1.340278669151762</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342150547993833</v>
+        <v>1.342170667498203</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341550081659279</v>
+        <v>1.341569451898526</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.342928207427465</v>
+        <v>1.343006461477468</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.343346353586948</v>
+        <v>1.343599959603143</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.342893554634485</v>
+        <v>1.343222740629378</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.344059845280247</v>
+        <v>1.344699128925105</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.345262202347028</v>
+        <v>1.346044121092028</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.3453566838888</v>
+        <v>1.346207667299626</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.343463163533409</v>
+        <v>1.344435340353821</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.339120234753213</v>
+        <v>1.340161077573441</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.334665110334838</v>
+        <v>1.336117080915115</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.327861759714668</v>
+        <v>1.329637352143369</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.326455229750745</v>
+        <v>1.328438364481307</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.333101870250726</v>
+        <v>1.334821374076097</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.346685515554194</v>
+        <v>1.346725890468144</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.366606366740299</v>
+        <v>1.363186429735685</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366550098996884</v>
+        <v>1.366556026434225</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.358969116639518</v>
+        <v>1.358979951224203</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.355976873327228</v>
+        <v>1.355989850827715</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350016183607779</v>
+        <v>1.350034896392756</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347703463711292</v>
+        <v>1.347722993971236</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343516512193045</v>
+        <v>1.343536766181396</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339070470409586</v>
+        <v>1.33909115879319</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336609289824516</v>
+        <v>1.336630178348609</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339671573325918</v>
+        <v>1.33968471850918</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334101944230825</v>
+        <v>1.334100163395566</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335023405115244</v>
+        <v>1.335021299417993</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332854821185406</v>
+        <v>1.332852377687542</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332557126216843</v>
+        <v>1.33254912600614</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329907706120229</v>
+        <v>1.329901169636381</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328053786951702</v>
+        <v>1.328048495478905</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331335606509489</v>
+        <v>1.33133145840481</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.32936593505322</v>
+        <v>1.329370066784146</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324112567240119</v>
+        <v>1.324122768178124</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319233442677622</v>
+        <v>1.319247966609749</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.318844250367327</v>
+        <v>1.318870288922958</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316097575528383</v>
+        <v>1.316119022866978</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.319999701044008</v>
+        <v>1.320014980465144</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318982915401538</v>
+        <v>1.318969455932717</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313742467168576</v>
+        <v>1.313711388880885</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311747960225098</v>
+        <v>1.311699823324106</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.305132722860127</v>
+        <v>1.305074255339265</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.295630171118976</v>
+        <v>1.295559262162659</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.292365213384603</v>
+        <v>1.292282601917382</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.296681339236136</v>
+        <v>1.296601133269408</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.314587838683209</v>
+        <v>1.314459337873607</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.327454933136748</v>
+        <v>1.327319524150764</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.357910666076349</v>
+        <v>1.35783885614111</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374958213681824</v>
+        <v>1.374945977566218</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380133843460114</v>
+        <v>1.380142416484555</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.388890385784456</v>
+        <v>1.388922599343597</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390287846701174</v>
+        <v>1.390334389837208</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.388149895501678</v>
+        <v>1.388222896185354</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.387247511854455</v>
+        <v>1.387343727915319</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.390613878992107</v>
+        <v>1.390768362780971</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.386729383190125</v>
+        <v>1.386895206808912</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.390126487823111</v>
+        <v>1.390305703755596</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.373719077799597</v>
+        <v>1.373847940081045</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.368964459110245</v>
+        <v>1.3690858780738</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.356661692103601</v>
+        <v>1.356731890542779</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339337019602813</v>
+        <v>1.339341478607513</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331484777058069</v>
+        <v>1.331438548323957</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.337163163043294</v>
+        <v>1.337132557043732</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338916134419008</v>
+        <v>1.338896980320978</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339744007699389</v>
+        <v>1.339723769032709</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340802784561508</v>
+        <v>1.340798717275282</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340278669151762</v>
+        <v>1.340287397360412</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342170667498203</v>
+        <v>1.342189969845741</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341569451898526</v>
+        <v>1.341588065021932</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343006461477468</v>
+        <v>1.343020404637061</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.343599959603143</v>
+        <v>1.343571157367936</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.343222740629378</v>
+        <v>1.343504323336956</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.344699128925105</v>
+        <v>1.345086203301383</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346044121092028</v>
+        <v>1.347068658684571</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.346207667299626</v>
+        <v>1.347707626726278</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.344435340353821</v>
+        <v>1.346415328505308</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.340161077573441</v>
+        <v>1.342314309198606</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.336117080915115</v>
+        <v>1.338266313351063</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.329637352143369</v>
+        <v>1.332515568657278</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.328438364481307</v>
+        <v>1.332476250460635</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.334821374076097</v>
+        <v>1.338720202360317</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.346725890468144</v>
+        <v>1.349879140793863</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,15 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.363186429735685</v>
+        <v>1.364808176194911</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B109">
+        <v>1.374313450750735</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366556026434225</v>
+        <v>1.366561738400972</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.358979951224203</v>
+        <v>1.358990393405509</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.355989850827715</v>
+        <v>1.356002361626485</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350034896392756</v>
+        <v>1.350052935487494</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347722993971236</v>
+        <v>1.347741820773547</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343536766181396</v>
+        <v>1.343556290282845</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.33909115879319</v>
+        <v>1.339111101507841</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336630178348609</v>
+        <v>1.336650314114552</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.33968471850918</v>
+        <v>1.339697406812274</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334100163395566</v>
+        <v>1.334098454813831</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335021299417993</v>
+        <v>1.33501927796851</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332852377687542</v>
+        <v>1.332850030849697</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.33254912600614</v>
+        <v>1.332541425953108</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329901169636381</v>
+        <v>1.329894875428205</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328048495478905</v>
+        <v>1.328043397291621</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.33133145840481</v>
+        <v>1.331327461310307</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329370066784146</v>
+        <v>1.329374037674889</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324122768178124</v>
+        <v>1.324132587560042</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319247966609749</v>
+        <v>1.319261949835767</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.318870288922958</v>
+        <v>1.318895390426343</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316119022866978</v>
+        <v>1.316139736459187</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320014980465144</v>
+        <v>1.320029772546691</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318969455932717</v>
+        <v>1.318956534025811</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313711388880885</v>
+        <v>1.313681488901049</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311699823324106</v>
+        <v>1.311653485069642</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.305074255339265</v>
+        <v>1.305017953840093</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.295559262162659</v>
+        <v>1.295490964512106</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.292282601917382</v>
+        <v>1.292203014675814</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.296601133269408</v>
+        <v>1.296523827317863</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.314459337873607</v>
+        <v>1.314335363751005</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.327319524150764</v>
+        <v>1.327188884866687</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.35783885614111</v>
+        <v>1.357769497684807</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374945977566218</v>
+        <v>1.374934132652661</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380142416484555</v>
+        <v>1.380150586622199</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.388922599343597</v>
+        <v>1.388953510839416</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390334389837208</v>
+        <v>1.390379046134434</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.388222896185354</v>
+        <v>1.38829305104938</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.387343727915319</v>
+        <v>1.387436257766925</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.390768362780971</v>
+        <v>1.390917296173211</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.386895206808912</v>
+        <v>1.387055152322191</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.390305703755596</v>
+        <v>1.390478629891612</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.373847940081045</v>
+        <v>1.373972436858667</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.3690858780738</v>
+        <v>1.369203274537941</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.356731890542779</v>
+        <v>1.356799914309359</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339341478607513</v>
+        <v>1.33934590782072</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331438548323957</v>
+        <v>1.331393907574458</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.337132557043732</v>
+        <v>1.33710300286339</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338896980320978</v>
+        <v>1.338878462168712</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339723769032709</v>
+        <v>1.339704165461323</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340798717275282</v>
+        <v>1.340794708795141</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340287397360412</v>
+        <v>1.34029570816778</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342189969845741</v>
+        <v>1.342208503197068</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341588065021932</v>
+        <v>1.341605963939335</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343020404637061</v>
+        <v>1.34303394529648</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.343571157367936</v>
+        <v>1.34319671824122</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.343504323336956</v>
+        <v>1.343326317996715</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.345086203301383</v>
+        <v>1.344969651780644</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347068658684571</v>
+        <v>1.34738917779873</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.347707626726278</v>
+        <v>1.34835099622774</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.346415328505308</v>
+        <v>1.347331927519582</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.342314309198606</v>
+        <v>1.343262036530814</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.338266313351063</v>
+        <v>1.339121286735455</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.332515568657278</v>
+        <v>1.333814105397715</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.332476250460635</v>
+        <v>1.334167451787544</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.338720202360317</v>
+        <v>1.339926693421159</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.349879140793863</v>
+        <v>1.349949843796816</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.364808176194911</v>
+        <v>1.362797824827286</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.374313450750735</v>
+        <v>1.361774247960683</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.343326317996715</v>
+        <v>1.343324840552797</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.344969651780644</v>
+        <v>1.344960824280699</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.34738917779873</v>
+        <v>1.347294047257672</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.34835099622774</v>
+        <v>1.348242255068016</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.347331927519582</v>
+        <v>1.347044546548552</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.343262036530814</v>
+        <v>1.343051599539781</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.339121286735455</v>
+        <v>1.338975003156577</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.333814105397715</v>
+        <v>1.333396117896144</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.334167451787544</v>
+        <v>1.333743561691983</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.339926693421159</v>
+        <v>1.339575574511897</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.349949843796816</v>
+        <v>1.349687085271563</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.362797824827286</v>
+        <v>1.362558874160052</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.361774247960683</v>
+        <v>1.361101862103683</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.343324840552797</v>
+        <v>1.343326449380873</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.344960824280699</v>
+        <v>1.344974999844071</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347294047257672</v>
+        <v>1.34735736373858</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.348242255068016</v>
+        <v>1.348345358273253</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.347044546548552</v>
+        <v>1.347193850177893</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.343051599539781</v>
+        <v>1.343276178449082</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.338975003156577</v>
+        <v>1.339423143581202</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.333396117896144</v>
+        <v>1.333688753900248</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.333743561691983</v>
+        <v>1.334046963955579</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.339575574511897</v>
+        <v>1.339855409273206</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.349687085271563</v>
+        <v>1.349865108891761</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.362558874160052</v>
+        <v>1.362707899202843</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.361101862103683</v>
+        <v>1.361471069517944</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366561738400972</v>
+        <v>1.366567246435147</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.358990393405509</v>
+        <v>1.359000464117418</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356002361626485</v>
+        <v>1.356014430442969</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350052935487494</v>
+        <v>1.350070336609898</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347741820773547</v>
+        <v>1.347759981432214</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343556290282845</v>
+        <v>1.343575123232503</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339111101507841</v>
+        <v>1.339130338133113</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336650314114552</v>
+        <v>1.336669737071771</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339697406812274</v>
+        <v>1.339709661581898</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334098454813831</v>
+        <v>1.334096814220046</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.33501927796851</v>
+        <v>1.335017335849318</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332850030849697</v>
+        <v>1.332847775082815</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332541425953108</v>
+        <v>1.332534009506649</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329894875428205</v>
+        <v>1.329888810298438</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328043397291621</v>
+        <v>1.328038481997085</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331327461310307</v>
+        <v>1.331323607135881</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329374037674889</v>
+        <v>1.329377856891793</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324132587560042</v>
+        <v>1.324142046338021</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319261949835767</v>
+        <v>1.319275421919608</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.318895390426343</v>
+        <v>1.31891960451019</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316139736459187</v>
+        <v>1.316159753118338</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320029772546691</v>
+        <v>1.320044099767844</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318956534025811</v>
+        <v>1.318944118465053</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313681488901049</v>
+        <v>1.313652701840489</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311653485069642</v>
+        <v>1.311608847013547</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.305017953840093</v>
+        <v>1.304963700839125</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.295490964512106</v>
+        <v>1.295425137361341</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.292203014675814</v>
+        <v>1.292126289606776</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.296523827317863</v>
+        <v>1.296449267547552</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.314335363751005</v>
+        <v>1.314215682228274</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.327188884866687</v>
+        <v>1.327062768634239</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.357769497684807</v>
+        <v>1.357702468041964</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374934132652661</v>
+        <v>1.374922661119259</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380150586622199</v>
+        <v>1.380158380398607</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.388953510839416</v>
+        <v>1.388983196750663</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390379046134434</v>
+        <v>1.39042192626128</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.38829305104938</v>
+        <v>1.388360521489053</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.387436257766925</v>
+        <v>1.387525307058867</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.390917296173211</v>
+        <v>1.391060971432484</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.387055152322191</v>
+        <v>1.387209524748423</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.390478629891612</v>
+        <v>1.390645589709601</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.373972436858667</v>
+        <v>1.374092784465464</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.369203274537941</v>
+        <v>1.369316842770265</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.356799914309359</v>
+        <v>1.356865860201133</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.33934590782072</v>
+        <v>1.339350302504929</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331393907574458</v>
+        <v>1.331350775075372</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.33710300286339</v>
+        <v>1.337074447734588</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338878462168712</v>
+        <v>1.338860549364973</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339704165461323</v>
+        <v>1.339685168317494</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340794708795141</v>
+        <v>1.340790760602375</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.34029570816778</v>
+        <v>1.340303628946299</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342208503197068</v>
+        <v>1.342226312041189</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341605963939335</v>
+        <v>1.341623188418564</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.34303394529648</v>
+        <v>1.343047099209802</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.34319671824122</v>
+        <v>1.342867322049416</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.343326449380873</v>
+        <v>1.343162443449833</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.344974999844071</v>
+        <v>1.344869989614201</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.34735736373858</v>
+        <v>1.347678626068896</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.348345358273253</v>
+        <v>1.348994412337778</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.347193850177893</v>
+        <v>1.348151377639882</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.343276178449082</v>
+        <v>1.344354188695789</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.339423143581202</v>
+        <v>1.340682801018594</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.333688753900248</v>
+        <v>1.335335026547066</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.334046963955579</v>
+        <v>1.33624515651015</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.339855409273206</v>
+        <v>1.341853460297304</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.349865108891761</v>
+        <v>1.35112710596421</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.362707899202843</v>
+        <v>1.36280005152109</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.361471069517944</v>
+        <v>1.362407998709904</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366567246435147</v>
+        <v>1.366572561265519</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359000464117418</v>
+        <v>1.359010182831199</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356014430442969</v>
+        <v>1.35602608028194</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350070336609898</v>
+        <v>1.350087132998122</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347759981432214</v>
+        <v>1.347777510669422</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343575123232503</v>
+        <v>1.343593301073628</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339130338133113</v>
+        <v>1.339148905497556</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336669737071771</v>
+        <v>1.336688484393396</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339709661581898</v>
+        <v>1.339721504605329</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334096814220046</v>
+        <v>1.334095237675215</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335017335849318</v>
+        <v>1.335015468515891</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332847775082815</v>
+        <v>1.332845605218372</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332534009506649</v>
+        <v>1.332526861308584</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329888810298438</v>
+        <v>1.329882961989402</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328038481997085</v>
+        <v>1.328033739933977</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331323607135881</v>
+        <v>1.331319888358587</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329377856891793</v>
+        <v>1.32938153292062</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324142046338021</v>
+        <v>1.324151163961862</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319275421919608</v>
+        <v>1.319288410313708</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.31891960451019</v>
+        <v>1.318942977366649</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316159753118338</v>
+        <v>1.316179107250412</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320044099767844</v>
+        <v>1.320057983282139</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318944118465053</v>
+        <v>1.318932180383692</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313652701840489</v>
+        <v>1.313624967036604</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311608847013547</v>
+        <v>1.311565817729968</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304963700839125</v>
+        <v>1.30491138712087</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.295425137361341</v>
+        <v>1.295361649793913</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.292126289606776</v>
+        <v>1.292052275963998</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.296449267547552</v>
+        <v>1.296377310772002</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.314215682228274</v>
+        <v>1.314100075019433</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.327062768634239</v>
+        <v>1.326940945452997</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.357702468041964</v>
+        <v>1.357637652542929</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374922661119259</v>
+        <v>1.374911546159001</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380158380398607</v>
+        <v>1.380165822129631</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.388983196750663</v>
+        <v>1.389011727739571</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.39042192626128</v>
+        <v>1.390463132506333</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.388360521489053</v>
+        <v>1.388425457037482</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.387525307058867</v>
+        <v>1.387611066562443</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.391060971432484</v>
+        <v>1.391199660764141</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.387209524748423</v>
+        <v>1.38735860850423</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.390645589709601</v>
+        <v>1.390806885013407</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.374092784465464</v>
+        <v>1.374209185300423</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.369316842770265</v>
+        <v>1.369426764896651</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.356865860201133</v>
+        <v>1.356929819560622</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339350302504929</v>
+        <v>1.339354658646595</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331350775075372</v>
+        <v>1.331309076292819</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.337074447734588</v>
+        <v>1.337046842323875</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338860549364973</v>
+        <v>1.338843213203909</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339685168317494</v>
+        <v>1.339666750575915</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340790760602375</v>
+        <v>1.340786873761453</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340303628946299</v>
+        <v>1.340311184821561</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342226312041189</v>
+        <v>1.342243437535676</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341623188418564</v>
+        <v>1.341639775364608</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343047099209802</v>
+        <v>1.343059881440031</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.342867322049416</v>
+        <v>1.342204290996772</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.343162443449833</v>
+        <v>1.342555840682617</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.344869989614201</v>
+        <v>1.344294913840616</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347678626068896</v>
+        <v>1.347454352303655</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.348994412337778</v>
+        <v>1.34900923396435</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.348151377639882</v>
+        <v>1.348494930517086</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.344354188695789</v>
+        <v>1.344689415519239</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.340682801018594</v>
+        <v>1.34081982005475</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.335335026547066</v>
+        <v>1.336025237315677</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.33624515651015</v>
+        <v>1.337030078720483</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.341853460297304</v>
+        <v>1.342147017161817</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.35112710596421</v>
+        <v>1.350538891332457</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.36280005152109</v>
+        <v>1.360767190450886</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.362407998709904</v>
+        <v>1.357678017720899</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.342555840682617</v>
+        <v>1.342555953448667</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.344294913840616</v>
+        <v>1.344299545856672</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347454352303655</v>
+        <v>1.347426735288838</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.34900923396435</v>
+        <v>1.349004258692761</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.348494930517086</v>
+        <v>1.348376850172432</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.344689415519239</v>
+        <v>1.344701179211604</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.34081982005475</v>
+        <v>1.341075618433468</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.336025237315677</v>
+        <v>1.335919202373473</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.337030078720483</v>
+        <v>1.33693082714872</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.342147017161817</v>
+        <v>1.34208890231085</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.350538891332457</v>
+        <v>1.350470963099086</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.360767190450886</v>
+        <v>1.360697916558325</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.357678017720899</v>
+        <v>1.35753142294404</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366572561265519</v>
+        <v>1.36657769288132</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359010182831199</v>
+        <v>1.359019567680942</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.35602608028194</v>
+        <v>1.35603733257958</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350087132998122</v>
+        <v>1.350103355621986</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347777510669422</v>
+        <v>1.347794440836631</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343593301073628</v>
+        <v>1.343610857387349</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339148905497556</v>
+        <v>1.339166837913508</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336688484393396</v>
+        <v>1.336706590713197</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339721504605329</v>
+        <v>1.339732956238076</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334095237675215</v>
+        <v>1.334093721536449</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335015468515891</v>
+        <v>1.335013671762146</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332845605218372</v>
+        <v>1.332843516469721</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332526861308584</v>
+        <v>1.332519967088236</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329882961989402</v>
+        <v>1.329877319100995</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328033739933977</v>
+        <v>1.328029162109233</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331319888358587</v>
+        <v>1.331316297973842</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.32938153292062</v>
+        <v>1.329385073628326</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324151163961862</v>
+        <v>1.324159958510969</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319288410313708</v>
+        <v>1.319300940543782</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.318942977366649</v>
+        <v>1.318965552040044</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316179107250412</v>
+        <v>1.316197831046343</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320057983282139</v>
+        <v>1.320071443010312</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318932180383692</v>
+        <v>1.3189206930488</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313624967036604</v>
+        <v>1.313598228135329</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311565817729968</v>
+        <v>1.31152431220293</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.30491138712087</v>
+        <v>1.304860911059952</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.295361649793913</v>
+        <v>1.295300379934139</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.292052275963998</v>
+        <v>1.291980833344424</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.296377310772002</v>
+        <v>1.296307823550296</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.314100075019433</v>
+        <v>1.313988338334051</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.326940945452997</v>
+        <v>1.326823200596531</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.357637652542929</v>
+        <v>1.357574943877495</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374911546159001</v>
+        <v>1.374900771913765</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380165822129631</v>
+        <v>1.380172934141843</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389011727739571</v>
+        <v>1.389039169189875</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390463132506333</v>
+        <v>1.390502759548482</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.388425457037482</v>
+        <v>1.388487996426646</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.387611066562443</v>
+        <v>1.387693713481254</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.391199660764141</v>
+        <v>1.391333617998028</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.38735860850423</v>
+        <v>1.387502669102824</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.390806885013407</v>
+        <v>1.390962797706415</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.374209185300423</v>
+        <v>1.374321828921467</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.369426764896651</v>
+        <v>1.369533211820137</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.356929819560622</v>
+        <v>1.356991878634429</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339354658646595</v>
+        <v>1.339358972864476</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331309076292819</v>
+        <v>1.331268741480438</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.337046842323875</v>
+        <v>1.33702014046034</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338843213203909</v>
+        <v>1.3388264267308</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339666750575915</v>
+        <v>1.339648886743165</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340786873761453</v>
+        <v>1.340783048981714</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340311184821561</v>
+        <v>1.340318398891815</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342243437535676</v>
+        <v>1.34225991781002</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341639775364608</v>
+        <v>1.341655759069841</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343059881440031</v>
+        <v>1.343072306382974</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.342204290996772</v>
+        <v>1.341602536193974</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.342555953448667</v>
+        <v>1.341931587364726</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.344299545856672</v>
+        <v>1.343606444179047</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347426735288838</v>
+        <v>1.346794915757435</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.349004258692761</v>
+        <v>1.348448465797891</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.348376850172432</v>
+        <v>1.347669846683952</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.344701179211604</v>
+        <v>1.343997728850262</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.341075618433468</v>
+        <v>1.340350492831898</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.335919202373473</v>
+        <v>1.335202331017429</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.33693082714872</v>
+        <v>1.335916440464352</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.34208890231085</v>
+        <v>1.340536702592985</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.350470963099086</v>
+        <v>1.34798589411826</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.360697916558325</v>
+        <v>1.356727974903587</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.35753142294404</v>
+        <v>1.350167630584741</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.36657769288132</v>
+        <v>1.366587443098011</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359019567680942</v>
+        <v>1.359037402304512</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.35603733257958</v>
+        <v>1.356058723228044</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350103355621986</v>
+        <v>1.350134193236379</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347794440836631</v>
+        <v>1.347826622686593</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343610857387349</v>
+        <v>1.343644228665637</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339166837913508</v>
+        <v>1.339200923814419</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336706590713197</v>
+        <v>1.336741007443061</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339732956238076</v>
+        <v>1.339754760275981</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334093721536449</v>
+        <v>1.334090857226254</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335013671762146</v>
+        <v>1.335010274680271</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332843516469721</v>
+        <v>1.332839564879396</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332519967088236</v>
+        <v>1.332506888378514</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329877319100995</v>
+        <v>1.329866607839523</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328029162109233</v>
+        <v>1.32802046620897</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331316297973842</v>
+        <v>1.331309476696746</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329385073628326</v>
+        <v>1.329391777779555</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324159958510969</v>
+        <v>1.324176644548478</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319300940543782</v>
+        <v>1.319324719958817</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.318965552040044</v>
+        <v>1.319008464830036</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316197831046343</v>
+        <v>1.316233506348055</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320071443010312</v>
+        <v>1.320097165133999</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.3189206930488</v>
+        <v>1.318898973223343</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313598228135329</v>
+        <v>1.313547531960344</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.31152431220293</v>
+        <v>1.311445561161181</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304860911059952</v>
+        <v>1.304765099553288</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.295300379934139</v>
+        <v>1.295184046534791</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291980833344424</v>
+        <v>1.291845146160365</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.296307823550296</v>
+        <v>1.296175767939385</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.313988338334051</v>
+        <v>1.313775726889565</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.326823200596531</v>
+        <v>1.32659915598763</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.357574943877495</v>
+        <v>1.357455451194657</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374900771913765</v>
+        <v>1.374880186515097</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380172934141843</v>
+        <v>1.380186249517472</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389039169189875</v>
+        <v>1.389091021445058</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390502759548482</v>
+        <v>1.390577620743407</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.388487996426646</v>
+        <v>1.388606393251727</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.387693713481254</v>
+        <v>1.387850317474259</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.391333617998028</v>
+        <v>1.391588268569676</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.387502669102824</v>
+        <v>1.387776697424198</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.390962797706415</v>
+        <v>1.3912595128426</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.374321828921467</v>
+        <v>1.374536544415409</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.369533211820137</v>
+        <v>1.369736312513393</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.356991878634429</v>
+        <v>1.357110617409461</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339358972864476</v>
+        <v>1.339367464696831</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331268741480438</v>
+        <v>1.331191906505255</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.33702014046034</v>
+        <v>1.336969277046576</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.3388264267308</v>
+        <v>1.338794403025924</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339648886743165</v>
+        <v>1.339614725883337</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340783048981714</v>
+        <v>1.340775586977662</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340318398891815</v>
+        <v>1.340331885020625</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.34225991781002</v>
+        <v>1.342291081673767</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341655759069841</v>
+        <v>1.341686042189955</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343072306382974</v>
+        <v>1.343096138804903</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341602536193974</v>
+        <v>1.341247907849203</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341931587364726</v>
+        <v>1.340890049438906</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343606444179047</v>
+        <v>1.342358162984275</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346794915757435</v>
+        <v>1.345268995585051</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.348448465797891</v>
+        <v>1.346941930881743</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.347669846683952</v>
+        <v>1.345992801666168</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.343997728850262</v>
+        <v>1.342414177774016</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.340350492831898</v>
+        <v>1.338791192714579</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.335202331017429</v>
+        <v>1.333895497244147</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.335916440464352</v>
+        <v>1.333940636454413</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.340536702592985</v>
+        <v>1.337583858664328</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.34798589411826</v>
+        <v>1.343583042168411</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.356727974903587</v>
+        <v>1.350154701384015</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,15 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.350167630584741</v>
+        <v>1.340855564558697</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B110">
+        <v>1.322968064558697</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366587443098011</v>
+        <v>1.36657769288132</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359037402304512</v>
+        <v>1.359019567680942</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356058723228044</v>
+        <v>1.35603733257958</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350134193236379</v>
+        <v>1.350103355621986</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347826622686593</v>
+        <v>1.347794440836631</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343644228665637</v>
+        <v>1.343610857387349</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339200923814419</v>
+        <v>1.339166837913508</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336741007443061</v>
+        <v>1.336706590713197</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339754760275981</v>
+        <v>1.339732956238076</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334090857226254</v>
+        <v>1.334093721536449</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335010274680271</v>
+        <v>1.335013671762146</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332839564879396</v>
+        <v>1.332843516469721</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332506888378514</v>
+        <v>1.332519967088236</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329866607839523</v>
+        <v>1.329877319100995</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.32802046620897</v>
+        <v>1.328029162109233</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331309476696746</v>
+        <v>1.331316297973842</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329391777779555</v>
+        <v>1.329385073628326</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324176644548478</v>
+        <v>1.324159958510969</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319324719958817</v>
+        <v>1.319300940543782</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319008464830036</v>
+        <v>1.318965552040044</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316233506348055</v>
+        <v>1.316197831046343</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320097165133999</v>
+        <v>1.320071443010312</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318898973223343</v>
+        <v>1.3189206930488</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313547531960344</v>
+        <v>1.313598228135329</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311445561161181</v>
+        <v>1.31152431220293</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304765099553288</v>
+        <v>1.304860911059952</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.295184046534791</v>
+        <v>1.295300379934139</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291845146160365</v>
+        <v>1.291980833344424</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.296175767939385</v>
+        <v>1.296307823550296</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.313775726889565</v>
+        <v>1.313988338334051</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.32659915598763</v>
+        <v>1.326823200596531</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.357455451194657</v>
+        <v>1.357574943877495</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374880186515097</v>
+        <v>1.374900771913765</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380186249517472</v>
+        <v>1.380172934141843</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389091021445058</v>
+        <v>1.389039169189875</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390577620743407</v>
+        <v>1.390502759548482</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.388606393251727</v>
+        <v>1.388487996426646</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.387850317474259</v>
+        <v>1.387693713481254</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.391588268569676</v>
+        <v>1.391333617998028</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.387776697424198</v>
+        <v>1.387502669102824</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.3912595128426</v>
+        <v>1.390962797706415</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.374536544415409</v>
+        <v>1.374321828921467</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.369736312513393</v>
+        <v>1.369533211820137</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357110617409461</v>
+        <v>1.356991878634429</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339367464696831</v>
+        <v>1.339358972864476</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331191906505255</v>
+        <v>1.331268741480438</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336969277046576</v>
+        <v>1.33702014046034</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338794403025924</v>
+        <v>1.3388264267308</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339614725883337</v>
+        <v>1.339648886743165</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340775586977662</v>
+        <v>1.340783048981714</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340331885020625</v>
+        <v>1.340318398891815</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342291081673767</v>
+        <v>1.34225991781002</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341686042189955</v>
+        <v>1.341655759069841</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343096138804903</v>
+        <v>1.343072306382974</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341247907849203</v>
+        <v>1.342220005397374</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.340890049438906</v>
+        <v>1.341771174470402</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.342358162984275</v>
+        <v>1.343326793040062</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.345268995585051</v>
+        <v>1.346322641002554</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.346941930881743</v>
+        <v>1.3480089521126</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.345992801666168</v>
+        <v>1.347558169118311</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.342414177774016</v>
+        <v>1.343957416863382</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.338791192714579</v>
+        <v>1.339959911688987</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.333895497244147</v>
+        <v>1.335072395440322</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.333940636454413</v>
+        <v>1.335596040986494</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.337583858664328</v>
+        <v>1.339968595332759</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.343583042168411</v>
+        <v>1.347361251209914</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.350154701384015</v>
+        <v>1.356064016553423</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.340855564558697</v>
+        <v>1.348994516565793</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.322968064558697</v>
+        <v>1.331107016565793</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343326793040062</v>
+        <v>1.343324089847242</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346322641002554</v>
+        <v>1.346316489120098</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.3480089521126</v>
+        <v>1.348027530833663</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.347558169118311</v>
+        <v>1.347372338161495</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.343957416863382</v>
+        <v>1.343581914866048</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.339959911688987</v>
+        <v>1.339686770054836</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.335072395440322</v>
+        <v>1.33486695967459</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.335596040986494</v>
+        <v>1.335432762836524</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.339968595332759</v>
+        <v>1.339827462447342</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.347361251209914</v>
+        <v>1.347262141387791</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.356064016553423</v>
+        <v>1.355985483531273</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.348994516565793</v>
+        <v>1.348887161142023</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.331107016565793</v>
+        <v>1.330999661142023</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.36657769288132</v>
+        <v>1.366582650594881</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359019567680942</v>
+        <v>1.359028635576386</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.35603733257958</v>
+        <v>1.356048207334879</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350103355621986</v>
+        <v>1.350119033373131</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347794440836631</v>
+        <v>1.347810802113407</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343610857387349</v>
+        <v>1.343627823499273</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339166837913508</v>
+        <v>1.339184167388278</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336706590713197</v>
+        <v>1.336724088338675</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339732956238076</v>
+        <v>1.33974403551925</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334093721536449</v>
+        <v>1.334092262429843</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335013671762146</v>
+        <v>1.335011941689677</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332843516469721</v>
+        <v>1.332841504397618</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332519967088236</v>
+        <v>1.33251331356799</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329877319100995</v>
+        <v>1.329871871017117</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328029162109233</v>
+        <v>1.328024740141281</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331316297973842</v>
+        <v>1.331312829451572</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329385073628326</v>
+        <v>1.329388486318257</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324159958510969</v>
+        <v>1.324168446812665</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319300940543782</v>
+        <v>1.319313036374572</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.318965552040044</v>
+        <v>1.31898736869024</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316197831046343</v>
+        <v>1.316215954656331</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320071443010312</v>
+        <v>1.320084497725879</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.3189206930488</v>
+        <v>1.318909631669147</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313598228135329</v>
+        <v>1.313572432716994</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.31152431220293</v>
+        <v>1.311484251276641</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304860911059952</v>
+        <v>1.304812177976057</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.295300379934139</v>
+        <v>1.295241214183849</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291980833344424</v>
+        <v>1.291911830820921</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.296307823550296</v>
+        <v>1.296240681374951</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.313988338334051</v>
+        <v>1.313880281698436</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.326823200596531</v>
+        <v>1.326709333370177</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.357574943877495</v>
+        <v>1.357514241517864</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374900771913765</v>
+        <v>1.374890323412752</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380172934141843</v>
+        <v>1.380179736967509</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389039169189875</v>
+        <v>1.389065581686641</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390502759548482</v>
+        <v>1.390540895144385</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.388487996426646</v>
+        <v>1.388548268537408</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.387693713481254</v>
+        <v>1.387773412626706</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.391333617998028</v>
+        <v>1.391463080105556</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.387502669102824</v>
+        <v>1.387641954688348</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.390962797706415</v>
+        <v>1.391113591395385</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.374321828921467</v>
+        <v>1.374430893038282</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.369533211820137</v>
+        <v>1.369636344059205</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.356991878634429</v>
+        <v>1.357052118906834</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339358972864476</v>
+        <v>1.33936324232983</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331268741480438</v>
+        <v>1.331229705304831</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.33702014046034</v>
+        <v>1.336994298888993</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.3388264267308</v>
+        <v>1.33881016461371</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339648886743165</v>
+        <v>1.339631552755354</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340783048981714</v>
+        <v>1.340779286670307</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340318398891815</v>
+        <v>1.340325292422731</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.34225991781002</v>
+        <v>1.342275788236684</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341655759069841</v>
+        <v>1.341671171438727</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343072306382974</v>
+        <v>1.343084387792248</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.342220005397374</v>
+        <v>1.34223526213669</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341771174470402</v>
+        <v>1.341036565900786</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343324089847242</v>
+        <v>1.342417204173405</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346316489120098</v>
+        <v>1.345257387974516</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.348027530833663</v>
+        <v>1.347099027882879</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.347372338161495</v>
+        <v>1.34631493299698</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.343581914866048</v>
+        <v>1.342532031955658</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.339686770054836</v>
+        <v>1.338604471104047</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.33486695967459</v>
+        <v>1.333755384978302</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.335432762836524</v>
+        <v>1.333939629681955</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.339827462447342</v>
+        <v>1.337698896614312</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.347262141387791</v>
+        <v>1.344322289084211</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.355985483531273</v>
+        <v>1.351843897368479</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.348887161142023</v>
+        <v>1.342691283428658</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.330999661142023</v>
+        <v>1.324803783428658</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366582650594881</v>
+        <v>1.366592078512828</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359028635576386</v>
+        <v>1.359045882621191</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356048207334879</v>
+        <v>1.3560688977274</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350119033373131</v>
+        <v>1.350148860444417</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347810802113407</v>
+        <v>1.347841928912033</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343627823499273</v>
+        <v>1.343660100241334</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339184167388278</v>
+        <v>1.339217135141465</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336724088338675</v>
+        <v>1.336757376238612</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.33974403551925</v>
+        <v>1.339765147218082</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334092262429843</v>
+        <v>1.33408950301964</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335011941689677</v>
+        <v>1.335008667371309</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332841504397618</v>
+        <v>1.332837694081355</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.33251331356799</v>
+        <v>1.332500679982505</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329871871017117</v>
+        <v>1.329861520328258</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328024740141281</v>
+        <v>1.328016333005529</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331312829451572</v>
+        <v>1.331306234013765</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329388486318257</v>
+        <v>1.329394954331473</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324168446812665</v>
+        <v>1.324184566349814</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319313036374572</v>
+        <v>1.319336011971369</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.31898736869024</v>
+        <v>1.319028875539514</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316215954656331</v>
+        <v>1.316250512650488</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320084497725879</v>
+        <v>1.320109461944212</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318909631669147</v>
+        <v>1.318888696305802</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313572432716994</v>
+        <v>1.313523480340267</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311484251276641</v>
+        <v>1.311408172987209</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304812177976057</v>
+        <v>1.304719593316557</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.295241214183849</v>
+        <v>1.295128777948148</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291911830820921</v>
+        <v>1.291780665117483</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.296240681374951</v>
+        <v>1.296112974476027</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.313880281698436</v>
+        <v>1.313674506969398</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.326709333370177</v>
+        <v>1.326492492553344</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.357514241517864</v>
+        <v>1.357398484420413</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374890323412752</v>
+        <v>1.374870347856432</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380179736967509</v>
+        <v>1.380192489234741</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389065581686641</v>
+        <v>1.389115540694386</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390540895144385</v>
+        <v>1.390613012038697</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.388548268537408</v>
+        <v>1.38866248221853</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.387773412626706</v>
+        <v>1.387924571114223</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.391463080105556</v>
+        <v>1.391709390624033</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.387641954688348</v>
+        <v>1.387907114751154</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.391113591395385</v>
+        <v>1.391400793282716</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.374430893038282</v>
+        <v>1.374638939694812</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.369636344059205</v>
+        <v>1.369833259163315</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357052118906834</v>
+        <v>1.3571674470087</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.33936324232983</v>
+        <v>1.339371638041815</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331229705304831</v>
+        <v>1.331155287583992</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336994298888993</v>
+        <v>1.336945036857508</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.33881016461371</v>
+        <v>1.338779119538162</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339631552755354</v>
+        <v>1.339598384644932</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340779286670307</v>
+        <v>1.340771949836591</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340325292422731</v>
+        <v>1.34033819478678</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342275788236684</v>
+        <v>1.342305828682673</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341671171438727</v>
+        <v>1.341700399038583</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343084387792248</v>
+        <v>1.343107571967232</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.34223526213669</v>
+        <v>1.341266453240329</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341036565900786</v>
+        <v>1.340247772047664</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.342417204173405</v>
+        <v>1.341548036664657</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.345257387974516</v>
+        <v>1.344265815520416</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.347099027882879</v>
+        <v>1.345841413631134</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.34631493299698</v>
+        <v>1.344843082481538</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.342532031955658</v>
+        <v>1.341302334362842</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.338604471104047</v>
+        <v>1.337683491634851</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.333755384978302</v>
+        <v>1.332807555576323</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.333939629681955</v>
+        <v>1.332571949985759</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.337698896614312</v>
+        <v>1.335703610575584</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.344322289084211</v>
+        <v>1.34108425971334</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.351843897368479</v>
+        <v>1.346758110171856</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.342691283428658</v>
+        <v>1.336536634403319</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.324803783428658</v>
+        <v>1.318649134403319</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366592078512828</v>
+        <v>1.366587443098011</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359045882621191</v>
+        <v>1.359037402304512</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.3560688977274</v>
+        <v>1.356058723228044</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350148860444417</v>
+        <v>1.350134193236379</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347841928912033</v>
+        <v>1.347826622686593</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343660100241334</v>
+        <v>1.343644228665637</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339217135141465</v>
+        <v>1.339200923814419</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336757376238612</v>
+        <v>1.336741007443061</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339765147218082</v>
+        <v>1.339754760275981</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.33408950301964</v>
+        <v>1.334090857226254</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335008667371309</v>
+        <v>1.335010274680271</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332837694081355</v>
+        <v>1.332839564879396</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332500679982505</v>
+        <v>1.332506888378514</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329861520328258</v>
+        <v>1.329866607839523</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328016333005529</v>
+        <v>1.32802046620897</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331306234013765</v>
+        <v>1.331309476696746</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329394954331473</v>
+        <v>1.329391777779555</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324184566349814</v>
+        <v>1.324176644548478</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319336011971369</v>
+        <v>1.319324719958817</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319028875539514</v>
+        <v>1.319008464830036</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316250512650488</v>
+        <v>1.316233506348055</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320109461944212</v>
+        <v>1.320097165133999</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318888696305802</v>
+        <v>1.318898973223343</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313523480340267</v>
+        <v>1.313547531960344</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311408172987209</v>
+        <v>1.311445561161181</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304719593316557</v>
+        <v>1.304765099553288</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.295128777948148</v>
+        <v>1.295184046534791</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291780665117483</v>
+        <v>1.291845146160365</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.296112974476027</v>
+        <v>1.296175767939385</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.313674506969398</v>
+        <v>1.313775726889565</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.326492492553344</v>
+        <v>1.32659915598763</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.357398484420413</v>
+        <v>1.357455451194657</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374870347856432</v>
+        <v>1.374880186515097</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380192489234741</v>
+        <v>1.380186249517472</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389115540694386</v>
+        <v>1.389091021445058</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390613012038697</v>
+        <v>1.390577620743407</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.38866248221853</v>
+        <v>1.388606393251727</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.387924571114223</v>
+        <v>1.387850317474259</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.391709390624033</v>
+        <v>1.391588268569676</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.387907114751154</v>
+        <v>1.387776697424198</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.391400793282716</v>
+        <v>1.3912595128426</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.374638939694812</v>
+        <v>1.374536544415409</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.369833259163315</v>
+        <v>1.369736312513393</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.3571674470087</v>
+        <v>1.357110617409461</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339371638041815</v>
+        <v>1.339367464696831</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331155287583992</v>
+        <v>1.331191906505255</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336945036857508</v>
+        <v>1.336969277046576</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338779119538162</v>
+        <v>1.338794403025924</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339598384644932</v>
+        <v>1.339614725883337</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340771949836591</v>
+        <v>1.340775586977662</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.34033819478678</v>
+        <v>1.340331885020625</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342305828682673</v>
+        <v>1.342291081673767</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341700399038583</v>
+        <v>1.341686042189955</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343107571967232</v>
+        <v>1.343096138804903</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341266453240329</v>
+        <v>1.342250080436516</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.340247772047664</v>
+        <v>1.340747712200714</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.341548036664657</v>
+        <v>1.342057941832001</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.344265815520416</v>
+        <v>1.344807980223147</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.345841413631134</v>
+        <v>1.346903278230628</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.344843082481538</v>
+        <v>1.346122941042501</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.341302334362842</v>
+        <v>1.342435829022299</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.337683491634851</v>
+        <v>1.338553563800299</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.332807555576323</v>
+        <v>1.333795373068662</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.332571949985759</v>
+        <v>1.333903537826709</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.335703610575584</v>
+        <v>1.33737908438935</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.34108425971334</v>
+        <v>1.343514233935971</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.346758110171856</v>
+        <v>1.350414857494542</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.336536634403319</v>
+        <v>1.341959248289352</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.318649134403319</v>
+        <v>1.322768895328923</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366587443098011</v>
+        <v>1.366596564437675</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359037402304512</v>
+        <v>1.359054090333997</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356058723228044</v>
+        <v>1.356078747186058</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350134193236379</v>
+        <v>1.350163058617663</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347826622686593</v>
+        <v>1.347856745460803</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343644228665637</v>
+        <v>1.343675463831831</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339200923814419</v>
+        <v>1.339232827531211</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336741007443061</v>
+        <v>1.336773221133302</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339754760275981</v>
+        <v>1.339775212024011</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334090857226254</v>
+        <v>1.334088197107647</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335010274680271</v>
+        <v>1.33500711663369</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332839564879396</v>
+        <v>1.33283588843398</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332506888378514</v>
+        <v>1.332494677605977</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329866607839523</v>
+        <v>1.329856599847911</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.32802046620897</v>
+        <v>1.328012333696985</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331309476696746</v>
+        <v>1.331303096074302</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329391777779555</v>
+        <v>1.3293980218632</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324176644548478</v>
+        <v>1.324192225884214</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319324719958817</v>
+        <v>1.319346931730173</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319008464830036</v>
+        <v>1.319048633659913</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316233506348055</v>
+        <v>1.316266998484821</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320097165133999</v>
+        <v>1.320121403937547</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318898973223343</v>
+        <v>1.318878780988415</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313547531960344</v>
+        <v>1.313500235355383</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311445561161181</v>
+        <v>1.311372022404122</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304765099553288</v>
+        <v>1.304675582158616</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.295184046534791</v>
+        <v>1.29507531579366</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291845146160365</v>
+        <v>1.291718280796086</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.296175767939385</v>
+        <v>1.296052199157311</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.313775726889565</v>
+        <v>1.313576465408793</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.32659915598763</v>
+        <v>1.326389178139347</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.357455451194657</v>
+        <v>1.357343258055671</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374880186515097</v>
+        <v>1.37486079479913</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380186249517472</v>
+        <v>1.380198472231228</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389091021445058</v>
+        <v>1.389139188022401</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390577620743407</v>
+        <v>1.390647139461961</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.388606393251727</v>
+        <v>1.38871663954322</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.387850317474259</v>
+        <v>1.387996307109091</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.391588268569676</v>
+        <v>1.391826640375595</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.387776697424198</v>
+        <v>1.38803341052926</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.3912595128426</v>
+        <v>1.391537649618688</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.374536544415409</v>
+        <v>1.374738226146083</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.369736312513393</v>
+        <v>1.369927317711416</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357110617409461</v>
+        <v>1.35722267667254</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339367464696831</v>
+        <v>1.33937576081017</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331191906505255</v>
+        <v>1.33111979452427</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336969277046576</v>
+        <v>1.33692154254791</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338794403025924</v>
+        <v>1.338764293019689</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339614725883337</v>
+        <v>1.339582508723599</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340775586977662</v>
+        <v>1.340768374995946</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340331885020625</v>
+        <v>1.340344238455223</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342291081673767</v>
+        <v>1.342320057723713</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341686042189955</v>
+        <v>1.341714267860433</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343096138804903</v>
+        <v>1.343118699260451</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.342250080436516</v>
+        <v>1.341284457740756</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.340747712200714</v>
+        <v>1.340561509058737</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.342057941832001</v>
+        <v>1.341922663714032</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.344807980223147</v>
+        <v>1.344600690652764</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.346903278230628</v>
+        <v>1.346290541123791</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.346122941042501</v>
+        <v>1.345404264784035</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.342435829022299</v>
+        <v>1.342004604431142</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.338553563800299</v>
+        <v>1.338456337831744</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.333795373068662</v>
+        <v>1.333738936692443</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.333903537826709</v>
+        <v>1.333550453582899</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.33737908438935</v>
+        <v>1.336445466911024</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.343514233935971</v>
+        <v>1.341484880192873</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.350414857494542</v>
+        <v>1.346814458053849</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.341959248289352</v>
+        <v>1.337939774256422</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.322768895328923</v>
+        <v>1.32132402746643</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366596564437675</v>
+        <v>1.366600907988672</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359054090333997</v>
+        <v>1.359062038377166</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356078747186058</v>
+        <v>1.356088286929485</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350163058617663</v>
+        <v>1.350176809890965</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347856745460803</v>
+        <v>1.347871095451657</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343675463831831</v>
+        <v>1.343690343430765</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339232827531211</v>
+        <v>1.339248025498339</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336773221133302</v>
+        <v>1.336788566872731</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339775212024011</v>
+        <v>1.339784969419024</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334088197107647</v>
+        <v>1.334086936974181</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.33500711663369</v>
+        <v>1.335005619552017</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.33283588843398</v>
+        <v>1.332834144609663</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332494677605977</v>
+        <v>1.332488871176249</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329856599847911</v>
+        <v>1.329851838319043</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328012333696985</v>
+        <v>1.328008461884555</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331303096074302</v>
+        <v>1.33130005788819</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.3293980218632</v>
+        <v>1.329400985869714</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324192225884214</v>
+        <v>1.32419963593327</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319346931730173</v>
+        <v>1.319357497305574</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319048633659913</v>
+        <v>1.319067769969269</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316266998484821</v>
+        <v>1.316282987283793</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320121403937547</v>
+        <v>1.320133006028485</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318878780988415</v>
+        <v>1.318869208696115</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313500235355383</v>
+        <v>1.313477757282099</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311372022404122</v>
+        <v>1.311337049216817</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304675582158616</v>
+        <v>1.304632993912144</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.29507531579366</v>
+        <v>1.295023573341816</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291718280796086</v>
+        <v>1.291657893070335</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.296052199157311</v>
+        <v>1.295993346552681</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.313576465408793</v>
+        <v>1.313481455291475</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.326389178139347</v>
+        <v>1.326289057946442</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.357343258055671</v>
+        <v>1.357289693913286</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.37486079479913</v>
+        <v>1.374851515386007</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380198472231228</v>
+        <v>1.380204213409729</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389139188022401</v>
+        <v>1.389162008684954</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390647139461961</v>
+        <v>1.390680068628491</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.38871663954322</v>
+        <v>1.388768962409502</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.387996307109091</v>
+        <v>1.388065650267893</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.391826640375595</v>
+        <v>1.39194019982326</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.38803341052926</v>
+        <v>1.388155776075698</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.391537649618688</v>
+        <v>1.391670285509452</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.374738226146083</v>
+        <v>1.374834542351519</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.369927317711416</v>
+        <v>1.370018614169124</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.35722267667254</v>
+        <v>1.357276371718307</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.33937576081017</v>
+        <v>1.339379831769864</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.33111979452427</v>
+        <v>1.331085376532935</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.33692154254791</v>
+        <v>1.336898760475889</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338764293019689</v>
+        <v>1.338749903547488</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339582508723599</v>
+        <v>1.339567078893072</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340768374995946</v>
+        <v>1.340764862049595</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340344238455223</v>
+        <v>1.340350031515941</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342320057723713</v>
+        <v>1.342333795332197</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341714267860433</v>
+        <v>1.341727672840712</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343118699260451</v>
+        <v>1.343129532126015</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341284457740756</v>
+        <v>1.341301944391372</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.340561509058737</v>
+        <v>1.341030239844556</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.341922663714032</v>
+        <v>1.342491988189775</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.344600690652764</v>
+        <v>1.345172548624408</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.346290541123791</v>
+        <v>1.346988919675824</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.345404264784035</v>
+        <v>1.346237894385931</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.342004604431142</v>
+        <v>1.343002801114413</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.338456337831744</v>
+        <v>1.339544773609175</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.333738936692443</v>
+        <v>1.335012223188423</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.333550453582899</v>
+        <v>1.334934836559629</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.336445466911024</v>
+        <v>1.337698459032949</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.341484880192873</v>
+        <v>1.342501329599707</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.346814458053849</v>
+        <v>1.34763825444229</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.337939774256422</v>
+        <v>1.340273859988586</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.32132402746643</v>
+        <v>1.331009450070996</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341301944391372</v>
+        <v>1.342292081844735</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341030239844556</v>
+        <v>1.341507148702311</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.342491988189775</v>
+        <v>1.342932044033717</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.345172548624408</v>
+        <v>1.345648083077952</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.346988919675824</v>
+        <v>1.347945550488082</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.346237894385931</v>
+        <v>1.34748656235905</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.343002801114413</v>
+        <v>1.344310618806692</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.339544773609175</v>
+        <v>1.34078315164575</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.335012223188423</v>
+        <v>1.336636627299999</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.334934836559629</v>
+        <v>1.337043186439283</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.337698459032949</v>
+        <v>1.340485722405024</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.342501329599707</v>
+        <v>1.345676855720373</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.34763825444229</v>
+        <v>1.351884025516092</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.340273859988586</v>
+        <v>1.347819674693585</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,15 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.331009450070996</v>
+        <v>1.342964969420485</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B111">
+        <v>1.323283248453742</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366600907988672</v>
+        <v>1.366605115837368</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359062038377166</v>
+        <v>1.35906973887956</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356088286929485</v>
+        <v>1.356097531334943</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350176809890965</v>
+        <v>1.350190135028528</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347871095451657</v>
+        <v>1.347885000571181</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343690343430765</v>
+        <v>1.343704761544754</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339248025498339</v>
+        <v>1.339262752037983</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336788566872731</v>
+        <v>1.336803436668854</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339784969419024</v>
+        <v>1.339794433246362</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334086936974181</v>
+        <v>1.334085720273719</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335005619552017</v>
+        <v>1.335004173406735</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332834144609663</v>
+        <v>1.332832459502622</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332488871176249</v>
+        <v>1.332483251265864</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329851838319043</v>
+        <v>1.329847228174227</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328008461884555</v>
+        <v>1.328004711570564</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.33130005788819</v>
+        <v>1.33129711477704</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329400985869714</v>
+        <v>1.329403851484118</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.32419963593327</v>
+        <v>1.324206808463114</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319357497305574</v>
+        <v>1.319367725619241</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319067769969269</v>
+        <v>1.319086313341787</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316282987283793</v>
+        <v>1.316298501100615</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320133006028485</v>
+        <v>1.320144282322185</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318869208696115</v>
+        <v>1.318859962094732</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313477757282099</v>
+        <v>1.313456008952199</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311337049216817</v>
+        <v>1.311303197056811</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304632993912144</v>
+        <v>1.304591760961952</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.295023573341816</v>
+        <v>1.29497346930338</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291657893070335</v>
+        <v>1.291599408059596</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295993346552681</v>
+        <v>1.295936327135638</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.313481455291475</v>
+        <v>1.313389338589718</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.326289057946442</v>
+        <v>1.326191986540963</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.357289693913286</v>
+        <v>1.357237718397154</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374851515386007</v>
+        <v>1.374842498297254</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380204213409729</v>
+        <v>1.380209726572944</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389162008684954</v>
+        <v>1.389184044884709</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390680068628491</v>
+        <v>1.390711860738139</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.388768962409502</v>
+        <v>1.388819541641096</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388065650267893</v>
+        <v>1.388132717346729</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.39194019982326</v>
+        <v>1.392050239783486</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.388155776075698</v>
+        <v>1.388274391109484</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.391670285509452</v>
+        <v>1.391798892360571</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.374834542351519</v>
+        <v>1.3749280188325</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.370018614169124</v>
+        <v>1.370107267395451</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357276371718307</v>
+        <v>1.357328594042756</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339379831769864</v>
+        <v>1.339383849970726</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331085376532935</v>
+        <v>1.331051985805417</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336898760475889</v>
+        <v>1.336876658976466</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338749903547488</v>
+        <v>1.338735932322777</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339567078893072</v>
+        <v>1.3395520769475</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340764862049595</v>
+        <v>1.340761410461408</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340350031515941</v>
+        <v>1.340355588325271</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342333795332197</v>
+        <v>1.342347066277223</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341727672840712</v>
+        <v>1.341740636608578</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343129532126015</v>
+        <v>1.34314008149037</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.342292081844735</v>
+        <v>1.341318934958479</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341507148702311</v>
+        <v>1.341043828943283</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.342932044033717</v>
+        <v>1.342512869761026</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.345648083077952</v>
+        <v>1.345116278528376</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.347945550488082</v>
+        <v>1.346817755798353</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.34748656235905</v>
+        <v>1.346014368390313</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.344310618806692</v>
+        <v>1.342848558565385</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.34078315164575</v>
+        <v>1.33945548042123</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.336636627299999</v>
+        <v>1.335020300057077</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.337043186439283</v>
+        <v>1.334837152627876</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.340485722405024</v>
+        <v>1.337368752629308</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.345676855720373</v>
+        <v>1.34161877541491</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.351884025516092</v>
+        <v>1.34628213490011</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.347819674693585</v>
+        <v>1.339069574875368</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.342964969420485</v>
+        <v>1.330338888177532</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.323283248453742</v>
+        <v>1.32655232688669</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341318934958479</v>
+        <v>1.34230531894676</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341043828943283</v>
+        <v>1.341518918378994</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.342512869761026</v>
+        <v>1.34292851487211</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.345116278528376</v>
+        <v>1.345547853110062</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.346817755798353</v>
+        <v>1.347680041025749</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.346014368390313</v>
+        <v>1.347128941345499</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.342848558565385</v>
+        <v>1.343972016737321</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.33945548042123</v>
+        <v>1.34048023480483</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.335020300057077</v>
+        <v>1.336361457911145</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.334837152627876</v>
+        <v>1.336579062557683</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.337368752629308</v>
+        <v>1.33972746603545</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.34161877541491</v>
+        <v>1.344275815433039</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.34628213490011</v>
+        <v>1.349901981068143</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.339069574875368</v>
+        <v>1.345429134733195</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.330338888177532</v>
+        <v>1.340106680496349</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.32655232688669</v>
+        <v>1.32358377366618</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366605115837368</v>
+        <v>1.366609194244922</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.35906973887956</v>
+        <v>1.359077203226382</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356097531334943</v>
+        <v>1.356106493903686</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350190135028528</v>
+        <v>1.35020305352835</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347885000571181</v>
+        <v>1.347898481182952</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343704761544754</v>
+        <v>1.343718739306787</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339262752037983</v>
+        <v>1.339277028741621</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336803436668854</v>
+        <v>1.336817852316933</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339794433246362</v>
+        <v>1.339803616532158</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334085720273719</v>
+        <v>1.334084544817189</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335004173406735</v>
+        <v>1.335002775658038</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332832459502622</v>
+        <v>1.332830830210798</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332483251265864</v>
+        <v>1.332477809041809</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329847228174227</v>
+        <v>1.329842762318171</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328004711570564</v>
+        <v>1.328001077127516</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.33129711477704</v>
+        <v>1.331294262350282</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329403851484118</v>
+        <v>1.329406623506853</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324206808463114</v>
+        <v>1.324213754688297</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319367725619241</v>
+        <v>1.319377632533848</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319086313341787</v>
+        <v>1.319104290892685</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316298501100615</v>
+        <v>1.316313560708525</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320144282322185</v>
+        <v>1.320155246167397</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318859962094732</v>
+        <v>1.318851024989755</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313456008952199</v>
+        <v>1.313434955551394</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311303197056811</v>
+        <v>1.311270413084011</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304591760961952</v>
+        <v>1.304551819893025</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.29497346930338</v>
+        <v>1.294924927411188</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291599408059596</v>
+        <v>1.291542737651201</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295936327135638</v>
+        <v>1.295881056835528</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.313389338589718</v>
+        <v>1.313299985504308</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.326191986540963</v>
+        <v>1.326097827159293</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.357237718397154</v>
+        <v>1.357187262171909</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374842498297254</v>
+        <v>1.374833732810354</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380209726572944</v>
+        <v>1.380215024521096</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389184044884709</v>
+        <v>1.389205336022515</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390711860738139</v>
+        <v>1.3907425729372</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.388819541641096</v>
+        <v>1.388868462209984</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388132717346729</v>
+        <v>1.388197617683521</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.392050239783486</v>
+        <v>1.392156920732639</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.388274391109484</v>
+        <v>1.388389424612525</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.391798892360571</v>
+        <v>1.391923650227718</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.3749280188325</v>
+        <v>1.3750187786229</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.370107267395451</v>
+        <v>1.370193389591587</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357328594042756</v>
+        <v>1.357379402335821</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339383849970726</v>
+        <v>1.339387814708743</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.331051985805417</v>
+        <v>1.33101957731078</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336876658976466</v>
+        <v>1.336855208219718</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338735932322777</v>
+        <v>1.338722361594199</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.3395520769475</v>
+        <v>1.339537485636655</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340761410461408</v>
+        <v>1.340758019586784</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340355588325271</v>
+        <v>1.340360922204984</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342347066277223</v>
+        <v>1.342359893705113</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341740636608578</v>
+        <v>1.341753180359165</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.34314008149037</v>
+        <v>1.343150357789028</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.34230531894676</v>
+        <v>1.341335450019655</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341518918378994</v>
+        <v>1.341057070619986</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.34292851487211</v>
+        <v>1.342531651516301</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.345547853110062</v>
+        <v>1.345064914696489</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.347680041025749</v>
+        <v>1.346657945496296</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.347128941345499</v>
+        <v>1.345807583584987</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.343972016737321</v>
+        <v>1.342722107371268</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.34048023480483</v>
+        <v>1.339376423718182</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.336361457911145</v>
+        <v>1.33503595130437</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.336579062557683</v>
+        <v>1.334762808579407</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.33972746603545</v>
+        <v>1.337090014306192</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.344275815433039</v>
+        <v>1.340853228756986</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.349901981068143</v>
+        <v>1.345111428362896</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.345429134733195</v>
+        <v>1.338107365186047</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.340106680496349</v>
+        <v>1.329963749405502</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.32358377366618</v>
+        <v>1.326770025221802</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341335450019655</v>
+        <v>1.342318199502456</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341057070619986</v>
+        <v>1.341530396212993</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.342531651516301</v>
+        <v>1.343122353589878</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.345064914696489</v>
+        <v>1.345693995071257</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.346657945496296</v>
+        <v>1.3476922791047</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.345807583584987</v>
+        <v>1.347152385339667</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.342722107371268</v>
+        <v>1.3440785483421</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.339376423718182</v>
+        <v>1.340645357534783</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.33503595130437</v>
+        <v>1.336622394443998</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.334762808579407</v>
+        <v>1.336775473738656</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.337090014306192</v>
+        <v>1.339732474030565</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.340853228756986</v>
+        <v>1.343841199956647</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.345111428362896</v>
+        <v>1.349088669667783</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.338107365186047</v>
+        <v>1.344805280566671</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.329963749405502</v>
+        <v>1.339999782789274</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.326770025221802</v>
+        <v>1.328997084876993</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366609194244922</v>
+        <v>1.36661314909318</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359077203226382</v>
+        <v>1.359084442115299</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356106493903686</v>
+        <v>1.356115187326651</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.35020305352835</v>
+        <v>1.350215583717247</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347898481182952</v>
+        <v>1.347911556426875</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343718739306787</v>
+        <v>1.34373229657941</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339277028741621</v>
+        <v>1.339290875902531</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336817852316933</v>
+        <v>1.336831834301951</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339803616532158</v>
+        <v>1.339812531544712</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334084544817189</v>
+        <v>1.334083408559207</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335002775658038</v>
+        <v>1.335001423931328</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332830830210798</v>
+        <v>1.332829254019477</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332477809041809</v>
+        <v>1.332472536219439</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329842762318171</v>
+        <v>1.329838434091521</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.328001077127516</v>
+        <v>1.327997553269989</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331294262350282</v>
+        <v>1.331291496483382</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329406623506853</v>
+        <v>1.329409306432136</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324213754688297</v>
+        <v>1.32422048512977</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319377632533848</v>
+        <v>1.319387232934492</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319104290892685</v>
+        <v>1.319121728110015</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316313560708525</v>
+        <v>1.316328185691882</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320155246167397</v>
+        <v>1.320165910205389</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318851024989755</v>
+        <v>1.318842382234795</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313434955551394</v>
+        <v>1.313414564436563</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311270413084011</v>
+        <v>1.31123864771584</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304551819893025</v>
+        <v>1.304513111170595</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294924927411188</v>
+        <v>1.29487787603979</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291542737651201</v>
+        <v>1.291487799066128</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295881056835528</v>
+        <v>1.295827456629432</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.313299985504308</v>
+        <v>1.313213273862285</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.326097827159293</v>
+        <v>1.326006451073251</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.357187262171909</v>
+        <v>1.35713825986057</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374833732810354</v>
+        <v>1.374825208762805</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380215024521096</v>
+        <v>1.380220119139498</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389205336022515</v>
+        <v>1.389225918924518</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.3907425729372</v>
+        <v>1.390772258645564</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.388868462209984</v>
+        <v>1.388915803696988</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388197617683521</v>
+        <v>1.388260453774025</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.392156920732639</v>
+        <v>1.392260393574637</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.388389424612525</v>
+        <v>1.388501035615525</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.391923650227718</v>
+        <v>1.392044728641786</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.3750187786229</v>
+        <v>1.375106937794633</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.370193389591587</v>
+        <v>1.370277086755552</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357379402335821</v>
+        <v>1.357428852279276</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339387814708743</v>
+        <v>1.339391725494719</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.33101957731078</v>
+        <v>1.330988108594913</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336855208219718</v>
+        <v>1.336834380080846</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338722361594199</v>
+        <v>1.338709174587086</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339537485636655</v>
+        <v>1.339523288605808</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340758019586784</v>
+        <v>1.340754688691222</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340360922204984</v>
+        <v>1.340366045531359</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342359893705113</v>
+        <v>1.342372299269189</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341753180359165</v>
+        <v>1.341765323964399</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343150357789028</v>
+        <v>1.343160370989854</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.342318199502456</v>
+        <v>1.341351509042854</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341530396212993</v>
+        <v>1.341069977513542</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343122353589878</v>
+        <v>1.342741147150677</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.345693995071257</v>
+        <v>1.345249324831569</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.3476922791047</v>
+        <v>1.346759517392906</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.347152385339667</v>
+        <v>1.345939858801307</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.3440785483421</v>
+        <v>1.342944517715134</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.340645357534783</v>
+        <v>1.339669699205649</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.336622394443998</v>
+        <v>1.335457460701167</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.336775473738656</v>
+        <v>1.33517326649265</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.339732474030565</v>
+        <v>1.337367050106074</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.343841199956647</v>
+        <v>1.340778262496966</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.349088669667783</v>
+        <v>1.344774599563322</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.344805280566671</v>
+        <v>1.338303038265195</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.339999782789274</v>
+        <v>1.331521878432907</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.328997084876993</v>
+        <v>1.331122544427409</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341351509042854</v>
+        <v>1.342330737445714</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341069977513542</v>
+        <v>1.341541592365645</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.342741147150677</v>
+        <v>1.343225497240242</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.345249324831569</v>
+        <v>1.345740349378733</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.346759517392906</v>
+        <v>1.347599174826269</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.345939858801307</v>
+        <v>1.347039093846104</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.342944517715134</v>
+        <v>1.344023088616854</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.339669699205649</v>
+        <v>1.340633026054481</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.335457460701167</v>
+        <v>1.336680379428979</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.33517326649265</v>
+        <v>1.336743119882339</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.337367050106074</v>
+        <v>1.339506119022906</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.340778262496966</v>
+        <v>1.343182956635017</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.344774599563322</v>
+        <v>1.348061758881131</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.338303038265195</v>
+        <v>1.343847934530944</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.331521878432907</v>
+        <v>1.33929697577533</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.331122544427409</v>
+        <v>1.330334967008858</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.36661314909318</v>
+        <v>1.366620709909879</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359084442115299</v>
+        <v>1.359098283174631</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356115187326651</v>
+        <v>1.356131813801428</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350215583717247</v>
+        <v>1.350239547125672</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347911556426875</v>
+        <v>1.347936561787637</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.34373229657941</v>
+        <v>1.343758223310267</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339290875902531</v>
+        <v>1.339317356846372</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336831834301951</v>
+        <v>1.336858573244688</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339812531544712</v>
+        <v>1.339829602354778</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334083408559207</v>
+        <v>1.334081246107699</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335001423931328</v>
+        <v>1.334998849793799</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332829254019477</v>
+        <v>1.332826250928654</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332472536219439</v>
+        <v>1.33246246813568</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329838434091521</v>
+        <v>1.329830165874071</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327997553269989</v>
+        <v>1.327990817728867</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331291496483382</v>
+        <v>1.331286209143965</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329409306432136</v>
+        <v>1.329414421577647</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.32422048512977</v>
+        <v>1.324233337588856</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319387232934492</v>
+        <v>1.31940556928398</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319121728110015</v>
+        <v>1.319155076070814</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316328185691882</v>
+        <v>1.316356204671887</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320165910205389</v>
+        <v>1.320186386155806</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318842382234795</v>
+        <v>1.318825923940244</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313414564436563</v>
+        <v>1.31337564836686</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.31123864771584</v>
+        <v>1.311177989294404</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304513111170595</v>
+        <v>1.304439170305797</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.29487787603979</v>
+        <v>1.294787979517937</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291487799066128</v>
+        <v>1.291382810577685</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295827456629432</v>
+        <v>1.295724973445872</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.313213273862285</v>
+        <v>1.313047321092832</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.326006451073251</v>
+        <v>1.325831570622751</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.35713825986057</v>
+        <v>1.357044373623777</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374825208762805</v>
+        <v>1.374808846930044</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380220119139498</v>
+        <v>1.380229741818038</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389225918924518</v>
+        <v>1.389265095665935</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390772258645564</v>
+        <v>1.390828747387375</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.388915803696988</v>
+        <v>1.389006043262869</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388260453774025</v>
+        <v>1.388380312082249</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.392260393574637</v>
+        <v>1.392458274833374</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.388501035615525</v>
+        <v>1.388714580736549</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.392044728641786</v>
+        <v>1.392276477073674</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375106937794633</v>
+        <v>1.375275886614138</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.370277086755552</v>
+        <v>1.370437601440419</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357428852279276</v>
+        <v>1.357523885898943</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339391725494719</v>
+        <v>1.339399384165972</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330988108594913</v>
+        <v>1.33092783249946</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336834380080846</v>
+        <v>1.336794486978024</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338709174587086</v>
+        <v>1.33868388913598</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339523288605808</v>
+        <v>1.339496016111812</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340754688691222</v>
+        <v>1.340748203543701</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340366045531359</v>
+        <v>1.340375705775096</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342372299269189</v>
+        <v>1.342395924648885</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341765323964399</v>
+        <v>1.341788484206146</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343160370989854</v>
+        <v>1.343179645765075</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.342330737445714</v>
+        <v>1.341382331731068</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341541592365645</v>
+        <v>1.341094834671757</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343225497240242</v>
+        <v>1.342971393227361</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.345740349378733</v>
+        <v>1.345405065583285</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.347599174826269</v>
+        <v>1.34670419334426</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.347039093846104</v>
+        <v>1.345983233902865</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.344023088616854</v>
+        <v>1.342928595260912</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.340633026054481</v>
+        <v>1.339627182403933</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.336680379428979</v>
+        <v>1.335457351344635</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.336743119882339</v>
+        <v>1.334935072260615</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.339506119022906</v>
+        <v>1.336717584846469</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.343182956635017</v>
+        <v>1.339133265342912</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.348061758881131</v>
+        <v>1.342387988274051</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.343847934530944</v>
+        <v>1.336024971613751</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.33929697577533</v>
+        <v>1.329223208318141</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.330334967008858</v>
+        <v>1.326452324072125</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366620709909879</v>
+        <v>1.366616985912965</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359098283174631</v>
+        <v>1.359091465607561</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356131813801428</v>
+        <v>1.356123623544332</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350239547125672</v>
+        <v>1.350227742837458</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347936561787637</v>
+        <v>1.347924244309702</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343758223310267</v>
+        <v>1.343745452048741</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339317356846372</v>
+        <v>1.339304312611872</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336858573244688</v>
+        <v>1.336845401895584</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339829602354778</v>
+        <v>1.339821189848696</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334081246107699</v>
+        <v>1.334082309586548</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334998849793799</v>
+        <v>1.335000116004057</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332826250928654</v>
+        <v>1.332827728386466</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.33246246813568</v>
+        <v>1.332467425020627</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329830165874071</v>
+        <v>1.329834237237931</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327990817728867</v>
+        <v>1.327994135029036</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331286209143965</v>
+        <v>1.331288813298013</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329414421577647</v>
+        <v>1.32941190447192</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324233337588856</v>
+        <v>1.32422700966758</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.31940556928398</v>
+        <v>1.319396540802727</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319155076070814</v>
+        <v>1.319138648974822</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316356204671887</v>
+        <v>1.316342394529634</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320186386155806</v>
+        <v>1.320176286415243</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318825923940244</v>
+        <v>1.318834019648679</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.31337564836686</v>
+        <v>1.313394804969708</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311177989294404</v>
+        <v>1.311207854380869</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304439170305797</v>
+        <v>1.304475578848918</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294787979517937</v>
+        <v>1.294832247859005</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291382810577685</v>
+        <v>1.291434514463167</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295724973445872</v>
+        <v>1.295775452170041</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.313047321092832</v>
+        <v>1.313129088566638</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325831570622751</v>
+        <v>1.325917737010241</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.357044373623777</v>
+        <v>1.35709064976743</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374808846930044</v>
+        <v>1.374816916517421</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380229741818038</v>
+        <v>1.380225021477245</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389265095665935</v>
+        <v>1.389245828047661</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390828747387375</v>
+        <v>1.390800967852922</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389006043262869</v>
+        <v>1.388961640709786</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388380312082249</v>
+        <v>1.38832132179532</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.392458274833374</v>
+        <v>1.392360800341478</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.388714580736549</v>
+        <v>1.388609373916208</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.392276477073674</v>
+        <v>1.392162287363389</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375275886614138</v>
+        <v>1.375192605939891</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.370437601440419</v>
+        <v>1.370358459100567</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357523885898943</v>
+        <v>1.357476996731434</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339399384165972</v>
+        <v>1.33939558202674</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.33092783249946</v>
+        <v>1.330957539600105</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336794486978024</v>
+        <v>1.336814148021023</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.33868388913598</v>
+        <v>1.338696355438279</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339496016111812</v>
+        <v>1.339509470339922</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340748203543701</v>
+        <v>1.340751416966344</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340375705775096</v>
+        <v>1.340370969815382</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342395924648885</v>
+        <v>1.342384303247368</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341788484206146</v>
+        <v>1.341777086073776</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343179645765075</v>
+        <v>1.343170130615522</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341382331731068</v>
+        <v>1.342342946010012</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341094834671757</v>
+        <v>1.341552516568791</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.342971393227361</v>
+        <v>1.343542327642538</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.345405065583285</v>
+        <v>1.34604601848594</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.34670419334426</v>
+        <v>1.34780013303275</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.345983233902865</v>
+        <v>1.347349487078517</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.342928595260912</v>
+        <v>1.344453960531798</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.339627182403933</v>
+        <v>1.341155496799114</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.335457351344635</v>
+        <v>1.337333195464389</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.334935072260615</v>
+        <v>1.33742002271322</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.336717584846469</v>
+        <v>1.340075872946872</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.339133265342912</v>
+        <v>1.343506367692382</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.342387988274051</v>
+        <v>1.348174587769071</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.336024971613751</v>
+        <v>1.344461735269465</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.329223208318141</v>
+        <v>1.340735269845822</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.326452324072125</v>
+        <v>1.335099715411958</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366616985912965</v>
+        <v>1.366624325987863</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359091465607561</v>
+        <v>1.359104903740764</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356123623544332</v>
+        <v>1.356139768696776</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350227742837458</v>
+        <v>1.350251011885259</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347924244309702</v>
+        <v>1.347948524841818</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343745452048741</v>
+        <v>1.343770626947241</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339304312611872</v>
+        <v>1.339330025548444</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336845401895584</v>
+        <v>1.336871365452153</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339821189848696</v>
+        <v>1.339837779365114</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334082309586548</v>
+        <v>1.334080216443381</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.335000116004057</v>
+        <v>1.334997623347431</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332827728386466</v>
+        <v>1.3328248194098</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332467425020627</v>
+        <v>1.332457658688635</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329834237237931</v>
+        <v>1.329826214462274</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327994135029036</v>
+        <v>1.32798759696555</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331288813298013</v>
+        <v>1.331283680582624</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.32941190447192</v>
+        <v>1.329416861460025</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.32422700966758</v>
+        <v>1.324239477631545</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319396540802727</v>
+        <v>1.319414330749033</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319138648974822</v>
+        <v>1.319171030684599</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316342394529634</v>
+        <v>1.31636963261022</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320176286415243</v>
+        <v>1.320196220204571</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318834019648679</v>
+        <v>1.318818082640023</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313394804969708</v>
+        <v>1.31335706756041</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311207854380869</v>
+        <v>1.311149011253775</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304475578848918</v>
+        <v>1.30440383600025</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294832247859005</v>
+        <v>1.294745011356373</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291434514463167</v>
+        <v>1.291332618391509</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295775452170041</v>
+        <v>1.295675954470616</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.313129088566638</v>
+        <v>1.312967869027596</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325917737010241</v>
+        <v>1.325747844002377</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.35709064976743</v>
+        <v>1.356999376354302</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374816916517421</v>
+        <v>1.374800991319483</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380225021477245</v>
+        <v>1.380234289744046</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389245828047661</v>
+        <v>1.389283752039429</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390800967852922</v>
+        <v>1.390855641159377</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.388961640709786</v>
+        <v>1.389049077123389</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.38832132179532</v>
+        <v>1.388437509561634</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.392360800341478</v>
+        <v>1.392552943204451</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.388609373916208</v>
+        <v>1.388816789324928</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.392162287363389</v>
+        <v>1.392387440007604</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375192605939891</v>
+        <v>1.375356877743514</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.370358459100567</v>
+        <v>1.370514603544783</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357476996731434</v>
+        <v>1.357569567496669</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.33939558202674</v>
+        <v>1.339403131915363</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330957539600105</v>
+        <v>1.330898951544745</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336814148021023</v>
+        <v>1.336775373265695</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338696355438279</v>
+        <v>1.338671761464236</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339509470339922</v>
+        <v>1.33948291193397</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340751416966344</v>
+        <v>1.340745047506691</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340370969815382</v>
+        <v>1.340380263400939</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342384303247368</v>
+        <v>1.342407181311295</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341777086073776</v>
+        <v>1.34179953483341</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343170130615522</v>
+        <v>1.34318892513459</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.342342946010012</v>
+        <v>1.341397129412783</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341552516568791</v>
+        <v>1.341106807465956</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343542327642538</v>
+        <v>1.343285449250866</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.34604601848594</v>
+        <v>1.345702035944566</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.34780013303275</v>
+        <v>1.346895216917899</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.347349487078517</v>
+        <v>1.346154732184594</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.344453960531798</v>
+        <v>1.343107433795344</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.341155496799114</v>
+        <v>1.339791199377063</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.337333195464389</v>
+        <v>1.335637216197009</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.33742002271322</v>
+        <v>1.335026405534378</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.340075872946872</v>
+        <v>1.336634200982286</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.343506367692382</v>
+        <v>1.338560769398481</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.348174587769071</v>
+        <v>1.341499340219677</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.344461735269465</v>
+        <v>1.335256285866239</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.340735269845822</v>
+        <v>1.328614530435756</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.335099715411958</v>
+        <v>1.325547788548805</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B111"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366624325987863</v>
+        <v>1.366627838770723</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359104903740764</v>
+        <v>1.359111335721963</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356139768696776</v>
+        <v>1.356147498229053</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350251011885259</v>
+        <v>1.350262151552348</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347948524841818</v>
+        <v>1.347960148547393</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343770626947241</v>
+        <v>1.343782678602412</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339330025548444</v>
+        <v>1.339342334699496</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336871365452153</v>
+        <v>1.336883794650884</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339837779365114</v>
+        <v>1.339845730615108</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334080216443381</v>
+        <v>1.33407921901795</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334997623347431</v>
+        <v>1.334996434831285</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.3328248194098</v>
+        <v>1.332823431729434</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332457658688635</v>
+        <v>1.332452990205598</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329826214462274</v>
+        <v>1.329822377785547</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.32798759696555</v>
+        <v>1.327984468587545</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331283680582624</v>
+        <v>1.331281224371876</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329416861460025</v>
+        <v>1.329419227607033</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324239477631545</v>
+        <v>1.32424543802434</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319414330749033</v>
+        <v>1.319422836850162</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319171030684599</v>
+        <v>1.319186532897423</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.31636963261022</v>
+        <v>1.31638269394235</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320196220204571</v>
+        <v>1.320205798793741</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318818082640023</v>
+        <v>1.318810484038096</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.31335706756041</v>
+        <v>1.31333903707348</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311149011253775</v>
+        <v>1.311120881451372</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.30440383600025</v>
+        <v>1.304369529250998</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294745011356373</v>
+        <v>1.294703287140853</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291332618391509</v>
+        <v>1.291283872830873</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295675954470616</v>
+        <v>1.295628332998739</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312967869027596</v>
+        <v>1.312890635645899</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325747844002377</v>
+        <v>1.325666455234093</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356999376354302</v>
+        <v>1.356955605862256</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374800991319483</v>
+        <v>1.374793341439524</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380234289744046</v>
+        <v>1.380238674193575</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389283752039429</v>
+        <v>1.389301825568004</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390855641159377</v>
+        <v>1.390881690383598</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389049077123389</v>
+        <v>1.389090804126398</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388437509561634</v>
+        <v>1.388492994148556</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.392552943204451</v>
+        <v>1.392644924499321</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.388816789324928</v>
+        <v>1.388916125508497</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.392387440007604</v>
+        <v>1.392495310535181</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375356877743514</v>
+        <v>1.375435671999912</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.370514603544783</v>
+        <v>1.370589550467147</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357569567496669</v>
+        <v>1.357614086896546</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339403131915363</v>
+        <v>1.339406825400894</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330898951544745</v>
+        <v>1.330870862926447</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336775373265695</v>
+        <v>1.336756784481464</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338671761464236</v>
+        <v>1.338659958951625</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.33948291193397</v>
+        <v>1.339470144513775</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340745047506691</v>
+        <v>1.34074194790082</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340380263400939</v>
+        <v>1.340384652014855</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342407181311295</v>
+        <v>1.342418089988765</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.34179953483341</v>
+        <v>1.341810253456948</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.34318892513459</v>
+        <v>1.343197977036934</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341397129412783</v>
+        <v>1.341411539209656</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341106807465956</v>
+        <v>1.341118490590427</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343285449250866</v>
+        <v>1.343288420178406</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.345702035944566</v>
+        <v>1.345917638915551</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.346895216917899</v>
+        <v>1.347087694573423</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.346154732184594</v>
+        <v>1.346328942337993</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.343107433795344</v>
+        <v>1.343136342002886</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.339791199377063</v>
+        <v>1.339970736991489</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.335637216197009</v>
+        <v>1.335759724396081</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.335026405534378</v>
+        <v>1.335127346993539</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.336634200982286</v>
+        <v>1.336677224256603</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.338560769398481</v>
+        <v>1.338550191342885</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.341499340219677</v>
+        <v>1.341194128722131</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.335256285866239</v>
+        <v>1.335393344229422</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.328614530435756</v>
+        <v>1.329492219290471</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,15 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.325547788548805</v>
+        <v>1.327193721159121</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B112">
+        <v>1.333628172068563</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366627838770723</v>
+        <v>1.366624325987863</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359111335721963</v>
+        <v>1.359104903740764</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356147498229053</v>
+        <v>1.356139768696776</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350262151552348</v>
+        <v>1.350251011885259</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347960148547393</v>
+        <v>1.347948524841818</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343782678602412</v>
+        <v>1.343770626947241</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339342334699496</v>
+        <v>1.339330025548444</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336883794650884</v>
+        <v>1.336871365452153</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339845730615108</v>
+        <v>1.339837779365114</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.33407921901795</v>
+        <v>1.334080216443381</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334996434831285</v>
+        <v>1.334997623347431</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332823431729434</v>
+        <v>1.3328248194098</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332452990205598</v>
+        <v>1.332457658688635</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329822377785547</v>
+        <v>1.329826214462274</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327984468587545</v>
+        <v>1.32798759696555</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331281224371876</v>
+        <v>1.331283680582624</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329419227607033</v>
+        <v>1.329416861460025</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.32424543802434</v>
+        <v>1.324239477631545</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319422836850162</v>
+        <v>1.319414330749033</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319186532897423</v>
+        <v>1.319171030684599</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.31638269394235</v>
+        <v>1.31636963261022</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320205798793741</v>
+        <v>1.320196220204571</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318810484038096</v>
+        <v>1.318818082640023</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.31333903707348</v>
+        <v>1.31335706756041</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311120881451372</v>
+        <v>1.311149011253775</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304369529250998</v>
+        <v>1.30440383600025</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294703287140853</v>
+        <v>1.294745011356373</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291283872830873</v>
+        <v>1.291332618391509</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295628332998739</v>
+        <v>1.295675954470616</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312890635645899</v>
+        <v>1.312967869027596</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325666455234093</v>
+        <v>1.325747844002377</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356955605862256</v>
+        <v>1.356999376354302</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374793341439524</v>
+        <v>1.374800991319483</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380238674193575</v>
+        <v>1.380234289744046</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389301825568004</v>
+        <v>1.389283752039429</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390881690383598</v>
+        <v>1.390855641159377</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389090804126398</v>
+        <v>1.389049077123389</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388492994148556</v>
+        <v>1.388437509561634</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.392644924499321</v>
+        <v>1.392552943204451</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.388916125508497</v>
+        <v>1.388816789324928</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.392495310535181</v>
+        <v>1.392387440007604</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375435671999912</v>
+        <v>1.375356877743514</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.370589550467147</v>
+        <v>1.370514603544783</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357614086896546</v>
+        <v>1.357569567496669</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339406825400894</v>
+        <v>1.339403131915363</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330870862926447</v>
+        <v>1.330898951544745</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336756784481464</v>
+        <v>1.336775373265695</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338659958951625</v>
+        <v>1.338671761464236</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339470144513775</v>
+        <v>1.33948291193397</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.34074194790082</v>
+        <v>1.340745047506691</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340384652014855</v>
+        <v>1.340380263400939</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342418089988765</v>
+        <v>1.342407181311295</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341810253456948</v>
+        <v>1.34179953483341</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343197977036934</v>
+        <v>1.34318892513459</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341411539209656</v>
+        <v>1.34236642468433</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341118490590427</v>
+        <v>1.341573586021669</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343288420178406</v>
+        <v>1.343548403321452</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.345917638915551</v>
+        <v>1.34644742594713</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.347087694573423</v>
+        <v>1.34806720145486</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.346328942337993</v>
+        <v>1.347439652515788</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.343136342002886</v>
+        <v>1.344161857812954</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.339970736991489</v>
+        <v>1.34109049654527</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.335759724396081</v>
+        <v>1.337097144412917</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.335127346993539</v>
+        <v>1.336906126898434</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.336677224256603</v>
+        <v>1.339110872123816</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.338550191342885</v>
+        <v>1.341997640831298</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.341194128722131</v>
+        <v>1.345239093466641</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.335393344229422</v>
+        <v>1.341050286506476</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.329492219290471</v>
+        <v>1.336702230534931</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.327193721159121</v>
+        <v>1.329699866909416</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.333628172068563</v>
+        <v>1.328602112842854</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366624325987863</v>
+        <v>1.366631252621866</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359104903740764</v>
+        <v>1.359117587061645</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356139768696776</v>
+        <v>1.356155011838652</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350251011885259</v>
+        <v>1.350272979756389</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347948524841818</v>
+        <v>1.347971447136801</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343770626947241</v>
+        <v>1.343794393043751</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339330025548444</v>
+        <v>1.339354299387094</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336871365452153</v>
+        <v>1.336895876071588</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339837779365114</v>
+        <v>1.339853465311779</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334080216443381</v>
+        <v>1.334078252351556</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334997623347431</v>
+        <v>1.334995282522202</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.3328248194098</v>
+        <v>1.332822085912733</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332457658688635</v>
+        <v>1.332448456585805</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329826214462274</v>
+        <v>1.329818650924723</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.32798759696555</v>
+        <v>1.327981428677888</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331283680582624</v>
+        <v>1.331278837452272</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329416861460025</v>
+        <v>1.329421523300342</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324239477631545</v>
+        <v>1.324251226523185</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319414330749033</v>
+        <v>1.319431098572476</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319171030684599</v>
+        <v>1.31920160166924</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.31636963261022</v>
+        <v>1.316395403431637</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320196220204571</v>
+        <v>1.320215131643703</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318818082640023</v>
+        <v>1.318803117127461</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.31335706756041</v>
+        <v>1.313321532905142</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311149011253775</v>
+        <v>1.311093563303634</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.30440383600025</v>
+        <v>1.304336206033744</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294745011356373</v>
+        <v>1.29466275382299</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291332618391509</v>
+        <v>1.291236512489685</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295675954470616</v>
+        <v>1.295582050264802</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312967869027596</v>
+        <v>1.312815529522482</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325747844002377</v>
+        <v>1.325587307986936</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356999376354302</v>
+        <v>1.356913012831639</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374800991319483</v>
+        <v>1.37478588945285</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380234289744046</v>
+        <v>1.380242903513219</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389283752039429</v>
+        <v>1.389319342931187</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390855641159377</v>
+        <v>1.390906933780992</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389049077123389</v>
+        <v>1.389131282462586</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388437509561634</v>
+        <v>1.388546841108482</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.392552943204451</v>
+        <v>1.392734331145254</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.388816789324928</v>
+        <v>1.389012708200459</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.392387440007604</v>
+        <v>1.392600215695537</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375356877743514</v>
+        <v>1.375512357146654</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.370514603544783</v>
+        <v>1.37066252284777</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357569567496669</v>
+        <v>1.357657487266239</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339403131915363</v>
+        <v>1.33941046485507</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330898951544745</v>
+        <v>1.330843534644898</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336775373265695</v>
+        <v>1.33673869942116</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338671761464236</v>
+        <v>1.338648468823805</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.33948291193397</v>
+        <v>1.339457701211813</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340745047506691</v>
+        <v>1.340738903742544</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340380263400939</v>
+        <v>1.340388880323851</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342407181311295</v>
+        <v>1.342428666432541</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.34179953483341</v>
+        <v>1.3418206546775</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.34318892513459</v>
+        <v>1.343206809420607</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.34236642468433</v>
+        <v>1.341425576030487</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341573586021669</v>
+        <v>1.341129894098963</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343548403321452</v>
+        <v>1.343291366648027</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.34644742594713</v>
+        <v>1.346116874216765</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.34806720145486</v>
+        <v>1.347266223866932</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.347439652515788</v>
+        <v>1.346494561390646</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.344161857812954</v>
+        <v>1.343184462420588</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.34109049654527</v>
+        <v>1.340045930685137</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.337097144412917</v>
+        <v>1.335883672924878</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.336906126898434</v>
+        <v>1.33522960906492</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.339110872123816</v>
+        <v>1.336726059684795</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.341997640831298</v>
+        <v>1.338549547055043</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.345239093466641</v>
+        <v>1.340929600000273</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.341050286506476</v>
+        <v>1.335530448981041</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.336702230534931</v>
+        <v>1.330241242657025</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.329699866909416</v>
+        <v>1.328447798828913</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.328602112842854</v>
+        <v>1.333677187921574</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366631252621866</v>
+        <v>1.366627838770723</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359117587061645</v>
+        <v>1.359111335721963</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356155011838652</v>
+        <v>1.356147498229053</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350272979756389</v>
+        <v>1.350262151552348</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347971447136801</v>
+        <v>1.347960148547393</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343794393043751</v>
+        <v>1.343782678602412</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339354299387094</v>
+        <v>1.339342334699496</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336895876071588</v>
+        <v>1.336883794650884</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339853465311779</v>
+        <v>1.339845730615108</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334078252351556</v>
+        <v>1.33407921901795</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334995282522202</v>
+        <v>1.334996434831285</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332822085912733</v>
+        <v>1.332823431729434</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332448456585805</v>
+        <v>1.332452990205598</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329818650924723</v>
+        <v>1.329822377785547</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327981428677888</v>
+        <v>1.327984468587545</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331278837452272</v>
+        <v>1.331281224371876</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329421523300342</v>
+        <v>1.329419227607033</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324251226523185</v>
+        <v>1.32424543802434</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319431098572476</v>
+        <v>1.319422836850162</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.31920160166924</v>
+        <v>1.319186532897423</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316395403431637</v>
+        <v>1.31638269394235</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320215131643703</v>
+        <v>1.320205798793741</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318803117127461</v>
+        <v>1.318810484038096</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313321532905142</v>
+        <v>1.31333903707348</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311093563303634</v>
+        <v>1.311120881451372</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304336206033744</v>
+        <v>1.304369529250998</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.29466275382299</v>
+        <v>1.294703287140853</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291236512489685</v>
+        <v>1.291283872830873</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295582050264802</v>
+        <v>1.295628332998739</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312815529522482</v>
+        <v>1.312890635645899</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325587307986936</v>
+        <v>1.325666455234093</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356913012831639</v>
+        <v>1.356955605862256</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.37478588945285</v>
+        <v>1.374793341439524</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380242903513219</v>
+        <v>1.380238674193575</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389319342931187</v>
+        <v>1.389301825568004</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390906933780992</v>
+        <v>1.390881690383598</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389131282462586</v>
+        <v>1.389090804126398</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388546841108482</v>
+        <v>1.388492994148556</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.392734331145254</v>
+        <v>1.392644924499321</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389012708200459</v>
+        <v>1.388916125508497</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.392600215695537</v>
+        <v>1.392495310535181</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375512357146654</v>
+        <v>1.375435671999912</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.37066252284777</v>
+        <v>1.370589550467147</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357657487266239</v>
+        <v>1.357614086896546</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.33941046485507</v>
+        <v>1.339406825400894</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330843534644898</v>
+        <v>1.330870862926447</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.33673869942116</v>
+        <v>1.336756784481464</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338648468823805</v>
+        <v>1.338659958951625</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339457701211813</v>
+        <v>1.339470144513775</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340738903742544</v>
+        <v>1.34074194790082</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340388880323851</v>
+        <v>1.340384652014855</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342428666432541</v>
+        <v>1.342418089988765</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.3418206546775</v>
+        <v>1.341810253456948</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343206809420607</v>
+        <v>1.343197977036934</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341425576030487</v>
+        <v>1.34237771812539</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341129894098963</v>
+        <v>1.341583748758008</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343291366648027</v>
+        <v>1.343551397104688</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346116874216765</v>
+        <v>1.346594552035726</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.347266223866932</v>
+        <v>1.348150916528057</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.346494561390646</v>
+        <v>1.347441829423757</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.343184462420588</v>
+        <v>1.343968220400158</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.340045930685137</v>
+        <v>1.341079028121856</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.335883672924878</v>
+        <v>1.336899005852369</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.33522960906492</v>
+        <v>1.336566709011204</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.336726059684795</v>
+        <v>1.338554854228956</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.338549547055043</v>
+        <v>1.341189624116967</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.340929600000273</v>
+        <v>1.34377768616131</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.335530448981041</v>
+        <v>1.339387168426707</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.330241242657025</v>
+        <v>1.3347922468911</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.328447798828913</v>
+        <v>1.327414056908639</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.333677187921574</v>
+        <v>1.327689492014284</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366627838770723</v>
+        <v>1.366634571662362</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359111335721963</v>
+        <v>1.359123665263348</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356147498229053</v>
+        <v>1.3561623184461</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350262151552348</v>
+        <v>1.350283509375699</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347960148547393</v>
+        <v>1.347982434057824</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343782678602412</v>
+        <v>1.343805784224734</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339342334699496</v>
+        <v>1.339365933866569</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336883794650884</v>
+        <v>1.336907624104947</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339845730615108</v>
+        <v>1.339860992169067</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.33407921901795</v>
+        <v>1.334077315053018</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334996434831285</v>
+        <v>1.334994164799352</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332823431729434</v>
+        <v>1.332820780101302</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332452990205598</v>
+        <v>1.332444052075155</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329822377785547</v>
+        <v>1.329815029237526</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327984468587545</v>
+        <v>1.327978473537861</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331281224371876</v>
+        <v>1.331276516934355</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329419227607033</v>
+        <v>1.3294237516303</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.32424543802434</v>
+        <v>1.324256850444685</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319422836850162</v>
+        <v>1.319439126280918</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319186532897423</v>
+        <v>1.319216254915839</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.31638269394235</v>
+        <v>1.316407775061936</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320205798793741</v>
+        <v>1.320224227994115</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318810484038096</v>
+        <v>1.318795971552378</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.31333903707348</v>
+        <v>1.313304532425398</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311120881451372</v>
+        <v>1.311067022294448</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304369529250998</v>
+        <v>1.304303824795384</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294703287140853</v>
+        <v>1.29462336131789</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291283872830873</v>
+        <v>1.291190479375677</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295628332998739</v>
+        <v>1.295537050744221</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312890635645899</v>
+        <v>1.312742464174718</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325666455234093</v>
+        <v>1.3255103111377</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356955605862256</v>
+        <v>1.356871550544879</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374793341439524</v>
+        <v>1.374778627906739</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380238674193575</v>
+        <v>1.380246985505106</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389301825568004</v>
+        <v>1.389336329215694</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390881690383598</v>
+        <v>1.390931407763081</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389090804126398</v>
+        <v>1.389170566941256</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388492994148556</v>
+        <v>1.388599121388616</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.392644924499321</v>
+        <v>1.392821269404161</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.388916125508497</v>
+        <v>1.389106649866497</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.392495310535181</v>
+        <v>1.392702275688258</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375435671999912</v>
+        <v>1.375587016357407</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.370589550467147</v>
+        <v>1.3707335971938</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357614086896546</v>
+        <v>1.357699809698388</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339406825400894</v>
+        <v>1.339414050602365</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330870862926447</v>
+        <v>1.330816936391485</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336756784481464</v>
+        <v>1.33672109800047</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338659958951625</v>
+        <v>1.338637278959576</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339470144513775</v>
+        <v>1.339445570003079</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.34074194790082</v>
+        <v>1.340735914026882</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340384652014855</v>
+        <v>1.340392956468578</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342418089988765</v>
+        <v>1.342438925464398</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341810253456948</v>
+        <v>1.341830752259137</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343197977036934</v>
+        <v>1.343215429887712</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.34237771812539</v>
+        <v>1.341439254037052</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341583748758008</v>
+        <v>1.341141027604948</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343551397104688</v>
+        <v>1.343294287413458</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346594552035726</v>
+        <v>1.346272268135054</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.348150916528057</v>
+        <v>1.347396681065223</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.347441829423757</v>
+        <v>1.346609492375487</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.343968220400158</v>
+        <v>1.343247535252909</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.341079028121856</v>
+        <v>1.340090289908839</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.336899005852369</v>
+        <v>1.335938497286158</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.336566709011204</v>
+        <v>1.33523468719099</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.338554854228956</v>
+        <v>1.336663560142277</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.341189624116967</v>
+        <v>1.338428387275137</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.34377768616131</v>
+        <v>1.340545436729708</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.339387168426707</v>
+        <v>1.335475782260426</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.3347922468911</v>
+        <v>1.330629160434321</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.327414056908639</v>
+        <v>1.329078837984887</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.327689492014284</v>
+        <v>1.332711958600273</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366634571662362</v>
+        <v>1.366637799787543</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359123665263348</v>
+        <v>1.359129577420766</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.3561623184461</v>
+        <v>1.356169426487346</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350283509375699</v>
+        <v>1.350293752588488</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347982434057824</v>
+        <v>1.347993122026911</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343805784224734</v>
+        <v>1.343816865339713</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339365933866569</v>
+        <v>1.339377251617605</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336907624104947</v>
+        <v>1.336919052358726</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339860992169067</v>
+        <v>1.339868319440343</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334077315053018</v>
+        <v>1.334076405813309</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334994164799352</v>
+        <v>1.33499308013679</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332820780101302</v>
+        <v>1.332819512544742</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332444052075155</v>
+        <v>1.332439771241951</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329815029237526</v>
+        <v>1.329811508339392</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327978473537861</v>
+        <v>1.327975599672006</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331276516934355</v>
+        <v>1.331274260087017</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.3294237516303</v>
+        <v>1.329425915509647</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324256850444685</v>
+        <v>1.324262316696731</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319439126280918</v>
+        <v>1.319446929763354</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319216254915839</v>
+        <v>1.319230509579705</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316407775061936</v>
+        <v>1.316419822088182</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320224227994115</v>
+        <v>1.320233096632803</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318795971552378</v>
+        <v>1.318789037561176</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313304532425398</v>
+        <v>1.313288014278982</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311067022294448</v>
+        <v>1.311041225831555</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304303824795384</v>
+        <v>1.304272346283567</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.29462336131789</v>
+        <v>1.294585062300751</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291190479375677</v>
+        <v>1.291145718677291</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295537050744221</v>
+        <v>1.295493281933447</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312742464174718</v>
+        <v>1.31267135773389</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.3255103111377</v>
+        <v>1.325435378424576</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356871550544879</v>
+        <v>1.356831174714604</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374778627906739</v>
+        <v>1.374771549710405</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380246985505106</v>
+        <v>1.380250927469749</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389336329215694</v>
+        <v>1.389352808031843</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390931407763081</v>
+        <v>1.39095514660025</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389170566941256</v>
+        <v>1.389208709230965</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388599121388616</v>
+        <v>1.388649901921454</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.392821269404161</v>
+        <v>1.392905839788147</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389106649866497</v>
+        <v>1.389198056954102</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.392702275688258</v>
+        <v>1.392801604325861</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375587016357407</v>
+        <v>1.375659728510704</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.3707335971938</v>
+        <v>1.370802846138543</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357699809698388</v>
+        <v>1.357741093331125</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339414050602365</v>
+        <v>1.339417583046396</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330816936391485</v>
+        <v>1.330791039439033</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.33672109800047</v>
+        <v>1.336703961182449</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338637278959576</v>
+        <v>1.338626377850192</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339445570003079</v>
+        <v>1.339433739440846</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340735914026882</v>
+        <v>1.340732977733943</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340392956468578</v>
+        <v>1.340396888067472</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342438925464398</v>
+        <v>1.342448881043763</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341830752259137</v>
+        <v>1.341840559187889</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343215429887712</v>
+        <v>1.34322384571104</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341439254037052</v>
+        <v>1.341452586689856</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341141027604948</v>
+        <v>1.341151900303758</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343294287413458</v>
+        <v>1.343297181408339</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346272268135054</v>
+        <v>1.34658262820984</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.347396681065223</v>
+        <v>1.34769672152657</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.346609492375487</v>
+        <v>1.346920379616443</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.343247535252909</v>
+        <v>1.343604687672218</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.340090289908839</v>
+        <v>1.340455947194198</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.335938497286158</v>
+        <v>1.33637060845449</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.33523468719099</v>
+        <v>1.335689498577221</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.336663560142277</v>
+        <v>1.337103477426192</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.338428387275137</v>
+        <v>1.338854621455815</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.340545436729708</v>
+        <v>1.34082222448541</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.335475782260426</v>
+        <v>1.336204020036159</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.330629160434321</v>
+        <v>1.332006260824054</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.329078837984887</v>
+        <v>1.330987871507559</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.332711958600273</v>
+        <v>1.335514297673324</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366637799787543</v>
+        <v>1.36664094068225</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359129577420766</v>
+        <v>1.359135330245341</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356169426487346</v>
+        <v>1.356176343946214</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350293752588488</v>
+        <v>1.350303720919782</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347993122026911</v>
+        <v>1.348003523078211</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343816865339713</v>
+        <v>1.343827648874832</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339377251617605</v>
+        <v>1.339388265396266</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336919052358726</v>
+        <v>1.336930173710287</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339868319440343</v>
+        <v>1.339875454948393</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334076405813309</v>
+        <v>1.33407552339961</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.33499308013679</v>
+        <v>1.334992027096632</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332819512544742</v>
+        <v>1.332818281592945</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332439771241951</v>
+        <v>1.332435608954657</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329811508339392</v>
+        <v>1.329808084085842</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327975599672006</v>
+        <v>1.327972803774358</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331274260087017</v>
+        <v>1.331272064326811</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329425915509647</v>
+        <v>1.329428017686049</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324262316696731</v>
+        <v>1.324267631806597</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319446929763354</v>
+        <v>1.319454518270128</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319230509579705</v>
+        <v>1.319244381695183</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316419822088182</v>
+        <v>1.316431557083107</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320233096632803</v>
+        <v>1.320241745922643</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318789037561176</v>
+        <v>1.318782305963087</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313288014278982</v>
+        <v>1.313271958297123</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311041225831555</v>
+        <v>1.311016143114736</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304272346283567</v>
+        <v>1.304241733390101</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294585062300751</v>
+        <v>1.294547812019944</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291145718677291</v>
+        <v>1.291102178549319</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295493281933447</v>
+        <v>1.295450694147753</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.31267135773389</v>
+        <v>1.312602132642291</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325435378424576</v>
+        <v>1.325362428127999</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356831174714604</v>
+        <v>1.356791843328259</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374771549710405</v>
+        <v>1.374764648113865</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380250927469749</v>
+        <v>1.380254736244974</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389352808031843</v>
+        <v>1.389368801619951</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.39095514660025</v>
+        <v>1.390978182575634</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389208709230965</v>
+        <v>1.389245758080028</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388649901921454</v>
+        <v>1.388699245903228</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.392905839788147</v>
+        <v>1.392988137442012</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389198056954102</v>
+        <v>1.389287030288193</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.392801604325861</v>
+        <v>1.392898309450968</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375659728510704</v>
+        <v>1.375730568462207</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.370802846138543</v>
+        <v>1.370870338681631</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357741093331125</v>
+        <v>1.357781375460529</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339417583046396</v>
+        <v>1.339421062658612</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330791039439033</v>
+        <v>1.330765816540552</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336703961182449</v>
+        <v>1.336687270910559</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338626377850192</v>
+        <v>1.338615754561615</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339433739440846</v>
+        <v>1.33942219862297</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340732977733943</v>
+        <v>1.340730093834549</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340396888067472</v>
+        <v>1.340400682256904</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342448881043763</v>
+        <v>1.342458546329133</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341840559187889</v>
+        <v>1.341850087725559</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.34322384571104</v>
+        <v>1.343232063850318</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341452586689856</v>
+        <v>1.341465586790596</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341151900303758</v>
+        <v>1.34116252099394</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343297181408339</v>
+        <v>1.343300047727438</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.34658262820984</v>
+        <v>1.346872452311764</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.34769672152657</v>
+        <v>1.347992015537189</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.346920379616443</v>
+        <v>1.347263902338471</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.343604687672218</v>
+        <v>1.344114036582792</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.340455947194198</v>
+        <v>1.341067766349918</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.33637060845449</v>
+        <v>1.337130832665212</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.335689498577221</v>
+        <v>1.336568878529004</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.337103477426192</v>
+        <v>1.338049632543387</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.338854621455815</v>
+        <v>1.339870271116659</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.34082222448541</v>
+        <v>1.341949681978524</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.336204020036159</v>
+        <v>1.33796557747436</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.332006260824054</v>
+        <v>1.334693051595912</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.330987871507559</v>
+        <v>1.334547965579314</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.335514297673324</v>
+        <v>1.34133278459475</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.36664094068225</v>
+        <v>1.366643997834856</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359135330245341</v>
+        <v>1.359140930091674</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356176343946214</v>
+        <v>1.356183078384289</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350303720919782</v>
+        <v>1.350313425284621</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348003523078211</v>
+        <v>1.348013648608714</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343827648874832</v>
+        <v>1.343838146654901</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339388265396266</v>
+        <v>1.339398987282898</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336930173710287</v>
+        <v>1.33694100035493</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339875454948393</v>
+        <v>1.339882406113086</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.33407552339961</v>
+        <v>1.334074666649875</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334992027096632</v>
+        <v>1.334991004322824</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332818281592945</v>
+        <v>1.332817085689031</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332435608954657</v>
+        <v>1.332431560361468</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329808084085842</v>
+        <v>1.329804752556294</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327972803774358</v>
+        <v>1.32797008271578</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331272064326811</v>
+        <v>1.331269927208106</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329428017686049</v>
+        <v>1.329430060753609</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324267631806597</v>
+        <v>1.324272801946758</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319454518270128</v>
+        <v>1.319461900550409</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319244381695183</v>
+        <v>1.319257886448483</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316431557083107</v>
+        <v>1.316442991980427</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320241745922643</v>
+        <v>1.320250183826573</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318782305963087</v>
+        <v>1.318775768088709</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313271958297123</v>
+        <v>1.313256345416513</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311016143114736</v>
+        <v>1.31099174501465</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304241733390101</v>
+        <v>1.304211951006966</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294547812019944</v>
+        <v>1.294511568125021</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291102178549319</v>
+        <v>1.291059809915612</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295450694147753</v>
+        <v>1.295409240335017</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312602132642291</v>
+        <v>1.312534715373822</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325362428127999</v>
+        <v>1.325291382776255</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356791843328259</v>
+        <v>1.356753516504447</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374764648113865</v>
+        <v>1.374757916688216</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380254736244974</v>
+        <v>1.380258418241332</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389368801619951</v>
+        <v>1.389384330947711</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390978182575634</v>
+        <v>1.391000546126013</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389245758080028</v>
+        <v>1.389281759518784</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388699245903228</v>
+        <v>1.388747213049605</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.392988137442012</v>
+        <v>1.393068252495713</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389287030288193</v>
+        <v>1.389373665436065</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.392898309450968</v>
+        <v>1.392992493321311</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375730568462207</v>
+        <v>1.375799607296638</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.370870338681631</v>
+        <v>1.370936140411705</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357781375460529</v>
+        <v>1.357820691645611</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339421062658612</v>
+        <v>1.339424489968319</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330765816540552</v>
+        <v>1.330741241835623</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336687270910559</v>
+        <v>1.336671010046733</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338615754561615</v>
+        <v>1.338605398699506</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.33942219862297</v>
+        <v>1.339410937160491</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340730093834549</v>
+        <v>1.34072726129503</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340400682256904</v>
+        <v>1.340404345727755</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342458546329133</v>
+        <v>1.342467933734355</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341850087725559</v>
+        <v>1.341859349459147</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343232063850318</v>
+        <v>1.343240090967639</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341465586790596</v>
+        <v>1.341478266521607</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.34116252099394</v>
+        <v>1.341172898097234</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343300047727438</v>
+        <v>1.343302885609819</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346872452311764</v>
+        <v>1.347144950146819</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.347992015537189</v>
+        <v>1.348263570166667</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.347263902338471</v>
+        <v>1.347578032379625</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.344114036582792</v>
+        <v>1.344573022490303</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.341067766349918</v>
+        <v>1.34162414220889</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.337130832665212</v>
+        <v>1.33782468411487</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.336568878529004</v>
+        <v>1.337369678521496</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.338049632543387</v>
+        <v>1.338911077521841</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.339870271116659</v>
+        <v>1.340794997402738</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.341949681978524</v>
+        <v>1.342972184494043</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.33796557747436</v>
+        <v>1.339544397672564</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.334693051595912</v>
+        <v>1.337027547631765</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.334547965579314</v>
+        <v>1.337513163924991</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.34133278459475</v>
+        <v>1.345257719897527</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B112"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366643997834856</v>
+        <v>1.366634571662362</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359140930091674</v>
+        <v>1.359123665263348</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356183078384289</v>
+        <v>1.3561623184461</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350313425284621</v>
+        <v>1.350283509375699</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348013648608714</v>
+        <v>1.347982434057824</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343838146654901</v>
+        <v>1.343805784224734</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339398987282898</v>
+        <v>1.339365933866569</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.33694100035493</v>
+        <v>1.336907624104947</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339882406113086</v>
+        <v>1.339860992169067</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334074666649875</v>
+        <v>1.334077315053018</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334991004322824</v>
+        <v>1.334994164799352</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332817085689031</v>
+        <v>1.332820780101302</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332431560361468</v>
+        <v>1.332444052075155</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329804752556294</v>
+        <v>1.329815029237526</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.32797008271578</v>
+        <v>1.327978473537861</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331269927208106</v>
+        <v>1.331276516934355</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329430060753609</v>
+        <v>1.3294237516303</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324272801946758</v>
+        <v>1.324256850444685</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319461900550409</v>
+        <v>1.319439126280918</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319257886448483</v>
+        <v>1.319216254915839</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316442991980427</v>
+        <v>1.316407775061936</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320250183826573</v>
+        <v>1.320224227994115</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318775768088709</v>
+        <v>1.318795971552378</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313256345416513</v>
+        <v>1.313304532425398</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.31099174501465</v>
+        <v>1.311067022294448</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304211951006966</v>
+        <v>1.304303824795384</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294511568125021</v>
+        <v>1.29462336131789</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291059809915612</v>
+        <v>1.291190479375677</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295409240335017</v>
+        <v>1.295537050744221</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312534715373822</v>
+        <v>1.312742464174718</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325291382776255</v>
+        <v>1.3255103111377</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356753516504447</v>
+        <v>1.356871550544879</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374757916688216</v>
+        <v>1.374778627906739</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380258418241332</v>
+        <v>1.380246985505106</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389384330947711</v>
+        <v>1.389336329215694</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391000546126013</v>
+        <v>1.390931407763081</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389281759518784</v>
+        <v>1.389170566941256</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388747213049605</v>
+        <v>1.388599121388616</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.393068252495713</v>
+        <v>1.392821269404161</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389373665436065</v>
+        <v>1.389106649866497</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.392992493321311</v>
+        <v>1.392702275688258</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375799607296638</v>
+        <v>1.375587016357407</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.370936140411705</v>
+        <v>1.3707335971938</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357820691645611</v>
+        <v>1.357699809698388</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339424489968319</v>
+        <v>1.339414050602365</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330741241835623</v>
+        <v>1.330816936391485</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336671010046733</v>
+        <v>1.33672109800047</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338605398699506</v>
+        <v>1.338637278959576</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339410937160491</v>
+        <v>1.339445570003079</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.34072726129503</v>
+        <v>1.340735914026882</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340404345727755</v>
+        <v>1.340392956468578</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342467933734355</v>
+        <v>1.342438925464398</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341859349459147</v>
+        <v>1.341830752259137</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343240090967639</v>
+        <v>1.343215429887712</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341478266521607</v>
+        <v>1.342399467379759</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341172898097234</v>
+        <v>1.34160337126723</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343302885609819</v>
+        <v>1.343557291878127</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347144950146819</v>
+        <v>1.346899625551769</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.348263570166667</v>
+        <v>1.348592216881358</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.347578032379625</v>
+        <v>1.347902412120041</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.344573022490303</v>
+        <v>1.344523641597718</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.34162414220889</v>
+        <v>1.341452526105721</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.33782468411487</v>
+        <v>1.337297073969812</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.337369678521496</v>
+        <v>1.336788841732534</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.338911077521841</v>
+        <v>1.338498355851271</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.340794997402738</v>
+        <v>1.340790014274438</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.342972184494043</v>
+        <v>1.342801129314567</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.339544397672564</v>
+        <v>1.338251336105595</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.337027547631765</v>
+        <v>1.335153388946406</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.337513163924991</v>
+        <v>1.329297233597454</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,15 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.345257719897527</v>
+        <v>1.332703966066748</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B113">
+        <v>1.340136344958385</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366634571662362</v>
+        <v>1.366646974550194</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359123665263348</v>
+        <v>1.359146382980921</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.3561623184461</v>
+        <v>1.356189636968454</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350283509375699</v>
+        <v>1.350322876027875</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347982434057824</v>
+        <v>1.348023509419856</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343805784224734</v>
+        <v>1.343848369886597</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339365933866569</v>
+        <v>1.339409428726275</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336907624104947</v>
+        <v>1.336951543850448</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339860992169067</v>
+        <v>1.339889179976947</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334077315053018</v>
+        <v>1.334073834467844</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334994164799352</v>
+        <v>1.334990010535417</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332820780101302</v>
+        <v>1.332815923362878</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332444052075155</v>
+        <v>1.332427620871518</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329815029237526</v>
+        <v>1.329801510039159</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327978473537861</v>
+        <v>1.327967433532305</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331276516934355</v>
+        <v>1.331267846414025</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.3294237516303</v>
+        <v>1.329432047163418</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324256850444685</v>
+        <v>1.324277832958638</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319439126280918</v>
+        <v>1.319469084885631</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319216254915839</v>
+        <v>1.319271038232991</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316407775061936</v>
+        <v>1.31645413811479</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320224227994115</v>
+        <v>1.320258417930894</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318795971552378</v>
+        <v>1.318769415753757</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313304532425398</v>
+        <v>1.313241157604817</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311067022294448</v>
+        <v>1.31096800396135</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304303824795384</v>
+        <v>1.304182965893725</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.29462336131789</v>
+        <v>1.294476290508304</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291190479375677</v>
+        <v>1.291018566287262</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295537050744221</v>
+        <v>1.295368875904032</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312742464174718</v>
+        <v>1.312469036175989</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.3255103111377</v>
+        <v>1.325222168873641</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356871550544879</v>
+        <v>1.356716156359979</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374778627906739</v>
+        <v>1.374751349307218</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380246985505106</v>
+        <v>1.380261979474349</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389336329215694</v>
+        <v>1.389399415799429</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390931407763081</v>
+        <v>1.391022265970962</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389170566941256</v>
+        <v>1.389316757045373</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388599121388616</v>
+        <v>1.388793859830781</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.392821269404161</v>
+        <v>1.39314627038949</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389106649866497</v>
+        <v>1.389458053044379</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.392702275688258</v>
+        <v>1.393084252965438</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375587016357407</v>
+        <v>1.375866912561113</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.3707335971938</v>
+        <v>1.371000313713062</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357699809698388</v>
+        <v>1.357859075806374</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339414050602365</v>
+        <v>1.339427865553879</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330816936391485</v>
+        <v>1.330717290763759</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.33672109800047</v>
+        <v>1.336655162314058</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338637278959576</v>
+        <v>1.338595300376691</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339445570003079</v>
+        <v>1.339399945148307</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340735914026882</v>
+        <v>1.34072447908133</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340392956468578</v>
+        <v>1.340407884758772</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342438925464398</v>
+        <v>1.342477054980244</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341830752259137</v>
+        <v>1.341868355346314</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343215429887712</v>
+        <v>1.34324793344211</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.342399467379759</v>
+        <v>1.341490637482535</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.34160337126723</v>
+        <v>1.341183039677498</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343557291878127</v>
+        <v>1.343305694423756</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346899625551769</v>
+        <v>1.347138504112397</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.348592216881358</v>
+        <v>1.348436792680977</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.347902412120041</v>
+        <v>1.347843072336942</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.344523641597718</v>
+        <v>1.344959211553864</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.341452526105721</v>
+        <v>1.342107937202846</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.337297073969812</v>
+        <v>1.338394446244854</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.336788841732534</v>
+        <v>1.338054898248518</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.338498355851271</v>
+        <v>1.339654514179768</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.340790014274438</v>
+        <v>1.341590217043933</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.342801129314567</v>
+        <v>1.343859125730599</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.338251336105595</v>
+        <v>1.340913782001214</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.335153388946406</v>
+        <v>1.339013301043044</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.329297233597454</v>
+        <v>1.339907792554316</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.332703966066748</v>
+        <v>1.347730565734145</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.340136344958385</v>
+        <v>1.35747677976063</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366646974550194</v>
+        <v>1.366637799787543</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359146382980921</v>
+        <v>1.359129577420766</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356189636968454</v>
+        <v>1.356169426487346</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350322876027875</v>
+        <v>1.350293752588488</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348023509419856</v>
+        <v>1.347993122026911</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343848369886597</v>
+        <v>1.343816865339713</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339409428726275</v>
+        <v>1.339377251617605</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336951543850448</v>
+        <v>1.336919052358726</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339889179976947</v>
+        <v>1.339868319440343</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334073834467844</v>
+        <v>1.334076405813309</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334990010535417</v>
+        <v>1.33499308013679</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332815923362878</v>
+        <v>1.332819512544742</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332427620871518</v>
+        <v>1.332439771241951</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329801510039159</v>
+        <v>1.329811508339392</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327967433532305</v>
+        <v>1.327975599672006</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331267846414025</v>
+        <v>1.331274260087017</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329432047163418</v>
+        <v>1.329425915509647</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324277832958638</v>
+        <v>1.324262316696731</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319469084885631</v>
+        <v>1.319446929763354</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319271038232991</v>
+        <v>1.319230509579705</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.31645413811479</v>
+        <v>1.316419822088182</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320258417930894</v>
+        <v>1.320233096632803</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318769415753757</v>
+        <v>1.318789037561176</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313241157604817</v>
+        <v>1.313288014278982</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.31096800396135</v>
+        <v>1.311041225831555</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304182965893725</v>
+        <v>1.304272346283567</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294476290508304</v>
+        <v>1.294585062300751</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291018566287262</v>
+        <v>1.291145718677291</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295368875904032</v>
+        <v>1.295493281933447</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312469036175989</v>
+        <v>1.31267135773389</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325222168873641</v>
+        <v>1.325435378424576</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356716156359979</v>
+        <v>1.356831174714604</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374751349307218</v>
+        <v>1.374771549710405</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380261979474349</v>
+        <v>1.380250927469749</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389399415799429</v>
+        <v>1.389352808031843</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391022265970962</v>
+        <v>1.39095514660025</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389316757045373</v>
+        <v>1.389208709230965</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388793859830781</v>
+        <v>1.388649901921454</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.39314627038949</v>
+        <v>1.392905839788147</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389458053044379</v>
+        <v>1.389198056954102</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.393084252965438</v>
+        <v>1.392801604325861</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375866912561113</v>
+        <v>1.375659728510704</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371000313713062</v>
+        <v>1.370802846138543</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357859075806374</v>
+        <v>1.357741093331125</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339427865553879</v>
+        <v>1.339417583046396</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330717290763759</v>
+        <v>1.330791039439033</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336655162314058</v>
+        <v>1.336703961182449</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338595300376691</v>
+        <v>1.338626377850192</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339399945148307</v>
+        <v>1.339433739440846</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.34072447908133</v>
+        <v>1.340732977733943</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340407884758772</v>
+        <v>1.340396888067472</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342477054980244</v>
+        <v>1.342448881043763</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341868355346314</v>
+        <v>1.341840559187889</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.34324793344211</v>
+        <v>1.34322384571104</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341490637482535</v>
+        <v>1.34240994332754</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341183039677498</v>
+        <v>1.341612846436086</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343305694423756</v>
+        <v>1.343560191468837</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347138504112397</v>
+        <v>1.346895432042909</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.348436792680977</v>
+        <v>1.348871652784788</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.347843072336942</v>
+        <v>1.348257389689159</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.344959211553864</v>
+        <v>1.34499241228565</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.342107937202846</v>
+        <v>1.341864501122711</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.338394446244854</v>
+        <v>1.337679814881462</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.338054898248518</v>
+        <v>1.337125411447655</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.339654514179768</v>
+        <v>1.338736457855622</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.341590217043933</v>
+        <v>1.340917778838289</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.343859125730599</v>
+        <v>1.342856852713245</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.340913782001214</v>
+        <v>1.338243266423958</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.339013301043044</v>
+        <v>1.336256762730656</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.339907792554316</v>
+        <v>1.331368196581149</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.347730565734145</v>
+        <v>1.335400232931623</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.35747677976063</v>
+        <v>1.34326020475601</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366637799787543</v>
+        <v>1.366649873961463</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359129577420766</v>
+        <v>1.359151694622382</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356169426487346</v>
+        <v>1.35619602649631</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350293752588488</v>
+        <v>1.350332082960988</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.347993122026911</v>
+        <v>1.348033115755908</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343816865339713</v>
+        <v>1.343858329198317</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339377251617605</v>
+        <v>1.339419600584327</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336919052358726</v>
+        <v>1.336961815158235</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339868319440343</v>
+        <v>1.339895783228801</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334076405813309</v>
+        <v>1.334073025818477</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.33499308013679</v>
+        <v>1.33498904452533</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332819512544742</v>
+        <v>1.33281479322518</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332439771241951</v>
+        <v>1.332423786137592</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329811508339392</v>
+        <v>1.329798353018118</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327975599672006</v>
+        <v>1.327964853414376</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331274260087017</v>
+        <v>1.331265819748088</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329425915509647</v>
+        <v>1.329433979233249</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324262316696731</v>
+        <v>1.324282730374475</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319446929763354</v>
+        <v>1.319476079120292</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319230509579705</v>
+        <v>1.319283850700311</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316419822088182</v>
+        <v>1.316465006258788</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320233096632803</v>
+        <v>1.320266455466991</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318789037561176</v>
+        <v>1.318763241225771</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313288014278982</v>
+        <v>1.313226377792102</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311041225831555</v>
+        <v>1.310944893841591</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304272346283567</v>
+        <v>1.304154746555323</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294585062300751</v>
+        <v>1.29444194115881</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291145718677291</v>
+        <v>1.290978403594881</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295493281933447</v>
+        <v>1.295329558566055</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.31267135773389</v>
+        <v>1.312405028831418</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325435378424576</v>
+        <v>1.325154716649182</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356831174714604</v>
+        <v>1.356679726886713</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374771549710405</v>
+        <v>1.374744940130098</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380250927469749</v>
+        <v>1.380265425593946</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389352808031843</v>
+        <v>1.389414074857883</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.39095514660025</v>
+        <v>1.391043369231383</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389208709230965</v>
+        <v>1.389350791796558</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388649901921454</v>
+        <v>1.388839239687857</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.392905839788147</v>
+        <v>1.3932222721741</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389198056954102</v>
+        <v>1.389540279150673</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.392801604325861</v>
+        <v>1.39317368051166</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375659728510704</v>
+        <v>1.375932548481459</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.370802846138543</v>
+        <v>1.371062917957577</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357741093331125</v>
+        <v>1.357896560315476</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339417583046396</v>
+        <v>1.339431190034953</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330791039439033</v>
+        <v>1.330693939984142</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336703961182449</v>
+        <v>1.336639712243658</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338626377850192</v>
+        <v>1.338585450182943</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339433739440846</v>
+        <v>1.339389213137814</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340732977733943</v>
+        <v>1.340721746162506</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340396888067472</v>
+        <v>1.340411305247031</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342448881043763</v>
+        <v>1.34248592114199</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341840559187889</v>
+        <v>1.341877115757249</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.34322384571104</v>
+        <v>1.343255597383745</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.34240994332754</v>
+        <v>1.341502710724451</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341612846436086</v>
+        <v>1.341192953458588</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343560191468837</v>
+        <v>1.343308473653198</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346895432042909</v>
+        <v>1.347132258775306</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.348871652784788</v>
+        <v>1.348699055875099</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.348257389689159</v>
+        <v>1.348200476747129</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.34499241228565</v>
+        <v>1.345471399324415</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.341864501122711</v>
+        <v>1.34279753699452</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.337679814881462</v>
+        <v>1.339181971257221</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.337125411447655</v>
+        <v>1.338969308681221</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.338736457855622</v>
+        <v>1.340649499648744</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.340917778838289</v>
+        <v>1.342661869749381</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.342856852713245</v>
+        <v>1.345049973557389</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.338243266423958</v>
+        <v>1.342658576624473</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.336256762730656</v>
+        <v>1.341430031862376</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.331368196581149</v>
+        <v>1.342818057894552</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.335400232931623</v>
+        <v>1.35110363411472</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.34326020475601</v>
+        <v>1.363568806809251</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366649873961463</v>
+        <v>1.36664094068225</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359151694622382</v>
+        <v>1.359135330245341</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.35619602649631</v>
+        <v>1.356176343946214</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350332082960988</v>
+        <v>1.350303720919782</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348033115755908</v>
+        <v>1.348003523078211</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343858329198317</v>
+        <v>1.343827648874832</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339419600584327</v>
+        <v>1.339388265396266</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336961815158235</v>
+        <v>1.336930173710287</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339895783228801</v>
+        <v>1.339875454948393</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334073025818477</v>
+        <v>1.33407552339961</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.33498904452533</v>
+        <v>1.334992027096632</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.33281479322518</v>
+        <v>1.332818281592945</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332423786137592</v>
+        <v>1.332435608954657</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329798353018118</v>
+        <v>1.329808084085842</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327964853414376</v>
+        <v>1.327972803774358</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331265819748088</v>
+        <v>1.331272064326811</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329433979233249</v>
+        <v>1.329428017686049</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324282730374475</v>
+        <v>1.324267631806597</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319476079120292</v>
+        <v>1.319454518270128</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319283850700311</v>
+        <v>1.319244381695183</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316465006258788</v>
+        <v>1.316431557083107</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320266455466991</v>
+        <v>1.320241745922643</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318763241225771</v>
+        <v>1.318782305963087</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313226377792102</v>
+        <v>1.313271958297123</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310944893841591</v>
+        <v>1.311016143114736</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304154746555323</v>
+        <v>1.304241733390101</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.29444194115881</v>
+        <v>1.294547812019944</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290978403594881</v>
+        <v>1.291102178549319</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295329558566055</v>
+        <v>1.295450694147753</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312405028831418</v>
+        <v>1.312602132642291</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325154716649182</v>
+        <v>1.325362428127999</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356679726886713</v>
+        <v>1.356791843328259</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374744940130098</v>
+        <v>1.374764648113865</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380265425593946</v>
+        <v>1.380254736244974</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389414074857883</v>
+        <v>1.389368801619951</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391043369231383</v>
+        <v>1.390978182575634</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389350791796558</v>
+        <v>1.389245758080028</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388839239687857</v>
+        <v>1.388699245903228</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.3932222721741</v>
+        <v>1.392988137442012</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389540279150673</v>
+        <v>1.389287030288193</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.39317368051166</v>
+        <v>1.392898309450968</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375932548481459</v>
+        <v>1.375730568462207</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371062917957577</v>
+        <v>1.370870338681631</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357896560315476</v>
+        <v>1.357781375460529</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339431190034953</v>
+        <v>1.339421062658612</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330693939984142</v>
+        <v>1.330765816540552</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336639712243658</v>
+        <v>1.336687270910559</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338585450182943</v>
+        <v>1.338615754561615</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339389213137814</v>
+        <v>1.33942219862297</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340721746162506</v>
+        <v>1.340730093834549</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340411305247031</v>
+        <v>1.340400682256904</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.34248592114199</v>
+        <v>1.342458546329133</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341877115757249</v>
+        <v>1.341850087725559</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343255597383745</v>
+        <v>1.343232063850318</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341502710724451</v>
+        <v>1.342420166129151</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341192953458588</v>
+        <v>1.341622107286456</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343308473653198</v>
+        <v>1.343563058485605</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347132258775306</v>
+        <v>1.346891382531462</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.348699055875099</v>
+        <v>1.349462919075689</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.348200476747129</v>
+        <v>1.348983002042403</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.345471399324415</v>
+        <v>1.345900547134408</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.34279753699452</v>
+        <v>1.342716658304864</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.339181971257221</v>
+        <v>1.339063389009248</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.338969308681221</v>
+        <v>1.338194504115821</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.340649499648744</v>
+        <v>1.339798401771673</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.342661869749381</v>
+        <v>1.341978634746762</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.345049973557389</v>
+        <v>1.343974752124776</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.342658576624473</v>
+        <v>1.33973198007176</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.341430031862376</v>
+        <v>1.338679171251244</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.342818057894552</v>
+        <v>1.335131423883176</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.35110363411472</v>
+        <v>1.340774404234806</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.363568806809251</v>
+        <v>1.352331856720612</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.36664094068225</v>
+        <v>1.366652699041232</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359135330245341</v>
+        <v>1.35915687043343</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356176343946214</v>
+        <v>1.35620225341965</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350303720919782</v>
+        <v>1.350341055395906</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348003523078211</v>
+        <v>1.348042477339431</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343827648874832</v>
+        <v>1.343868034676999</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339388265396266</v>
+        <v>1.33942951316176</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336930173710287</v>
+        <v>1.336971824681254</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339875454948393</v>
+        <v>1.339902222225675</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.33407552339961</v>
+        <v>1.334072239723759</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334992027096632</v>
+        <v>1.334988105149524</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332818281592945</v>
+        <v>1.332813693961983</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332435608954657</v>
+        <v>1.332420052040183</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329808084085842</v>
+        <v>1.329795278159454</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327972803774358</v>
+        <v>1.327962339696934</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331272064326811</v>
+        <v>1.331263845126494</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329428017686049</v>
+        <v>1.329435859156482</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324267631806597</v>
+        <v>1.324287499437482</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319454518270128</v>
+        <v>1.319482890690366</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319244381695183</v>
+        <v>1.319296336807415</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316431557083107</v>
+        <v>1.316475606657258</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320241745922643</v>
+        <v>1.32027430333159</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318782305963087</v>
+        <v>1.31875723719353</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313271958297123</v>
+        <v>1.313211989807656</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.311016143114736</v>
+        <v>1.310922389904113</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304241733390101</v>
+        <v>1.304127263129331</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294547812019944</v>
+        <v>1.29440848402741</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.291102178549319</v>
+        <v>1.290939280033721</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295450694147753</v>
+        <v>1.295291248188418</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312602132642291</v>
+        <v>1.312342630437183</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325362428127999</v>
+        <v>1.325088959824129</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356791843328259</v>
+        <v>1.356644193837357</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374764648113865</v>
+        <v>1.37473868358547</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380254736244974</v>
+        <v>1.3802687619113</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389368801619951</v>
+        <v>1.389428325779522</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.390978182575634</v>
+        <v>1.391063881538408</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389245758080028</v>
+        <v>1.389383902704961</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388699245903228</v>
+        <v>1.388883403232222</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.392988137442012</v>
+        <v>1.393296334788343</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389287030288193</v>
+        <v>1.389620425471578</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.392898309450968</v>
+        <v>1.393260863492563</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375730568462207</v>
+        <v>1.37599657616292</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.370870338681631</v>
+        <v>1.371124009683113</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357781375460529</v>
+        <v>1.357933176083939</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339421062658612</v>
+        <v>1.339434464065656</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330765816540552</v>
+        <v>1.330671167301209</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336687270910559</v>
+        <v>1.336624645125451</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338615754561615</v>
+        <v>1.338575839156854</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.33942219862297</v>
+        <v>1.339378732111326</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340730093834549</v>
+        <v>1.340719061513697</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340400682256904</v>
+        <v>1.340414612735777</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342458546329133</v>
+        <v>1.342494542692755</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341850087725559</v>
+        <v>1.341885640513246</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343232063850318</v>
+        <v>1.343263088646636</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.342420166129151</v>
+        <v>1.341514496781628</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341622107286456</v>
+        <v>1.341202646841268</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343563058485605</v>
+        <v>1.343311222885621</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346891382531462</v>
+        <v>1.34712620540041</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.349462919075689</v>
+        <v>1.349250658548365</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.348983002042403</v>
+        <v>1.348887135959505</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.345900547134408</v>
+        <v>1.346389013078627</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.342716658304864</v>
+        <v>1.343814529000361</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.339063389009248</v>
+        <v>1.340408582294739</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.338194504115821</v>
+        <v>1.34038375393725</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.339798401771673</v>
+        <v>1.342196932640273</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.341978634746762</v>
+        <v>1.344349730236515</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.343974752124776</v>
+        <v>1.346933234960109</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.33973198007176</v>
+        <v>1.345282060045236</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.338679171251244</v>
+        <v>1.344949018736086</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.335131423883176</v>
+        <v>1.347111521447923</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.340774404234806</v>
+        <v>1.356692660605127</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.352331856720612</v>
+        <v>1.374484889048056</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366652699041232</v>
+        <v>1.366655452611601</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.35915687043343</v>
+        <v>1.35916191555793</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.35620225341965</v>
+        <v>1.356208323866166</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350341055395906</v>
+        <v>1.350349802176463</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348042477339431</v>
+        <v>1.348051603404069</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343868034676999</v>
+        <v>1.343877495902156</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.33942951316176</v>
+        <v>1.33943917624484</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336971824681254</v>
+        <v>1.336981582299145</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339902222225675</v>
+        <v>1.339908503013085</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334072239723759</v>
+        <v>1.334071475258843</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334988105149524</v>
+        <v>1.33498719132657</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332813693961983</v>
+        <v>1.332812624329662</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332420052040183</v>
+        <v>1.332416414672792</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329795278159454</v>
+        <v>1.329792282300366</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327962339696934</v>
+        <v>1.327959889850241</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331263845126494</v>
+        <v>1.331261920570991</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329435859156482</v>
+        <v>1.329437689010318</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324287499437482</v>
+        <v>1.324292145120451</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319482890690366</v>
+        <v>1.31948952664951</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319296336807415</v>
+        <v>1.319308508860242</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316475606657258</v>
+        <v>1.316485949059116</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.32027430333159</v>
+        <v>1.320281968105655</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.31875723719353</v>
+        <v>1.318751396738894</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313211989807656</v>
+        <v>1.313197978321706</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310922389904113</v>
+        <v>1.310900468672219</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304127263129331</v>
+        <v>1.304100487281793</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.29440848402741</v>
+        <v>1.29437588490224</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290939280033721</v>
+        <v>1.290901155920502</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295291248188418</v>
+        <v>1.295253906659135</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312342630437183</v>
+        <v>1.312281781200439</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325088959824129</v>
+        <v>1.32502483539662</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356644193837357</v>
+        <v>1.356609524619493</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.37473868358547</v>
+        <v>1.374732574356306</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.3802687619113</v>
+        <v>1.380271993423411</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389428325779522</v>
+        <v>1.389442185263609</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391063881538408</v>
+        <v>1.391083827133589</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389383902704961</v>
+        <v>1.389416126643975</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388883403232222</v>
+        <v>1.388926398429467</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.393296334788343</v>
+        <v>1.39336853131585</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389620425471578</v>
+        <v>1.389698569669771</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.393260863492563</v>
+        <v>1.393345885127163</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.37599657616292</v>
+        <v>1.376059053776573</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371124009683113</v>
+        <v>1.37118364275949</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357933176083939</v>
+        <v>1.357968952641355</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339434464065656</v>
+        <v>1.33943768832852</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330671167301209</v>
+        <v>1.330648951595589</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336624645125451</v>
+        <v>1.33660994696243</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338575839156854</v>
+        <v>1.338566458759667</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339378732111326</v>
+        <v>1.339368493458169</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340719061513697</v>
+        <v>1.340716424118628</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340414612735777</v>
+        <v>1.340417812439925</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342494542692755</v>
+        <v>1.342502929543789</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341885640513246</v>
+        <v>1.34189393892231</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343263088646636</v>
+        <v>1.343270412841438</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341514496781628</v>
+        <v>1.341526005701147</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341202646841268</v>
+        <v>1.341212126919174</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343311222885621</v>
+        <v>1.343313941801108</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.34712620540041</v>
+        <v>1.347120335733038</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.349250658548365</v>
+        <v>1.349854130360837</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.348887135959505</v>
+        <v>1.349638082149413</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.346389013078627</v>
+        <v>1.347346071590555</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.343814529000361</v>
+        <v>1.344847464414226</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.340408582294739</v>
+        <v>1.341663931738755</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.34038375393725</v>
+        <v>1.341817889923219</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.342196932640273</v>
+        <v>1.343760934674303</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.344349730236515</v>
+        <v>1.346052648796346</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.346933234960109</v>
+        <v>1.348828777794707</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.345282060045236</v>
+        <v>1.347870446502659</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.344949018736086</v>
+        <v>1.348339176306079</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.347111521447923</v>
+        <v>1.351154305940739</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.356692660605127</v>
+        <v>1.36161919634698</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.374484889048056</v>
+        <v>1.381059678519543</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366655452611601</v>
+        <v>1.366658137353605</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.35916191555793</v>
+        <v>1.359166834883284</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356208323866166</v>
+        <v>1.356214243659548</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350349802176463</v>
+        <v>1.350358331707416</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348051603404069</v>
+        <v>1.348060502724879</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343877495902156</v>
+        <v>1.343886721977382</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.33943917624484</v>
+        <v>1.339448599133578</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336981582299145</v>
+        <v>1.33699109740071</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339908503013085</v>
+        <v>1.33991463134386</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334071475258843</v>
+        <v>1.334070731548502</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.33498719132657</v>
+        <v>1.334986302032573</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332812624329662</v>
+        <v>1.332811583150288</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332416414672792</v>
+        <v>1.332412870328347</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329792282300366</v>
+        <v>1.329789362438166</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327959889850241</v>
+        <v>1.327957501471409</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331261920570991</v>
+        <v>1.331260044202281</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329437689010318</v>
+        <v>1.329439470763353</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324292145120451</v>
+        <v>1.324296672142939</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.31948952664951</v>
+        <v>1.319495993693301</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319308508860242</v>
+        <v>1.319320378554062</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316485949059116</v>
+        <v>1.316496042746915</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320281968105655</v>
+        <v>1.320289456072059</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318751396738894</v>
+        <v>1.318745713310875</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313197978321706</v>
+        <v>1.313184328791604</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310900468672219</v>
+        <v>1.31087910786297</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304100487281793</v>
+        <v>1.304074392110927</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.29437588490224</v>
+        <v>1.294344111293454</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290901155920502</v>
+        <v>1.290863993560932</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295253906659135</v>
+        <v>1.295217497761573</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312281781200439</v>
+        <v>1.31222242424894</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.32502483539662</v>
+        <v>1.324962283442049</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356609524619493</v>
+        <v>1.356575688197127</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374732574356306</v>
+        <v>1.37472660736587</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380271993423411</v>
+        <v>1.380275124835584</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389442185263609</v>
+        <v>1.389455669115886</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391083827133589</v>
+        <v>1.39110322896114</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389416126643975</v>
+        <v>1.389447498561436</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388926398429467</v>
+        <v>1.388968270769193</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.39336853131585</v>
+        <v>1.393438931222921</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389698569669771</v>
+        <v>1.389774785601424</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.393345885127163</v>
+        <v>1.393428824582586</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376059053776573</v>
+        <v>1.376120036732584</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.37118364275949</v>
+        <v>1.371241868543013</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357968952641355</v>
+        <v>1.358003918210971</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.33943768832852</v>
+        <v>1.339440863529182</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330648951595589</v>
+        <v>1.330627272759951</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.33660994696243</v>
+        <v>1.336595604428201</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338566458759667</v>
+        <v>1.338557300850883</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339368493458169</v>
+        <v>1.339358488952322</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340716424118628</v>
+        <v>1.340713832971723</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340417812439925</v>
+        <v>1.340420909269408</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342502929543789</v>
+        <v>1.342511091081412</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.34189393892231</v>
+        <v>1.34190201981204</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343270412841438</v>
+        <v>1.343277575347202</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341526005701147</v>
+        <v>1.34153724707051</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341212126919174</v>
+        <v>1.341221400493922</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343313941801108</v>
+        <v>1.343316630162547</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347120335733038</v>
+        <v>1.34711464196738</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.349854130360837</v>
+        <v>1.350421676306627</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.349638082149413</v>
+        <v>1.350337959495498</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.347346071590555</v>
+        <v>1.34820056213662</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.344847464414226</v>
+        <v>1.345653221358802</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.341663931738755</v>
+        <v>1.342599168912853</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.341817889923219</v>
+        <v>1.342800748901145</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.343760934674303</v>
+        <v>1.344739364698878</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.346052648796346</v>
+        <v>1.347027496695079</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.348828777794707</v>
+        <v>1.349815299893851</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.347870446502659</v>
+        <v>1.349003835098832</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.348339176306079</v>
+        <v>1.349756953360012</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.351154305940739</v>
+        <v>1.352729519872831</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.36161919634698</v>
+        <v>1.363801372558946</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.381059678519543</v>
+        <v>1.381758022623972</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366658137353605</v>
+        <v>1.366660755815913</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359166834883284</v>
+        <v>1.359171633056216</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356214243659548</v>
+        <v>1.356220018338096</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350358331707416</v>
+        <v>1.350366651981356</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348060502724879</v>
+        <v>1.348069183646455</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343886721977382</v>
+        <v>1.343895721559532</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339448599133578</v>
+        <v>1.33945779067156</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.33699109740071</v>
+        <v>1.337000378914019</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.33991463134386</v>
+        <v>1.33992061269562</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334070731548502</v>
+        <v>1.334070007763863</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334986302032573</v>
+        <v>1.334985436297403</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332811583150288</v>
+        <v>1.33281056930736</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332412870328347</v>
+        <v>1.332409415486649</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329789362438166</v>
+        <v>1.329786515720283</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327957501471409</v>
+        <v>1.327955172276544</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331260044202281</v>
+        <v>1.331258214233914</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329439470763353</v>
+        <v>1.329441206282568</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324296672142939</v>
+        <v>1.324301084987167</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319495993693301</v>
+        <v>1.319502298181641</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319320378554062</v>
+        <v>1.319331957010866</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316496042746915</v>
+        <v>1.316505896564327</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320289456072059</v>
+        <v>1.320296773232074</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318745713310875</v>
+        <v>1.318740180701713</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313184328791604</v>
+        <v>1.313171027412073</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.31087910786297</v>
+        <v>1.310858286312449</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304074392110927</v>
+        <v>1.304048952058003</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294344111293454</v>
+        <v>1.294313132326523</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290863993560932</v>
+        <v>1.290827757127011</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295217497761573</v>
+        <v>1.295181987058317</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.31222242424894</v>
+        <v>1.312164505455232</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324962283442049</v>
+        <v>1.324901246927817</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356575688197127</v>
+        <v>1.356542654999172</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.37472660736587</v>
+        <v>1.374720777764555</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380275124835584</v>
+        <v>1.380278160582034</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389455669115886</v>
+        <v>1.389468792307237</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.39110322896114</v>
+        <v>1.391122108752991</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389447498561436</v>
+        <v>1.38947805160306</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388968270769193</v>
+        <v>1.389009063421982</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.393438931222921</v>
+        <v>1.393507600579011</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389774785601424</v>
+        <v>1.389849143545835</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.393428824582586</v>
+        <v>1.393509757217</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376120036732584</v>
+        <v>1.376179577841397</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371241868543013</v>
+        <v>1.371298736020467</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358003918210971</v>
+        <v>1.358038099780036</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339440863529182</v>
+        <v>1.339443990391697</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330627272759951</v>
+        <v>1.330606111639371</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336595604428201</v>
+        <v>1.336581604827495</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338557300850883</v>
+        <v>1.338548357665529</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339358488952322</v>
+        <v>1.339348710731479</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340713832971723</v>
+        <v>1.340711287079869</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340420909269408</v>
+        <v>1.340423907850613</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342511091081412</v>
+        <v>1.342519036201113</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.34190201981204</v>
+        <v>1.34190989156003</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343277575347202</v>
+        <v>1.343284581322578</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.34153724707051</v>
+        <v>1.341548230043409</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341221400493922</v>
+        <v>1.341230474089369</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343316630162547</v>
+        <v>1.343319287806806</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.34711464196738</v>
+        <v>1.347109116717271</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350421676306627</v>
+        <v>1.350852344673426</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.350337959495498</v>
+        <v>1.350864759002451</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.34820056213662</v>
+        <v>1.348885860578338</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.345653221358802</v>
+        <v>1.346295689550147</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.342599168912853</v>
+        <v>1.343277348216336</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342800748901145</v>
+        <v>1.343491379011739</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.344739364698878</v>
+        <v>1.345399364163381</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.347027496695079</v>
+        <v>1.347657989409496</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.349815299893851</v>
+        <v>1.350420996028985</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.349003835098832</v>
+        <v>1.349640024115114</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.349756953360012</v>
+        <v>1.350518317580747</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.352729519872831</v>
+        <v>1.353478720369846</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.363801372558946</v>
+        <v>1.364877952265888</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.381758022623972</v>
+        <v>1.380780937372625</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366660755815913</v>
+        <v>1.366649873961463</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359171633056216</v>
+        <v>1.359151694622382</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356220018338096</v>
+        <v>1.35619602649631</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350366651981356</v>
+        <v>1.350332082960988</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348069183646455</v>
+        <v>1.348033115755908</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343895721559532</v>
+        <v>1.343858329198317</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.33945779067156</v>
+        <v>1.339419600584327</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337000378914019</v>
+        <v>1.336961815158235</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.33992061269562</v>
+        <v>1.339895783228801</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334070007763863</v>
+        <v>1.334073025818477</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334985436297403</v>
+        <v>1.33498904452533</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.33281056930736</v>
+        <v>1.33281479322518</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332409415486649</v>
+        <v>1.332423786137592</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329786515720283</v>
+        <v>1.329798353018118</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327955172276544</v>
+        <v>1.327964853414376</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331258214233914</v>
+        <v>1.331265819748088</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329441206282568</v>
+        <v>1.329433979233249</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324301084987167</v>
+        <v>1.324282730374475</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319502298181641</v>
+        <v>1.319476079120292</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319331957010866</v>
+        <v>1.319283850700311</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316505896564327</v>
+        <v>1.316465006258788</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320296773232074</v>
+        <v>1.320266455466991</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318740180701713</v>
+        <v>1.318763241225771</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313171027412073</v>
+        <v>1.313226377792102</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310858286312449</v>
+        <v>1.310944893841591</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304048952058003</v>
+        <v>1.304154746555323</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294313132326523</v>
+        <v>1.29444194115881</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290827757127011</v>
+        <v>1.290978403594881</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295181987058317</v>
+        <v>1.295329558566055</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312164505455232</v>
+        <v>1.312405028831418</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324901246927817</v>
+        <v>1.325154716649182</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356542654999172</v>
+        <v>1.356679726886713</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374720777764555</v>
+        <v>1.374744940130098</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380278160582034</v>
+        <v>1.380265425593946</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389468792307237</v>
+        <v>1.389414074857883</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391122108752991</v>
+        <v>1.391043369231383</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.38947805160306</v>
+        <v>1.389350791796558</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389009063421982</v>
+        <v>1.388839239687857</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.393507600579011</v>
+        <v>1.3932222721741</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389849143545835</v>
+        <v>1.389540279150673</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.393509757217</v>
+        <v>1.39317368051166</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376179577841397</v>
+        <v>1.375932548481459</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371298736020467</v>
+        <v>1.371062917957577</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358038099780036</v>
+        <v>1.357896560315476</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339443990391697</v>
+        <v>1.339431190034953</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330606111639371</v>
+        <v>1.330693939984142</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336581604827495</v>
+        <v>1.336639712243658</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338548357665529</v>
+        <v>1.338585450182943</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339348710731479</v>
+        <v>1.339389213137814</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340711287079869</v>
+        <v>1.340721746162506</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340423907850613</v>
+        <v>1.340411305247031</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342519036201113</v>
+        <v>1.34248592114199</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.34190989156003</v>
+        <v>1.341877115757249</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343284581322578</v>
+        <v>1.343255597383745</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341548230043409</v>
+        <v>1.342449402964035</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341230474089369</v>
+        <v>1.341648671853447</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343319287806806</v>
+        <v>1.343571460715927</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347109116717271</v>
+        <v>1.346880032451431</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350852344673426</v>
+        <v>1.350581524633061</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.350864759002451</v>
+        <v>1.350890543516748</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.348885860578338</v>
+        <v>1.348348539740354</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.346295689550147</v>
+        <v>1.345254907363829</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.343277348216336</v>
+        <v>1.342091007143304</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.343491379011739</v>
+        <v>1.341496026673482</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.345399364163381</v>
+        <v>1.343057587206082</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.347657989409496</v>
+        <v>1.34523804140006</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.350420996028985</v>
+        <v>1.347416224036582</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.349640024115114</v>
+        <v>1.34441284460549</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.350518317580747</v>
+        <v>1.344460391720916</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.353478720369846</v>
+        <v>1.344464047573962</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.364877952265888</v>
+        <v>1.351993491318773</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,15 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.380780937372625</v>
+        <v>1.363674817026689</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B114">
+        <v>1.371054187582347</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366649873961463</v>
+        <v>1.366663310422902</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359151694622382</v>
+        <v>1.359176314497407</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.35619602649631</v>
+        <v>1.356225653171991</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350332082960988</v>
+        <v>1.350374770603663</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348033115755908</v>
+        <v>1.348077654108993</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343858329198317</v>
+        <v>1.343904502885791</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339419600584327</v>
+        <v>1.339466759273597</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336961815158235</v>
+        <v>1.337009435334318</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339895783228801</v>
+        <v>1.339926452287014</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334073025818477</v>
+        <v>1.334069303119385</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.33498904452533</v>
+        <v>1.334984593201227</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.33281479322518</v>
+        <v>1.332809581741864</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332423786137592</v>
+        <v>1.332406046802751</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329798353018118</v>
+        <v>1.329783739435004</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327964853414376</v>
+        <v>1.327952900093476</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331265819748088</v>
+        <v>1.331256428966621</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329433979233249</v>
+        <v>1.32944289733979</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324282730374475</v>
+        <v>1.324305387912728</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319476079120292</v>
+        <v>1.319508446159508</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319283850700311</v>
+        <v>1.319343254814055</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316465006258788</v>
+        <v>1.316515518941707</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320266455466991</v>
+        <v>1.320303925320809</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318763241225771</v>
+        <v>1.318734793024805</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313226377792102</v>
+        <v>1.313158061069183</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310944893841591</v>
+        <v>1.310837983906544</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304154746555323</v>
+        <v>1.304024142824768</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.29444194115881</v>
+        <v>1.294282918643352</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290978403594881</v>
+        <v>1.290792412543266</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295329558566055</v>
+        <v>1.295147341783444</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312405028831418</v>
+        <v>1.31210797327336</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325154716649182</v>
+        <v>1.324841671541291</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356679726886713</v>
+        <v>1.356510396834284</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374744940130098</v>
+        <v>1.374715080917555</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380265425593946</v>
+        <v>1.380281104844804</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389414074857883</v>
+        <v>1.389481569027818</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391043369231383</v>
+        <v>1.391140487107264</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389350791796558</v>
+        <v>1.389507817226565</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388839239687857</v>
+        <v>1.389048817384609</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.3932222721741</v>
+        <v>1.393574602261333</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389540279150673</v>
+        <v>1.389921710418668</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.39317368051166</v>
+        <v>1.393588754805309</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.375932548481459</v>
+        <v>1.376237727463814</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371062917957577</v>
+        <v>1.371354291943384</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357896560315476</v>
+        <v>1.358071523165727</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339431190034953</v>
+        <v>1.339447069654413</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330693939984142</v>
+        <v>1.330585449975844</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336639712243658</v>
+        <v>1.33656793605943</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338585450182943</v>
+        <v>1.338539621792948</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339389213137814</v>
+        <v>1.339339151277453</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340721746162506</v>
+        <v>1.34070878546387</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340411305247031</v>
+        <v>1.340426812546061</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.34248592114199</v>
+        <v>1.342526773339045</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341877115757249</v>
+        <v>1.341917562122004</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343255597383745</v>
+        <v>1.343291435716437</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.342449402964035</v>
+        <v>1.341558963363801</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341648671853447</v>
+        <v>1.341239353965109</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343571460715927</v>
+        <v>1.343321914636799</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346880032451431</v>
+        <v>1.347103752989185</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350581524633061</v>
+        <v>1.350834772119139</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.350890543516748</v>
+        <v>1.351305222968209</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.348348539740354</v>
+        <v>1.349428242299603</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.345254907363829</v>
+        <v>1.346929701224788</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.342091007143304</v>
+        <v>1.344138658236681</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.341496026673482</v>
+        <v>1.344249086242598</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.343057587206082</v>
+        <v>1.346108351919618</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.34523804140006</v>
+        <v>1.348322061735253</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.347416224036582</v>
+        <v>1.351070371384404</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.34441284460549</v>
+        <v>1.350491640750452</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.344460391720916</v>
+        <v>1.351507303597715</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.344464047573962</v>
+        <v>1.354504862859436</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.351993491318773</v>
+        <v>1.365242804168965</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.363674817026689</v>
+        <v>1.378874557327932</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.371054187582347</v>
+        <v>1.368263031182447</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366663310422902</v>
+        <v>1.366652699041232</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359176314497407</v>
+        <v>1.35915687043343</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356225653171991</v>
+        <v>1.35620225341965</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350374770603663</v>
+        <v>1.350341055395906</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348077654108993</v>
+        <v>1.348042477339431</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343904502885791</v>
+        <v>1.343868034676999</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339466759273597</v>
+        <v>1.33942951316176</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337009435334318</v>
+        <v>1.336971824681254</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339926452287014</v>
+        <v>1.339902222225675</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334069303119385</v>
+        <v>1.334072239723759</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334984593201227</v>
+        <v>1.334988105149524</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332809581741864</v>
+        <v>1.332813693961983</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332406046802751</v>
+        <v>1.332420052040183</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329783739435004</v>
+        <v>1.329795278159454</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327952900093476</v>
+        <v>1.327962339696934</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331256428966621</v>
+        <v>1.331263845126494</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.32944289733979</v>
+        <v>1.329435859156482</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324305387912728</v>
+        <v>1.324287499437482</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319508446159508</v>
+        <v>1.319482890690366</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319343254814055</v>
+        <v>1.319296336807415</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316515518941707</v>
+        <v>1.316475606657258</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320303925320809</v>
+        <v>1.32027430333159</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318734793024805</v>
+        <v>1.31875723719353</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313158061069183</v>
+        <v>1.313211989807656</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310837983906544</v>
+        <v>1.310922389904113</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304024142824768</v>
+        <v>1.304127263129331</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294282918643352</v>
+        <v>1.29440848402741</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290792412543266</v>
+        <v>1.290939280033721</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295147341783444</v>
+        <v>1.295291248188418</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.31210797327336</v>
+        <v>1.312342630437183</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324841671541291</v>
+        <v>1.325088959824129</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356510396834284</v>
+        <v>1.356644193837357</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374715080917555</v>
+        <v>1.37473868358547</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380281104844804</v>
+        <v>1.3802687619113</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389481569027818</v>
+        <v>1.389428325779522</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391140487107264</v>
+        <v>1.391063881538408</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389507817226565</v>
+        <v>1.389383902704961</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389048817384609</v>
+        <v>1.388883403232222</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.393574602261333</v>
+        <v>1.393296334788343</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389921710418668</v>
+        <v>1.389620425471578</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.393588754805309</v>
+        <v>1.393260863492563</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376237727463814</v>
+        <v>1.37599657616292</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371354291943384</v>
+        <v>1.371124009683113</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358071523165727</v>
+        <v>1.357933176083939</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339447069654413</v>
+        <v>1.339434464065656</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330585449975844</v>
+        <v>1.330671167301209</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.33656793605943</v>
+        <v>1.336624645125451</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338539621792948</v>
+        <v>1.338575839156854</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339339151277453</v>
+        <v>1.339378732111326</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.34070878546387</v>
+        <v>1.340719061513697</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340426812546061</v>
+        <v>1.340414612735777</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342526773339045</v>
+        <v>1.342494542692755</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341917562122004</v>
+        <v>1.341885640513246</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343291435716437</v>
+        <v>1.343263088646636</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341558963363801</v>
+        <v>1.34245869853465</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341239353965109</v>
+        <v>1.341657142002707</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343321914636799</v>
+        <v>1.34357419452195</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347103752989185</v>
+        <v>1.346876495265821</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350834772119139</v>
+        <v>1.350566615372728</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351305222968209</v>
+        <v>1.351346996464516</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.349428242299603</v>
+        <v>1.348978449295191</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.346929701224788</v>
+        <v>1.346009728648512</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.344138658236681</v>
+        <v>1.343099913303663</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.344249086242598</v>
+        <v>1.342566495703835</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.346108351919618</v>
+        <v>1.344072540399831</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.348322061735253</v>
+        <v>1.346230897622704</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.351070371384404</v>
+        <v>1.348450980189367</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.350491640750452</v>
+        <v>1.345886741748282</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.351507303597715</v>
+        <v>1.346250192708611</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.354504862859436</v>
+        <v>1.346777705991968</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.365242804168965</v>
+        <v>1.354299851720285</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.378874557327932</v>
+        <v>1.364967667415822</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.368263031182447</v>
+        <v>1.370043406630141</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366652699041232</v>
+        <v>1.366665803482142</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.35915687043343</v>
+        <v>1.359180883415069</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.35620225341965</v>
+        <v>1.356231153179321</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350341055395906</v>
+        <v>1.350382694815664</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348042477339431</v>
+        <v>1.348085921672489</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343868034676999</v>
+        <v>1.343913073798794</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.33942951316176</v>
+        <v>1.339475512951393</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.336971824681254</v>
+        <v>1.337018274749941</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339902222225675</v>
+        <v>1.339932155092828</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334072239723759</v>
+        <v>1.334068616870082</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334988105149524</v>
+        <v>1.334983771871303</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332813693961983</v>
+        <v>1.332808619448627</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332420052040183</v>
+        <v>1.332402761096194</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329795278159454</v>
+        <v>1.329781031002895</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327962339696934</v>
+        <v>1.327950682855014</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331263845126494</v>
+        <v>1.33125468678307</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329435859156482</v>
+        <v>1.329444545617661</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324287499437482</v>
+        <v>1.324309584970226</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319482890690366</v>
+        <v>1.319514443376189</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319296336807415</v>
+        <v>1.319354282040628</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316475606657258</v>
+        <v>1.316524917919894</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.32027430333159</v>
+        <v>1.32031091782165</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.31875723719353</v>
+        <v>1.318729544694295</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313211989807656</v>
+        <v>1.313145417297712</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310922389904113</v>
+        <v>1.310818181516812</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.304127263129331</v>
+        <v>1.303999941296882</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.29440848402741</v>
+        <v>1.294253442310554</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290939280033721</v>
+        <v>1.2907579273812</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295291248188418</v>
+        <v>1.295113530742532</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312342630437183</v>
+        <v>1.312052778587072</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.325088959824129</v>
+        <v>1.324783505529862</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356644193837357</v>
+        <v>1.356478886811555</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.37473868358547</v>
+        <v>1.374709512393308</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.3802687619113</v>
+        <v>1.380283961571126</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389428325779522</v>
+        <v>1.389494012737043</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391063881538408</v>
+        <v>1.391158383560773</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389383902704961</v>
+        <v>1.389536825307246</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.388883403232222</v>
+        <v>1.389087571614547</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.393296334788343</v>
+        <v>1.393639996144876</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389620425471578</v>
+        <v>1.389992549970182</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.393260863492563</v>
+        <v>1.393665885749047</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.37599657616292</v>
+        <v>1.376294533650834</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371124009683113</v>
+        <v>1.37140858095335</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.357933176083939</v>
+        <v>1.358104213076983</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339434464065656</v>
+        <v>1.33945010206635</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330671167301209</v>
+        <v>1.330565270356609</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336624645125451</v>
+        <v>1.336554586583291</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338575839156854</v>
+        <v>1.338531086156992</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339378732111326</v>
+        <v>1.339329803397794</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340719061513697</v>
+        <v>1.340706327159653</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340414612735777</v>
+        <v>1.340429627472493</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342494542692755</v>
+        <v>1.342534310501144</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341885640513246</v>
+        <v>1.341925039057884</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343263088646636</v>
+        <v>1.343298143277925</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.34245869853465</v>
+        <v>1.341569455388403</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341657142002707</v>
+        <v>1.341248046129223</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.34357419452195</v>
+        <v>1.343324510614341</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.346876495265821</v>
+        <v>1.34709854415723</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350566615372728</v>
+        <v>1.350817643079397</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351346996464516</v>
+        <v>1.351701789525126</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.348978449295191</v>
+        <v>1.349919887098007</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.346009728648512</v>
+        <v>1.347505134703088</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.343099913303663</v>
+        <v>1.344863475268675</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.342566495703835</v>
+        <v>1.344849338284679</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.344072540399831</v>
+        <v>1.346673385542321</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.346230897622704</v>
+        <v>1.348849758422382</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.348450980189367</v>
+        <v>1.351583624267451</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.345886741748282</v>
+        <v>1.351176979803101</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.346250192708611</v>
+        <v>1.352273854267205</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.346777705991968</v>
+        <v>1.355265816601457</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.354299851720285</v>
+        <v>1.365331648986587</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.364967667415822</v>
+        <v>1.377056609076334</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.370043406630141</v>
+        <v>1.366671663459111</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366665803482142</v>
+        <v>1.366668237191342</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359180883415069</v>
+        <v>1.359185343817562</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356231153179321</v>
+        <v>1.35623652314097</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350382694815664</v>
+        <v>1.350390431516156</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348085921672489</v>
+        <v>1.348093993539222</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343913073798794</v>
+        <v>1.343921441769962</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339475512951393</v>
+        <v>1.339484059337395</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337018274749941</v>
+        <v>1.337026904866375</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339932155092828</v>
+        <v>1.339937725858043</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334068616870082</v>
+        <v>1.33406794830895</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334983771871303</v>
+        <v>1.334982971479011</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332808619448627</v>
+        <v>1.33280768147295</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332402761096194</v>
+        <v>1.332399555341031</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329781031002895</v>
+        <v>1.329778387968845</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327950682855014</v>
+        <v>1.327948518592676</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.33125468678307</v>
+        <v>1.331252986142983</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329444545617661</v>
+        <v>1.329446152715171</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324309584970226</v>
+        <v>1.32431368001392</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319514443376189</v>
+        <v>1.319520295303117</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319354282040628</v>
+        <v>1.319365048291104</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316524917919894</v>
+        <v>1.316534101172395</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.32031091782165</v>
+        <v>1.320317755979786</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318729544694295</v>
+        <v>1.318724430406204</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313145417297712</v>
+        <v>1.313133084241626</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310818181516812</v>
+        <v>1.310798860940958</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303999941296882</v>
+        <v>1.303976325472854</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294253442310554</v>
+        <v>1.294224676734279</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.2907579273812</v>
+        <v>1.290724270761247</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295113530742532</v>
+        <v>1.29508052421973</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.312052778587072</v>
+        <v>1.311998874568594</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324783505529862</v>
+        <v>1.32472669955215</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356478886811555</v>
+        <v>1.356448099266597</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374709512393308</v>
+        <v>1.374704067952666</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380283961571126</v>
+        <v>1.380286734489398</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389494012737043</v>
+        <v>1.389506136209798</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391158383560773</v>
+        <v>1.391175816656059</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389536825307246</v>
+        <v>1.389565104235774</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389087571614547</v>
+        <v>1.389125363154628</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.393639996144876</v>
+        <v>1.39370383927905</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.389992549970182</v>
+        <v>1.39006172296964</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.393665885749047</v>
+        <v>1.393741215271727</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376294533650834</v>
+        <v>1.37635004227407</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.37140858095335</v>
+        <v>1.371461645699027</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358104213076983</v>
+        <v>1.358136193172526</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.33945010206635</v>
+        <v>1.339453088384012</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330565270356609</v>
+        <v>1.330545556165995</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336554586583291</v>
+        <v>1.336541545386638</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338531086156992</v>
+        <v>1.338522743997518</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339329803397794</v>
+        <v>1.339320660208574</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340706327159653</v>
+        <v>1.340703911219234</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340429627472493</v>
+        <v>1.34043235651753</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342534310501144</v>
+        <v>1.342541655290056</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341925039057884</v>
+        <v>1.341932329555947</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343298143277925</v>
+        <v>1.343304708565987</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341569455388403</v>
+        <v>1.341579714107736</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341248046129223</v>
+        <v>1.341256556350348</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343324510614341</v>
+        <v>1.34332707575372</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.34709854415723</v>
+        <v>1.347093483939986</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350817643079397</v>
+        <v>1.35080094131905</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351701789525126</v>
+        <v>1.351899926195851</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.349919887098007</v>
+        <v>1.350182381242233</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.347505134703088</v>
+        <v>1.34784178927701</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.344863475268675</v>
+        <v>1.34525145291678</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.344849338284679</v>
+        <v>1.345111090778842</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.346673385542321</v>
+        <v>1.34685654775022</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.348849758422382</v>
+        <v>1.348953682438448</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.351583624267451</v>
+        <v>1.351614334952132</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.351176979803101</v>
+        <v>1.351262497989643</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.352273854267205</v>
+        <v>1.35223092003409</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.355265816601457</v>
+        <v>1.35503549109836</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.365331648986587</v>
+        <v>1.364116543248338</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.377056609076334</v>
+        <v>1.373502743199374</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.366671663459111</v>
+        <v>1.35975466828369</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366668237191342</v>
+        <v>1.366670613644817</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359185343817562</v>
+        <v>1.359189699525113</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.35623652314097</v>
+        <v>1.356241767614474</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350390431516156</v>
+        <v>1.350397987281417</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348093993539222</v>
+        <v>1.348101876574655</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343921441769962</v>
+        <v>1.343929613921205</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339484059337395</v>
+        <v>1.339492405706965</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337026904866375</v>
+        <v>1.337035333028644</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339937725858043</v>
+        <v>1.339943169110942</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.33406794830895</v>
+        <v>1.334067296764582</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334982971479011</v>
+        <v>1.334982191237111</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.33280768147295</v>
+        <v>1.332806766907487</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332399555341031</v>
+        <v>1.332396426656558</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329778387968845</v>
+        <v>1.329775807994662</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327948518592676</v>
+        <v>1.327946405430876</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331252986142983</v>
+        <v>1.331251325578607</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329446152715171</v>
+        <v>1.32944772015278</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.32431368001392</v>
+        <v>1.324317676713461</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319520295303117</v>
+        <v>1.319526007150442</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319365048291104</v>
+        <v>1.319375562717337</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316534101172395</v>
+        <v>1.316543076026071</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320317755979786</v>
+        <v>1.320324444814875</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318724430406204</v>
+        <v>1.318719445120951</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313133084241626</v>
+        <v>1.313121050617403</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310798860940958</v>
+        <v>1.310780004847583</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303976325472854</v>
+        <v>1.30395327439802</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294224676734279</v>
+        <v>1.294196596581076</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290724270761247</v>
+        <v>1.290691413261635</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.29508052421973</v>
+        <v>1.295048293891348</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311998874568594</v>
+        <v>1.311946216547121</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.32472669955215</v>
+        <v>1.324671206539436</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356448099266597</v>
+        <v>1.356418009692595</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374704067952666</v>
+        <v>1.374698743538736</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380286734489398</v>
+        <v>1.380289427123884</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389506136209798</v>
+        <v>1.389517951579208</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391175816656059</v>
+        <v>1.391192804003442</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389565104235774</v>
+        <v>1.389592681008856</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389125363154628</v>
+        <v>1.389162227248719</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.39370383927905</v>
+        <v>1.393766186052025</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.39006172296964</v>
+        <v>1.390129287377019</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.393741215271727</v>
+        <v>1.393814805600804</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.37635004227407</v>
+        <v>1.376404297147455</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371461645699027</v>
+        <v>1.371513526945526</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358136193172526</v>
+        <v>1.358167486115334</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339453088384012</v>
+        <v>1.339456029368593</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330545556165995</v>
+        <v>1.330526291540508</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336541545386638</v>
+        <v>1.336528801955562</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338522743997518</v>
+        <v>1.338514588853089</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339320660208574</v>
+        <v>1.339311715118224</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340703911219234</v>
+        <v>1.340701536711495</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.34043235651753</v>
+        <v>1.34043500335501</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342541655290056</v>
+        <v>1.342548814930092</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341932329555947</v>
+        <v>1.34193944045526</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343304708565987</v>
+        <v>1.343311135958389</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341579714107736</v>
+        <v>1.341589747165819</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341256556350348</v>
+        <v>1.341264890169074</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.34332707575372</v>
+        <v>1.343329610115893</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347093483939986</v>
+        <v>1.347088566379035</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.35080094131905</v>
+        <v>1.35078465137118</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.351899926195851</v>
+        <v>1.352107994895265</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350182381242233</v>
+        <v>1.350453183557725</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.34784178927701</v>
+        <v>1.348186017369194</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.34525145291678</v>
+        <v>1.345659455067892</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.345111090778842</v>
+        <v>1.345381036303513</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.34685654775022</v>
+        <v>1.347050764398534</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.348953682438448</v>
+        <v>1.349071274729795</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.351614334952132</v>
+        <v>1.35166167241794</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.351262497989643</v>
+        <v>1.351360350527424</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.35223092003409</v>
+        <v>1.352203826153882</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.35503549109836</v>
+        <v>1.354834027914991</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.364116543248338</v>
+        <v>1.363055355145583</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.373502743199374</v>
+        <v>1.370644966645104</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.35975466828369</v>
+        <v>1.356210476102848</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366670613644817</v>
+        <v>1.366672934839493</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359189699525113</v>
+        <v>1.35919395418073</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356241767614474</v>
+        <v>1.356246890946903</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350397987281417</v>
+        <v>1.350405368383831</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348101876574655</v>
+        <v>1.348109577326902</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343929613921205</v>
+        <v>1.343937597045117</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339492405706965</v>
+        <v>1.339500558999017</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337035333028644</v>
+        <v>1.337043566242141</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339943169110942</v>
+        <v>1.339948489175321</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334067296764582</v>
+        <v>1.334066661598969</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334982191237111</v>
+        <v>1.3349814303972</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332806766907487</v>
+        <v>1.332805874889349</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332396426656558</v>
+        <v>1.332393372298716</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329775807994662</v>
+        <v>1.32977328885221</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327946405430876</v>
+        <v>1.327944341581503</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331251325578607</v>
+        <v>1.331249703690492</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.32944772015278</v>
+        <v>1.329449249377172</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324317676713461</v>
+        <v>1.324321578564805</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319526007150442</v>
+        <v>1.319531583882421</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319375562717337</v>
+        <v>1.319385834048412</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316543076026071</v>
+        <v>1.316551849480444</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320324444814875</v>
+        <v>1.320330989132926</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318719445120951</v>
+        <v>1.318714584047155</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313121050617403</v>
+        <v>1.313109305679965</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310780004847583</v>
+        <v>1.310761596724823</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.30395327439802</v>
+        <v>1.30393076810316</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294196596581076</v>
+        <v>1.294169177704279</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290691413261635</v>
+        <v>1.290659326833589</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295048293891348</v>
+        <v>1.295016812745421</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311946216547121</v>
+        <v>1.311894761886254</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324671206539436</v>
+        <v>1.324616981566539</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356418009692595</v>
+        <v>1.356388594675948</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374698743538736</v>
+        <v>1.37469353526734</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380289427123884</v>
+        <v>1.380292042808269</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389517951579208</v>
+        <v>1.389529470376248</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391192804003442</v>
+        <v>1.391209362338503</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389592681008856</v>
+        <v>1.389619581313365</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389162227248719</v>
+        <v>1.389198197449148</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.393766186052025</v>
+        <v>1.393827088343773</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.390129287377019</v>
+        <v>1.390195298503019</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.393814805600804</v>
+        <v>1.393886716137316</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376404297147455</v>
+        <v>1.376457340140925</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371513526945526</v>
+        <v>1.37156426367669</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358167486115334</v>
+        <v>1.358198113623816</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339456029368593</v>
+        <v>1.339458925783524</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330526291540508</v>
+        <v>1.330507461326905</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336528801955562</v>
+        <v>1.336516346246906</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338514588853089</v>
+        <v>1.338506614544787</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339311715118224</v>
+        <v>1.339302961812359</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340701536711495</v>
+        <v>1.34069920272278</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.34043500335501</v>
+        <v>1.340437571459135</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342548814930092</v>
+        <v>1.342555796290346</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.34193944045526</v>
+        <v>1.341946378266503</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343311135958389</v>
+        <v>1.343317429660266</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341589747165819</v>
+        <v>1.341599561878621</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341264890169074</v>
+        <v>1.341273052908745</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343329610115893</v>
+        <v>1.343332113803277</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347088566379035</v>
+        <v>1.347083785819034</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.35078465137118</v>
+        <v>1.350768758492961</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.352107994895265</v>
+        <v>1.352305270216488</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350453183557725</v>
+        <v>1.350707001929479</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.348186017369194</v>
+        <v>1.34849348054296</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.345659455067892</v>
+        <v>1.346030353534839</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.345381036303513</v>
+        <v>1.345611872244964</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.347050764398534</v>
+        <v>1.347212283915979</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.349071274729795</v>
+        <v>1.34915804653999</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.35166167241794</v>
+        <v>1.351676735050296</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.351360350527424</v>
+        <v>1.351409320511854</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.352203826153882</v>
+        <v>1.352126986829797</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.354834027914991</v>
+        <v>1.354591534891891</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.363055355145583</v>
+        <v>1.362046846653371</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.370644966645104</v>
+        <v>1.368157704131514</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.356210476102848</v>
+        <v>1.353556048937534</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366672934839493</v>
+        <v>1.366675202680504</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.35919395418073</v>
+        <v>1.359198111260353</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356246890946903</v>
+        <v>1.356251897286876</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350405368383831</v>
+        <v>1.350412580809236</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348109577326902</v>
+        <v>1.34811710204484</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343937597045117</v>
+        <v>1.343945397623791</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339500558999017</v>
+        <v>1.33950852583524</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337043566242141</v>
+        <v>1.337051611192027</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339948489175321</v>
+        <v>1.339953690181892</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334066661598969</v>
+        <v>1.334066042205457</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.3349814303972</v>
+        <v>1.334980688247352</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332805874889349</v>
+        <v>1.332805004597428</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332393372298716</v>
+        <v>1.332390389652085</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.32977328885221</v>
+        <v>1.329770828417005</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327944341581503</v>
+        <v>1.327942325338885</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331249703690492</v>
+        <v>1.331248119143571</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329449249377172</v>
+        <v>1.329450741765667</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324321578564805</v>
+        <v>1.324325388900355</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319531583882421</v>
+        <v>1.319537030231744</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319385834048412</v>
+        <v>1.319395870614769</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316551849480444</v>
+        <v>1.316560428225735</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320330989132926</v>
+        <v>1.320337393537445</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318714584047155</v>
+        <v>1.318709842626611</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313109305679965</v>
+        <v>1.313097839191017</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310761596724823</v>
+        <v>1.310743620832579</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.30393076810316</v>
+        <v>1.303908787547374</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294169177704279</v>
+        <v>1.29414239707548</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290659326833589</v>
+        <v>1.290627984722375</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.295016812745421</v>
+        <v>1.29498605500677</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311894761886254</v>
+        <v>1.311844469869693</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324616981566539</v>
+        <v>1.324563981731367</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356388594675948</v>
+        <v>1.356359831836143</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.37469353526734</v>
+        <v>1.374688439418059</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380292042808269</v>
+        <v>1.380294584698153</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389529470376248</v>
+        <v>1.389540703566468</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391209362338503</v>
+        <v>1.391225507575393</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389619581313365</v>
+        <v>1.389645829604461</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389198197449148</v>
+        <v>1.389233305716545</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.393827088343773</v>
+        <v>1.393886595668677</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.390195298503019</v>
+        <v>1.390259809158295</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.393886716137316</v>
+        <v>1.393957003614156</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376457340140925</v>
+        <v>1.376509211286669</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.37156426367669</v>
+        <v>1.371613893190833</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358198113623816</v>
+        <v>1.358228096519907</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339458925783524</v>
+        <v>1.33946177839234</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330507461326905</v>
+        <v>1.330489051043032</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336516346246906</v>
+        <v>1.336504168662328</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338506614544787</v>
+        <v>1.338498815161056</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339302961812359</v>
+        <v>1.339294394239533</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.34069920272278</v>
+        <v>1.340696908357357</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340437571459135</v>
+        <v>1.340440064117525</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342555796290346</v>
+        <v>1.342562605906161</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341946378266503</v>
+        <v>1.341953149191335</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343317429660266</v>
+        <v>1.343323593712216</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341599561878621</v>
+        <v>1.341609165251348</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341273052908745</v>
+        <v>1.341281049685669</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343332113803277</v>
+        <v>1.343334586955034</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347083785819034</v>
+        <v>1.347079136889219</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350768758492961</v>
+        <v>1.350753248624489</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.352305270216488</v>
+        <v>1.35232134246582</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350707001929479</v>
+        <v>1.350741459312038</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.34849348054296</v>
+        <v>1.348547912432486</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346030353534839</v>
+        <v>1.346017773890889</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.345611872244964</v>
+        <v>1.345556969763333</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.347212283915979</v>
+        <v>1.347078529210687</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.34915804653999</v>
+        <v>1.348935487948405</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.351676735050296</v>
+        <v>1.351356441916503</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.351409320511854</v>
+        <v>1.351057205035031</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.352126986829797</v>
+        <v>1.351550940560858</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.354591534891891</v>
+        <v>1.353751055257237</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.362046846653371</v>
+        <v>1.360300217911486</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.368157704131514</v>
+        <v>1.364774071351506</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.353556048937534</v>
+        <v>1.349086118499642</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B114"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366675202680504</v>
+        <v>1.366677418986406</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359198111260353</v>
+        <v>1.359202174082327</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356251897286876</v>
+        <v>1.356256790595749</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350412580809236</v>
+        <v>1.350419630273102</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.34811710204484</v>
+        <v>1.348124456695009</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343945397623791</v>
+        <v>1.343953021846354</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.33950852583524</v>
+        <v>1.339516312538015</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337051611192027</v>
+        <v>1.337059474261316</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339953690181892</v>
+        <v>1.339958776078929</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334066042205457</v>
+        <v>1.334065438006849</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334980688247352</v>
+        <v>1.334979964109932</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332805004597428</v>
+        <v>1.332804155249896</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332390389652085</v>
+        <v>1.332387476222437</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329770828417005</v>
+        <v>1.329768424662274</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327942325338885</v>
+        <v>1.327940355075095</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331248119143571</v>
+        <v>1.331246570663498</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329450741765667</v>
+        <v>1.32945219863032</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324325388900355</v>
+        <v>1.3243291108984</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319537030231744</v>
+        <v>1.319542350712862</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319395870614769</v>
+        <v>1.319405680370688</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316560428225735</v>
+        <v>1.316568818659719</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320337393537445</v>
+        <v>1.320343662439897</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318709842626611</v>
+        <v>1.31870521652034</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313097839191017</v>
+        <v>1.313086641389587</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310743620832579</v>
+        <v>1.310726062158038</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303908787547374</v>
+        <v>1.303887314564875</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.29414239707548</v>
+        <v>1.294116232720694</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290627984722375</v>
+        <v>1.290597361393709</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.29498605500677</v>
+        <v>1.294955996067148</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311844469869693</v>
+        <v>1.311795301594531</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324563981731367</v>
+        <v>1.324512166042496</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356359831836143</v>
+        <v>1.356331699769538</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374688439418059</v>
+        <v>1.374683452425818</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380294584698153</v>
+        <v>1.380297055782592</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389540703566468</v>
+        <v>1.389551661584076</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391225507575393</v>
+        <v>1.391241254856309</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389645829604461</v>
+        <v>1.389671449178228</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389233305716545</v>
+        <v>1.389267582512728</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.393886595668677</v>
+        <v>1.39394475530855</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.390259809158295</v>
+        <v>1.39032286979274</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.393957003614156</v>
+        <v>1.394025722243851</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376509211286669</v>
+        <v>1.376559948878513</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371613893190833</v>
+        <v>1.371662451190396</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358228096519907</v>
+        <v>1.358257454774303</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.33946177839234</v>
+        <v>1.339464587956806</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330489051043032</v>
+        <v>1.330471046841218</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336504168662328</v>
+        <v>1.336492260024047</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338498815161056</v>
+        <v>1.338491185043508</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339294394239533</v>
+        <v>1.339286006597847</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340696908357357</v>
+        <v>1.340694652737737</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340440064117525</v>
+        <v>1.340442484443289</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342562605906161</v>
+        <v>1.342569249999048</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341953149191335</v>
+        <v>1.341959759140416</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343323593712216</v>
+        <v>1.343329631997969</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341609165251348</v>
+        <v>1.341618563994657</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341281049685669</v>
+        <v>1.341288885418786</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343334586955034</v>
+        <v>1.343337029742829</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347079136889219</v>
+        <v>1.347074614486209</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350753248624489</v>
+        <v>1.350738108350334</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.35232134246582</v>
+        <v>1.35229938440236</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350741459312038</v>
+        <v>1.350799812997239</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.348547912432486</v>
+        <v>1.34866236196899</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346017773890889</v>
+        <v>1.346160315579086</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.345556969763333</v>
+        <v>1.345752262691317</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.347078529210687</v>
+        <v>1.347216062875954</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.348935487948405</v>
+        <v>1.349009720085195</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.351356441916503</v>
+        <v>1.351383995864044</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.351057205035031</v>
+        <v>1.351142194609734</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.351550940560858</v>
+        <v>1.3516609784824</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.353751055257237</v>
+        <v>1.353786748194552</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.360300217911486</v>
+        <v>1.35987506940212</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.364774071351506</v>
+        <v>1.363671447775393</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,15 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.349086118499642</v>
+        <v>1.349344190574632</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B115">
+        <v>1.350744395621822</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366677418986406</v>
+        <v>1.366679585494041</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359202174082327</v>
+        <v>1.359206145816231</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356256790595749</v>
+        <v>1.356261574658068</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350419630273102</v>
+        <v>1.350426522235618</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348124456695009</v>
+        <v>1.348131646977382</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343953021846354</v>
+        <v>1.343960475625334</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339516312538015</v>
+        <v>1.339523925147139</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337059474261316</v>
+        <v>1.337067161547758</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339958776078929</v>
+        <v>1.339963750642218</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334065438006849</v>
+        <v>1.334064848453649</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334979964109932</v>
+        <v>1.334979257339558</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332804155249896</v>
+        <v>1.332803326101896</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332387476222437</v>
+        <v>1.332384629629809</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329768424662274</v>
+        <v>1.329766075653396</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327940355075095</v>
+        <v>1.327938429235568</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331246570663498</v>
+        <v>1.331245057033236</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.32945219863032</v>
+        <v>1.329453621221734</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.3243291108984</v>
+        <v>1.324332747591921</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319542350712862</v>
+        <v>1.319547549634416</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319405680370688</v>
+        <v>1.31941527091528</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316568818659719</v>
+        <v>1.3165770269035</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320343662439897</v>
+        <v>1.32034980006953</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.31870521652034</v>
+        <v>1.318700701595619</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313086641389587</v>
+        <v>1.313075702964584</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310726062158038</v>
+        <v>1.31070890637423</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303887314564875</v>
+        <v>1.303866331815395</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294116232720694</v>
+        <v>1.294090663660826</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290597361393709</v>
+        <v>1.290567432465127</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294955996067148</v>
+        <v>1.294926612420042</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311795301594531</v>
+        <v>1.311747219871576</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324512166042496</v>
+        <v>1.324461495314143</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356331699769538</v>
+        <v>1.356304177996778</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374683452425818</v>
+        <v>1.374678570872979</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380297055782592</v>
+        <v>1.380299458894764</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389551661584076</v>
+        <v>1.389562354363595</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391241254856309</v>
+        <v>1.391256618597455</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389671449178228</v>
+        <v>1.389696462239237</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389267582512728</v>
+        <v>1.389301056887184</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.39394475530855</v>
+        <v>1.394001612436799</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.39032286979274</v>
+        <v>1.390384528625584</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394025722243851</v>
+        <v>1.394092923856653</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376559948878513</v>
+        <v>1.376609589564955</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371662451190396</v>
+        <v>1.371709971865978</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358257454774303</v>
+        <v>1.35828620754902</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339464587956806</v>
+        <v>1.339467355235293</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330471046841218</v>
+        <v>1.330453435474022</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336492260024047</v>
+        <v>1.336480611552149</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338491185043508</v>
+        <v>1.338483718773608</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339286006597847</v>
+        <v>1.339277793322357</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340694652737737</v>
+        <v>1.340692435004895</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340442484443289</v>
+        <v>1.340444835386173</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342569249999048</v>
+        <v>1.342575734495218</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341959759140416</v>
+        <v>1.341966213750178</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343329631997969</v>
+        <v>1.343335548251659</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341618563994657</v>
+        <v>1.341627764539878</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341288885418786</v>
+        <v>1.341296564838818</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343337029742829</v>
+        <v>1.343339442367007</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347074614486209</v>
+        <v>1.347070213758021</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350738108350334</v>
+        <v>1.350723324863633</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.35229938440236</v>
+        <v>1.352277907005636</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350799812997239</v>
+        <v>1.350697402061265</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.34866236196899</v>
+        <v>1.348589335798251</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346160315579086</v>
+        <v>1.346101496877834</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.345752262691317</v>
+        <v>1.345641480258664</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.347216062875954</v>
+        <v>1.347063120086519</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.349009720085195</v>
+        <v>1.348794497486635</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.351383995864044</v>
+        <v>1.35111371945497</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.351142194609734</v>
+        <v>1.350886041911488</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.3516609784824</v>
+        <v>1.35137043225644</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.353786748194552</v>
+        <v>1.353354505051474</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.35987506940212</v>
+        <v>1.358901267417813</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.363671447775393</v>
+        <v>1.36189518578145</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.349344190574632</v>
+        <v>1.348098058938084</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.350744395621822</v>
+        <v>1.345045828161505</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366679585494041</v>
+        <v>1.366681703863073</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359206145816231</v>
+        <v>1.35921002949112</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356261574658068</v>
+        <v>1.356266253091317</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350426522235618</v>
+        <v>1.350433261915789</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348131646977382</v>
+        <v>1.348138678340075</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343960475625334</v>
+        <v>1.343967764611931</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339523925147139</v>
+        <v>1.339531369435428</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337067161547758</v>
+        <v>1.33707467887959</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339963750642218</v>
+        <v>1.339968617484365</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334064848453649</v>
+        <v>1.334064273022423</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334979257339558</v>
+        <v>1.334978567321218</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332803326101896</v>
+        <v>1.332802516443385</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332384629629809</v>
+        <v>1.332381847602031</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329766075653396</v>
+        <v>1.32976377954273</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327938429235568</v>
+        <v>1.327936546335021</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331245057033236</v>
+        <v>1.331243577089875</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329453621221734</v>
+        <v>1.32945501073261</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324332747591921</v>
+        <v>1.32433630187678</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319547549634416</v>
+        <v>1.319552631110813</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.31941527091528</v>
+        <v>1.31942464951208</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.3165770269035</v>
+        <v>1.31658505881627</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.32034980006953</v>
+        <v>1.320355810482611</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318700701595619</v>
+        <v>1.318696293913927</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313075702964584</v>
+        <v>1.31306501502924</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.31070890637423</v>
+        <v>1.310692139801389</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303866331815395</v>
+        <v>1.303845822737917</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294090663660826</v>
+        <v>1.294065669856123</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290567432465127</v>
+        <v>1.290538174641917</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294926612420042</v>
+        <v>1.294897881599807</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311747219871576</v>
+        <v>1.311700189132169</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324461495314143</v>
+        <v>1.324411932067991</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356304177996778</v>
+        <v>1.356277246913552</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374678570872979</v>
+        <v>1.374673791481896</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380299458894764</v>
+        <v>1.380301796721839</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389562354363595</v>
+        <v>1.389572791369291</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391256618597455</v>
+        <v>1.39127161253178</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389696462239237</v>
+        <v>1.389720889963464</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389301056887184</v>
+        <v>1.389333756557648</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394001612436799</v>
+        <v>1.3940572102344</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.390384528625584</v>
+        <v>1.390444831767007</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394092923856653</v>
+        <v>1.394158658029671</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376609589564955</v>
+        <v>1.376658168436295</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371709971865978</v>
+        <v>1.371756487975143</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.35828620754902</v>
+        <v>1.358314373237463</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339467355235293</v>
+        <v>1.339470080981366</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330453435474022</v>
+        <v>1.330436204262176</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336480611552149</v>
+        <v>1.336469214843346</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338483718773608</v>
+        <v>1.338476411160191</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339277793322357</v>
+        <v>1.339269749073224</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340692435004895</v>
+        <v>1.340690254318384</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340444835386173</v>
+        <v>1.340447119742898</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342575734495218</v>
+        <v>1.342582065042809</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341966213750178</v>
+        <v>1.341972518398468</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343335548251659</v>
+        <v>1.343341346064711</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341627764539878</v>
+        <v>1.3416367730533</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341296564838818</v>
+        <v>1.341304092496935</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343339442367007</v>
+        <v>1.34334182505314</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347070213758021</v>
+        <v>1.347065930089188</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350723324863633</v>
+        <v>1.350708885932504</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.352277907005636</v>
+        <v>1.352256895031497</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350697402061265</v>
+        <v>1.350630419923296</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.348589335798251</v>
+        <v>1.348555062491706</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346101496877834</v>
+        <v>1.346082177497603</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.345641480258664</v>
+        <v>1.345578509855708</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.347063120086519</v>
+        <v>1.346964163857982</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.348794497486635</v>
+        <v>1.348639960237273</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.35111371945497</v>
+        <v>1.350910943479331</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.350886041911488</v>
+        <v>1.350704863451048</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.35137043225644</v>
+        <v>1.35116713858218</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.353354505051474</v>
+        <v>1.353030296174424</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.358901267417813</v>
+        <v>1.358111744586813</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.36189518578145</v>
+        <v>1.360474100290799</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.348098058938084</v>
+        <v>1.347308221873017</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.345045828161505</v>
+        <v>1.343665978009802</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366681703863073</v>
+        <v>1.366683775680227</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.35921002949112</v>
+        <v>1.359213828003229</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356266253091317</v>
+        <v>1.356270829355037</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350433261915789</v>
+        <v>1.3504398543046</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348138678340075</v>
+        <v>1.348145555993108</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343967764611931</v>
+        <v>1.343974894210302</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339531369435428</v>
+        <v>1.339538650923313</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.33707467887959</v>
+        <v>1.337082031830261</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339968617484365</v>
+        <v>1.339973380063508</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334064273022423</v>
+        <v>1.334063711214283</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334978567321218</v>
+        <v>1.334977893468499</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332802516443385</v>
+        <v>1.332801725597127</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332381847602031</v>
+        <v>1.3323791279687</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.32976377954273</v>
+        <v>1.329761534564788</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327936546335021</v>
+        <v>1.327934704953633</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331243577089875</v>
+        <v>1.331242129721653</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.32945501073261</v>
+        <v>1.329456368301055</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.32433630187678</v>
+        <v>1.324339776519386</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319552631110813</v>
+        <v>1.319557599073049</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.31942464951208</v>
+        <v>1.31943382310736</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.31658505881627</v>
+        <v>1.316592920009143</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320355810482611</v>
+        <v>1.320361697571115</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318696293913927</v>
+        <v>1.318691989719712</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.31306501502924</v>
+        <v>1.313054569097256</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310692139801389</v>
+        <v>1.310675749370879</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303845822737917</v>
+        <v>1.303825771507477</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294065669856123</v>
+        <v>1.294041232154302</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290538174641917</v>
+        <v>1.290509565657278</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294897881599807</v>
+        <v>1.294869782124775</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311700189132169</v>
+        <v>1.311654175341</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324411932067991</v>
+        <v>1.324363440441329</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356277246913552</v>
+        <v>1.356250887744462</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374673791481896</v>
+        <v>1.374669111107919</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380301796721839</v>
+        <v>1.380304071814111</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389572791369291</v>
+        <v>1.38958298162255</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.39127161253178</v>
+        <v>1.391286249748738</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389720889963464</v>
+        <v>1.389744752556918</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389333756557648</v>
+        <v>1.389365707985257</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.3940572102344</v>
+        <v>1.394111589998332</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.390444831767007</v>
+        <v>1.390503823331906</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394158658029671</v>
+        <v>1.394222972207713</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376658168436295</v>
+        <v>1.376705719106318</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371756487975143</v>
+        <v>1.371802030916362</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358314373237463</v>
+        <v>1.35834196950216</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339470080981366</v>
+        <v>1.339472765942566</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330436204262176</v>
+        <v>1.330419341064548</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336469214843346</v>
+        <v>1.336458061851074</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338476411160191</v>
+        <v>1.338469257227744</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339269749073224</v>
+        <v>1.339261868724568</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340690254318384</v>
+        <v>1.340688109856377</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340447119742898</v>
+        <v>1.340449340166714</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342582065042809</v>
+        <v>1.34258824702793</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341972518398468</v>
+        <v>1.341978678219124</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343341346064711</v>
+        <v>1.343347028892367</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.3416367730533</v>
+        <v>1.341645595449604</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341304092496935</v>
+        <v>1.341311472772969</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.34334182505314</v>
+        <v>1.343344178048914</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347065930089188</v>
+        <v>1.3470617590869</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350708885932504</v>
+        <v>1.350694779868648</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.352256895031497</v>
+        <v>1.352236333858011</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.350630419923296</v>
+        <v>1.35067988372104</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.348555062491706</v>
+        <v>1.3486527170028</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346082177497603</v>
+        <v>1.346199895383469</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.345578509855708</v>
+        <v>1.345671213571831</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.346964163857982</v>
+        <v>1.347030832213596</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.348639960237273</v>
+        <v>1.348665017902995</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.350910943479331</v>
+        <v>1.350903713905999</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.350704863451048</v>
+        <v>1.350748618279623</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.35116713858218</v>
+        <v>1.351230540278654</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.353030296174424</v>
+        <v>1.353027942069957</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.358111744586813</v>
+        <v>1.35776948446835</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.360474100290799</v>
+        <v>1.359737768764894</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.347308221873017</v>
+        <v>1.347466142009907</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.343665978009802</v>
+        <v>1.344920044106392</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.366683775680227</v>
+        <v>1.36668580246326</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359213828003229</v>
+        <v>1.359217544123172</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356270829355037</v>
+        <v>1.356275306759352</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.3504398543046</v>
+        <v>1.350446304177333</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348145555993108</v>
+        <v>1.348152284921269</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343974894210302</v>
+        <v>1.343981869590907</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339538650923313</v>
+        <v>1.339545774892473</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337082031830261</v>
+        <v>1.337089225732206</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339973380063508</v>
+        <v>1.339978041691477</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.334063711214283</v>
+        <v>1.33406316255346</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334977893468499</v>
+        <v>1.334977235221957</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332801725597127</v>
+        <v>1.332800952916827</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.3323791279687</v>
+        <v>1.332376468655548</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329761534564788</v>
+        <v>1.329759339031722</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327934704953633</v>
+        <v>1.327932903733481</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.331242129721653</v>
+        <v>1.33124071386518</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329456368301055</v>
+        <v>1.329457695013661</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324339776519386</v>
+        <v>1.324343174163832</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319557599073049</v>
+        <v>1.319562457278794</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.31943382310736</v>
+        <v>1.319442798347258</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316592920009143</v>
+        <v>1.316600615858118</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320361697571115</v>
+        <v>1.320367465070888</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318691989719712</v>
+        <v>1.318687785429938</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313054569097256</v>
+        <v>1.313044357060545</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310675749370879</v>
+        <v>1.310659722591512</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303825771507477</v>
+        <v>1.303806162994809</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294041232154302</v>
+        <v>1.294017332242062</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290509565657278</v>
+        <v>1.290481584216368</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294869782124775</v>
+        <v>1.294842293444048</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311654175341</v>
+        <v>1.311609145914491</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324363440441329</v>
+        <v>1.324315986101056</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356250887744462</v>
+        <v>1.356225082499775</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374669111107919</v>
+        <v>1.374664526732795</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380304071814111</v>
+        <v>1.380306286593469</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.38958298162255</v>
+        <v>1.389592933727382</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391286249748738</v>
+        <v>1.391300542731333</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389744752556918</v>
+        <v>1.389768069310321</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389365707985257</v>
+        <v>1.389396936444681</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394111589998332</v>
+        <v>1.394164791243009</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.390503823331906</v>
+        <v>1.390561545546394</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394222972207713</v>
+        <v>1.394285911816453</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376705719106318</v>
+        <v>1.376752273788905</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371802030916362</v>
+        <v>1.371846630798461</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.35834196950216</v>
+        <v>1.358369013310339</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339472765942566</v>
+        <v>1.339475410859358</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330419341064548</v>
+        <v>1.330402834249985</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336458061851074</v>
+        <v>1.336447144866832</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338469257227744</v>
+        <v>1.338462252205392</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.339261868724568</v>
+        <v>1.33925414735396</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340688109856377</v>
+        <v>1.340686000815634</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340449340166714</v>
+        <v>1.340451499176281</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.34258824702793</v>
+        <v>1.342594285589617</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341978678219124</v>
+        <v>1.341984698115594</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343347028892367</v>
+        <v>1.343352600059883</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341645595449604</v>
+        <v>1.341654237404481</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341311472772969</v>
+        <v>1.341318709883191</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343344178048914</v>
+        <v>1.343346501621324</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.3470617590869</v>
+        <v>1.347057696568091</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350694779868648</v>
+        <v>1.350680995497934</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.352236333858011</v>
+        <v>1.352216209454879</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.35067988372104</v>
+        <v>1.35072752564616</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.3486527170028</v>
+        <v>1.348753958388034</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346199895383469</v>
+        <v>1.346323675420972</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.345671213571831</v>
+        <v>1.345767261333807</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.347030832213596</v>
+        <v>1.3471063746012</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.348665017902995</v>
+        <v>1.348696883760465</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.350903713905999</v>
+        <v>1.35088113994948</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.350748618279623</v>
+        <v>1.350738760721715</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.351230540278654</v>
+        <v>1.351195451857321</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.353027942069957</v>
+        <v>1.352832994107185</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.35776948446835</v>
+        <v>1.357129325626787</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.359737768764894</v>
+        <v>1.358505566682056</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.347466142009907</v>
+        <v>1.346455981405359</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.344920044106392</v>
+        <v>1.342725819373445</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPUSD_forecast.xlsx
+++ b/public/data/files/GBPUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>1.36668580246326</v>
+        <v>1.366687785664654</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>1.359217544123172</v>
+        <v>1.35922118050268</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>1.356275306759352</v>
+        <v>1.356279688472947</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>1.350446304177333</v>
+        <v>1.350452616105098</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>1.348152284921269</v>
+        <v>1.34815886989615</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>1.343981869590907</v>
+        <v>1.343988695703006</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>1.339545774892473</v>
+        <v>1.339552746398607</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>1.337089225732206</v>
+        <v>1.337096265689725</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>1.339978041691477</v>
+        <v>1.339982605541442</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>1.33406316255346</v>
+        <v>1.334062626585999</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>1.334977235221957</v>
+        <v>1.334976592047587</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>1.332800952916827</v>
+        <v>1.332800197785386</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>1.332376468655548</v>
+        <v>1.33237386767918</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>1.329759339031722</v>
+        <v>1.329757191329101</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>1.327932903733481</v>
+        <v>1.327931141375204</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>1.33124071386518</v>
+        <v>1.331239328502835</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>1.329457695013661</v>
+        <v>1.329458991908384</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>1.324343174163832</v>
+        <v>1.324346497338577</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>1.319562457278794</v>
+        <v>1.319567209321843</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>1.319442798347258</v>
+        <v>1.31945158159381</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>1.316600615858118</v>
+        <v>1.31660815151624</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>1.320367465070888</v>
+        <v>1.320373116569346</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>1.318687785429938</v>
+        <v>1.318683677624327</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>1.313044357060545</v>
+        <v>1.313034371168437</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>1.310659722591512</v>
+        <v>1.310644047518065</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>1.303806162994809</v>
+        <v>1.303786982728603</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>1.294017332242062</v>
+        <v>1.293993952599741</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>1.290481584216368</v>
+        <v>1.29045420994397</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>1.294842293444048</v>
+        <v>1.294815395887713</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>1.311609145914491</v>
+        <v>1.311565069644326</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>1.324315986101056</v>
+        <v>1.324269536163112</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>1.356225082499775</v>
+        <v>1.356199813934837</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>1.374664526732795</v>
+        <v>1.374660035458465</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>1.380306286593469</v>
+        <v>1.380308443361249</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>1.389592933727382</v>
+        <v>1.389602655894179</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>1.391300542731333</v>
+        <v>1.391314503390628</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>1.389768069310321</v>
+        <v>1.389790858650147</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>1.389396936444681</v>
+        <v>1.389427466089628</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>1.394164791243009</v>
+        <v>1.394216851795245</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>1.390561545546394</v>
+        <v>1.390618038847561</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>1.394285911816453</v>
+        <v>1.394347520368476</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>1.376752273788905</v>
+        <v>1.376797863369936</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>1.371846630798461</v>
+        <v>1.371890316505871</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>1.358369013310339</v>
+        <v>1.358395520967452</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>1.339475410859358</v>
+        <v>1.339478016464232</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>1.330402834249985</v>
+        <v>1.330386672670901</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>1.336447144866832</v>
+        <v>1.336436456502679</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>1.338462252205392</v>
+        <v>1.338455391516559</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>1.33925414735396</v>
+        <v>1.339246580232523</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>1.340686000815634</v>
+        <v>1.340683926411407</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>1.340451499176281</v>
+        <v>1.340453599163894</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>1.342594285589617</v>
+        <v>1.342600185633768</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>1.341984698115594</v>
+        <v>1.341990582773648</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>1.343352600059883</v>
+        <v>1.343358062768398</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>1.341654237404481</v>
+        <v>1.341662704366513</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>1.341318709883191</v>
+        <v>1.341325807887686</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>1.343346501621324</v>
+        <v>1.343348796054139</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>1.347057696568091</v>
+        <v>1.347053738547387</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>1.350680995497934</v>
+        <v>1.350667522132863</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>1.352216209454879</v>
+        <v>1.352196508354585</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>1.35072752564616</v>
+        <v>1.350773436165726</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>1.348753958388034</v>
+        <v>1.348860448470888</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>1.346323675420972</v>
+        <v>1.346466460479829</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>1.345767261333807</v>
+        <v>1.345921042302126</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>1.3471063746012</v>
+        <v>1.347253669071548</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>1.348696883760465</v>
+        <v>1.348818877837676</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>1.35088113994948</v>
+        <v>1.350959754708442</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>1.350738760721715</v>
+        <v>1.350842334611154</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>1.351195451857321</v>
+        <v>1.351288427421895</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>1.352832994107185</v>
+        <v>1.352819479017216</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>1.357129325626787</v>
+        <v>1.356786463137595</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>1.358505566682056</v>
+        <v>1.357857365247346</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>1.346455981405359</v>
+        <v>1.346566122876506</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>1.342725819373445</v>
+        <v>1.343803518989225</v>
       </c>
     </row>
   </sheetData>
